--- a/research/HyperParams.xlsx
+++ b/research/HyperParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Subnet-18-Zeus\research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8B2C75-A354-4938-A13C-FA59280F94B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B98F8C-1D55-4629-ADC4-8C89684CC3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{701B61B4-A6E2-434A-B336-77C79E78CCA1}"/>
   </bookViews>
@@ -111,9 +111,6 @@
     <t>Mode.2</t>
   </si>
   <si>
-    <t>Mode.3</t>
-  </si>
-  <si>
     <t>Mode.4</t>
   </si>
   <si>
@@ -124,6 +121,9 @@
   </si>
   <si>
     <t>Mode.7</t>
+  </si>
+  <si>
+    <t>Mode.3  --- diver</t>
   </si>
 </sst>
 </file>
@@ -535,19 +535,19 @@
         <v>23</v>
       </c>
       <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>15</v>
@@ -744,7 +744,7 @@
       <c r="D9" s="7">
         <v>512</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="7">
         <v>64</v>
       </c>
       <c r="F9" s="5">

--- a/research/HyperParams.xlsx
+++ b/research/HyperParams.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Subnet-18-Zeus\research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B98F8C-1D55-4629-ADC4-8C89684CC3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F0814D-5F01-447C-A7E9-A1257294EC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{701B61B4-A6E2-434A-B336-77C79E78CCA1}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="2" xr2:uid="{701B61B4-A6E2-434A-B336-77C79E78CCA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="232">
   <si>
     <t>H</t>
   </si>
@@ -124,13 +126,634 @@
   </si>
   <si>
     <t>Mode.3  --- diver</t>
+  </si>
+  <si>
+    <t>Epoch 1, loss: 10.346706</t>
+  </si>
+  <si>
+    <t>Epoch 2, loss: 9.306038</t>
+  </si>
+  <si>
+    <t>Epoch 3, loss: 8.720799</t>
+  </si>
+  <si>
+    <t>Epoch 4, loss: 8.249773</t>
+  </si>
+  <si>
+    <t>Epoch 5, loss: 7.859680</t>
+  </si>
+  <si>
+    <t>Epoch 6, loss: 7.501871</t>
+  </si>
+  <si>
+    <t>Epoch 7, loss: 7.196929</t>
+  </si>
+  <si>
+    <t>Epoch 8, loss: 6.938165</t>
+  </si>
+  <si>
+    <t>Epoch 9, loss: 6.700725</t>
+  </si>
+  <si>
+    <t>Epoch 10, loss: 6.484732</t>
+  </si>
+  <si>
+    <t>Epoch 11, loss: 6.364629</t>
+  </si>
+  <si>
+    <t>Epoch 12, loss: 6.168781</t>
+  </si>
+  <si>
+    <t>Epoch 13, loss: 6.006773</t>
+  </si>
+  <si>
+    <t>Epoch 14, loss: 5.889474</t>
+  </si>
+  <si>
+    <t>Epoch 15, loss: 5.759676</t>
+  </si>
+  <si>
+    <t>Epoch 16, loss: 5.664981</t>
+  </si>
+  <si>
+    <t>Epoch 17, loss: 5.557730</t>
+  </si>
+  <si>
+    <t>Epoch 18, loss: 5.469544</t>
+  </si>
+  <si>
+    <t>Epoch 19, loss: 5.383344</t>
+  </si>
+  <si>
+    <t>Epoch 20, loss: 5.352592</t>
+  </si>
+  <si>
+    <t>Epoch 21, loss: 5.269504</t>
+  </si>
+  <si>
+    <t>Epoch 22, loss: 5.199634</t>
+  </si>
+  <si>
+    <t>Epoch 23, loss: 5.123388</t>
+  </si>
+  <si>
+    <t>Epoch 24, loss: 5.063388</t>
+  </si>
+  <si>
+    <t>Epoch 25, loss: 5.017103</t>
+  </si>
+  <si>
+    <t>Epoch 26, loss: 4.970678</t>
+  </si>
+  <si>
+    <t>Epoch 27, loss: 4.915464</t>
+  </si>
+  <si>
+    <t>factor 5, 24c-12c-c, 1e-3</t>
+  </si>
+  <si>
+    <t>factor 5, 24c-24c-12c-c, 1e-3</t>
+  </si>
+  <si>
+    <t>Epoch 2, loss: 9.538632</t>
+  </si>
+  <si>
+    <t>Epoch 3, loss: 8.910780</t>
+  </si>
+  <si>
+    <t>Epoch 4, loss: 8.409369</t>
+  </si>
+  <si>
+    <t>Epoch 5, loss: 7.986500</t>
+  </si>
+  <si>
+    <t>Epoch 6, loss: 7.615491</t>
+  </si>
+  <si>
+    <t>Epoch 7, loss: 7.286349</t>
+  </si>
+  <si>
+    <t>Epoch 8, loss: 7.005177</t>
+  </si>
+  <si>
+    <t>Epoch 9, loss: 6.752085</t>
+  </si>
+  <si>
+    <t>Epoch 10, loss: 6.547058</t>
+  </si>
+  <si>
+    <t>Epoch 11, loss: 6.363682</t>
+  </si>
+  <si>
+    <t>Epoch 12, loss: 6.223873</t>
+  </si>
+  <si>
+    <t>Epoch 13, loss: 6.069219</t>
+  </si>
+  <si>
+    <t>Epoch 14, loss: 5.917526</t>
+  </si>
+  <si>
+    <t>Epoch 15, loss: 5.808626</t>
+  </si>
+  <si>
+    <t>Epoch 16, loss: 5.693556</t>
+  </si>
+  <si>
+    <t>Epoch 1, loss: 10.534499</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">factor 5, 24c-24c-12c-c, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1e-5</t>
+    </r>
+  </si>
+  <si>
+    <t>Epoch 1, loss: 11.471894</t>
+  </si>
+  <si>
+    <t>Epoch 2, loss: 11.396761</t>
+  </si>
+  <si>
+    <t>Epoch 3, loss: 11.330163</t>
+  </si>
+  <si>
+    <t>Epoch 1, loss: 12.281869</t>
+  </si>
+  <si>
+    <t>Epoch 2, loss: 10.475530</t>
+  </si>
+  <si>
+    <t>Epoch 3, loss: 9.022104</t>
+  </si>
+  <si>
+    <t>Epoch 4, loss: 7.710941</t>
+  </si>
+  <si>
+    <t>Epoch 5, loss: 6.686558</t>
+  </si>
+  <si>
+    <t>Epoch 6, loss: 5.719036</t>
+  </si>
+  <si>
+    <t>Epoch 7, loss: 4.880164</t>
+  </si>
+  <si>
+    <t>Epoch 8, loss: 4.163061</t>
+  </si>
+  <si>
+    <t>Epoch 9, loss: 3.394669</t>
+  </si>
+  <si>
+    <t>Epoch 10, loss: 2.838234</t>
+  </si>
+  <si>
+    <t>Epoch 11, loss: 2.425724</t>
+  </si>
+  <si>
+    <t>Epoch 12, loss: 1.996673</t>
+  </si>
+  <si>
+    <t>Epoch 13, loss: 1.602676</t>
+  </si>
+  <si>
+    <t>Epoch 14, loss: 1.530042</t>
+  </si>
+  <si>
+    <t>Epoch 15, loss: 1.242557</t>
+  </si>
+  <si>
+    <t>Epoch 16, loss: 1.260838</t>
+  </si>
+  <si>
+    <t>Epoch 17, loss: 1.161841</t>
+  </si>
+  <si>
+    <t>Epoch 18, loss: 1.201096</t>
+  </si>
+  <si>
+    <t>Epoch 19, loss: 1.398683</t>
+  </si>
+  <si>
+    <t>Epoch 20, loss: 1.213396</t>
+  </si>
+  <si>
+    <t>Epoch 1, loss: 11.477462</t>
+  </si>
+  <si>
+    <t>Epoch 2, loss: 10.243162</t>
+  </si>
+  <si>
+    <t>Epoch 3, loss: 9.420267</t>
+  </si>
+  <si>
+    <t>Epoch 4, loss: 8.697382</t>
+  </si>
+  <si>
+    <t>Epoch 5, loss: 8.088422</t>
+  </si>
+  <si>
+    <t>Epoch 6, loss: 7.508651</t>
+  </si>
+  <si>
+    <t>Epoch 7, loss: 7.041237</t>
+  </si>
+  <si>
+    <t>Epoch 8, loss: 6.598259</t>
+  </si>
+  <si>
+    <t>Epoch 9, loss: 6.194946</t>
+  </si>
+  <si>
+    <t>Epoch 10, loss: 5.867760</t>
+  </si>
+  <si>
+    <t>Epoch 11, loss: 5.454253</t>
+  </si>
+  <si>
+    <t>Epoch 12, loss: 5.222091</t>
+  </si>
+  <si>
+    <t>Epoch 13, loss: 4.901389</t>
+  </si>
+  <si>
+    <t>Epoch 14, loss: 4.663501</t>
+  </si>
+  <si>
+    <t>Epoch 15, loss: 4.540565</t>
+  </si>
+  <si>
+    <t>Epoch 16, loss: 4.334877</t>
+  </si>
+  <si>
+    <t>Epoch 17, loss: 4.141030</t>
+  </si>
+  <si>
+    <t>Epoch 18, loss: 3.982562</t>
+  </si>
+  <si>
+    <t>Epoch 19, loss: 3.864969</t>
+  </si>
+  <si>
+    <t>Epoch 20, loss: 3.784898</t>
+  </si>
+  <si>
+    <t>Epoch 21, loss: 3.635381</t>
+  </si>
+  <si>
+    <t>Epoch 22, loss: 3.539110</t>
+  </si>
+  <si>
+    <t>Epoch 23, loss: 3.377213</t>
+  </si>
+  <si>
+    <t>Epoch 24, loss: 3.352773</t>
+  </si>
+  <si>
+    <t>Epoch 25, loss: 3.223030</t>
+  </si>
+  <si>
+    <t>Epoch 26, loss: 3.061386</t>
+  </si>
+  <si>
+    <t>Epoch 27, loss: 2.974332</t>
+  </si>
+  <si>
+    <t>Epoch 28, loss: 2.900237</t>
+  </si>
+  <si>
+    <t>Epoch 29, loss: 2.798476</t>
+  </si>
+  <si>
+    <t>Epoch 30, loss: 2.729570</t>
+  </si>
+  <si>
+    <t>Epoch 31, loss: 2.627523</t>
+  </si>
+  <si>
+    <t>Epoch 32, loss: 2.535836</t>
+  </si>
+  <si>
+    <t>Epoch 33, loss: 2.473301</t>
+  </si>
+  <si>
+    <t>Epoch 34, loss: 2.386200</t>
+  </si>
+  <si>
+    <t>Epoch 35, loss: 2.317128</t>
+  </si>
+  <si>
+    <t>Epoch 36, loss: 2.259426</t>
+  </si>
+  <si>
+    <t>Epoch 37, loss: 2.191773</t>
+  </si>
+  <si>
+    <t>Epoch 38, loss: 2.123129</t>
+  </si>
+  <si>
+    <t>Epoch 39, loss: 2.048693</t>
+  </si>
+  <si>
+    <t>Epoch 40, loss: 2.002573</t>
+  </si>
+  <si>
+    <t>Epoch 41, loss: 1.940473</t>
+  </si>
+  <si>
+    <t>Epoch 42, loss: 1.886076</t>
+  </si>
+  <si>
+    <t>Epoch 43, loss: 1.835834</t>
+  </si>
+  <si>
+    <t>Epoch 44, loss: 1.777252</t>
+  </si>
+  <si>
+    <t>Epoch 45, loss: 1.725334</t>
+  </si>
+  <si>
+    <t>Epoch 46, loss: 1.681463</t>
+  </si>
+  <si>
+    <t>Epoch 47, loss: 1.639722</t>
+  </si>
+  <si>
+    <t>Epoch 48, loss: 1.596332</t>
+  </si>
+  <si>
+    <t>Epoch 49, loss: 1.554901</t>
+  </si>
+  <si>
+    <t>Epoch 50, loss: 1.518641</t>
+  </si>
+  <si>
+    <t>Epoch 51, loss: 1.475791</t>
+  </si>
+  <si>
+    <t>Epoch 52, loss: 1.436789</t>
+  </si>
+  <si>
+    <t>Epoch 53, loss: 1.400769</t>
+  </si>
+  <si>
+    <t>Epoch 54, loss: 1.368222</t>
+  </si>
+  <si>
+    <t>Epoch 55, loss: 1.341401</t>
+  </si>
+  <si>
+    <t>Epoch 56, loss: 1.310616</t>
+  </si>
+  <si>
+    <t>Epoch 57, loss: 1.280481</t>
+  </si>
+  <si>
+    <t>Epoch 58, loss: 1.256044</t>
+  </si>
+  <si>
+    <t>Epoch 59, loss: 1.228986</t>
+  </si>
+  <si>
+    <t>Epoch 60, loss: 1.216789</t>
+  </si>
+  <si>
+    <t>Epoch 61, loss: 1.184456</t>
+  </si>
+  <si>
+    <t>Epoch 62, loss: 1.158072</t>
+  </si>
+  <si>
+    <t>Epoch 63, loss: 1.136714</t>
+  </si>
+  <si>
+    <t>Epoch 64, loss: 1.114737</t>
+  </si>
+  <si>
+    <t>Epoch 65, loss: 1.101069</t>
+  </si>
+  <si>
+    <t>Epoch 66, loss: 1.081159</t>
+  </si>
+  <si>
+    <t>Epoch 67, loss: 1.061044</t>
+  </si>
+  <si>
+    <t>Epoch 68, loss: 1.058828</t>
+  </si>
+  <si>
+    <t>Epoch 69, loss: 1.034818</t>
+  </si>
+  <si>
+    <t>Epoch 70, loss: 1.012495</t>
+  </si>
+  <si>
+    <t>Epoch 71, loss: 0.997314</t>
+  </si>
+  <si>
+    <t>Epoch 72, loss: 0.985868</t>
+  </si>
+  <si>
+    <t>Epoch 73, loss: 0.971784</t>
+  </si>
+  <si>
+    <t>Epoch 74, loss: 0.958516</t>
+  </si>
+  <si>
+    <t>Epoch 75, loss: 0.945669</t>
+  </si>
+  <si>
+    <t>Epoch 76, loss: 0.935403</t>
+  </si>
+  <si>
+    <t>Epoch 77, loss: 0.927497</t>
+  </si>
+  <si>
+    <t>Epoch 78, loss: 0.918171</t>
+  </si>
+  <si>
+    <t>Epoch 79, loss: 0.907163</t>
+  </si>
+  <si>
+    <t>Epoch 80, loss: 0.891689</t>
+  </si>
+  <si>
+    <t>Epoch 81, loss: 0.880421</t>
+  </si>
+  <si>
+    <t>Epoch 82, loss: 0.871693</t>
+  </si>
+  <si>
+    <t>Epoch 83, loss: 0.866567</t>
+  </si>
+  <si>
+    <t>Epoch 84, loss: 0.858507</t>
+  </si>
+  <si>
+    <t>Epoch 85, loss: 0.843729</t>
+  </si>
+  <si>
+    <t>Epoch 86, loss: 0.834172</t>
+  </si>
+  <si>
+    <t>Epoch 87, loss: 0.843587</t>
+  </si>
+  <si>
+    <t>Epoch 88, loss: 0.827720</t>
+  </si>
+  <si>
+    <t>Epoch 89, loss: 0.810280</t>
+  </si>
+  <si>
+    <t>Epoch 90, loss: 0.802923</t>
+  </si>
+  <si>
+    <t>Epoch 91, loss: 0.793765</t>
+  </si>
+  <si>
+    <t>Epoch 92, loss: 0.796117</t>
+  </si>
+  <si>
+    <t>Epoch 93, loss: 0.786510</t>
+  </si>
+  <si>
+    <t>Epoch 94, loss: 0.781767</t>
+  </si>
+  <si>
+    <t>Epoch 95, loss: 0.766877</t>
+  </si>
+  <si>
+    <t>Epoch 96, loss: 0.764054</t>
+  </si>
+  <si>
+    <t>Epoch 97, loss: 0.755534</t>
+  </si>
+  <si>
+    <t>Epoch 98, loss: 0.745691</t>
+  </si>
+  <si>
+    <t>Epoch 99, loss: 0.747766</t>
+  </si>
+  <si>
+    <t>Epoch 100, loss: 0.744247</t>
+  </si>
+  <si>
+    <t>Epoch 101, loss: 0.733087</t>
+  </si>
+  <si>
+    <t>Epoch 102, loss: 0.722541</t>
+  </si>
+  <si>
+    <t>Epoch 103, loss: 0.718890</t>
+  </si>
+  <si>
+    <t>Epoch 104, loss: 0.717551</t>
+  </si>
+  <si>
+    <t>Epoch 105, loss: 0.706140</t>
+  </si>
+  <si>
+    <t>Epoch 106, loss: 0.700950</t>
+  </si>
+  <si>
+    <t>Epoch 107, loss: 0.703976</t>
+  </si>
+  <si>
+    <t>Epoch 108, loss: 0.701008</t>
+  </si>
+  <si>
+    <t>Epoch 109, loss: 0.693825</t>
+  </si>
+  <si>
+    <t>Epoch 110, loss: 0.682525</t>
+  </si>
+  <si>
+    <t>Epoch 111, loss: 0.679352</t>
+  </si>
+  <si>
+    <t>Epoch 112, loss: 0.672255</t>
+  </si>
+  <si>
+    <t>Epoch 113, loss: 0.675385</t>
+  </si>
+  <si>
+    <t>Epoch 114, loss: 0.674036</t>
+  </si>
+  <si>
+    <t>Epoch 115, loss: 0.666563</t>
+  </si>
+  <si>
+    <t>Epoch 116, loss: 0.658701</t>
+  </si>
+  <si>
+    <t>Epoch 117, loss: 0.651802</t>
+  </si>
+  <si>
+    <t>Epoch 118, loss: 0.648337</t>
+  </si>
+  <si>
+    <t>Epoch 119, loss: 0.653472</t>
+  </si>
+  <si>
+    <t>Epoch 120, loss: 0.647181</t>
+  </si>
+  <si>
+    <t>f 8, ks 9, [nC, C], 1e-3, 628km</t>
+  </si>
+  <si>
+    <t>f 4, ks 5, [nC, C], 1e-3, 698km</t>
+  </si>
+  <si>
+    <t>f 2, ks 3, [nC, C], 1e-3, 837km</t>
+  </si>
+  <si>
+    <t>Epoch 1, loss: 10.178493</t>
+  </si>
+  <si>
+    <t>Epoch 2, loss: 9.379157</t>
+  </si>
+  <si>
+    <t>Epoch 3, loss: 8.954072</t>
+  </si>
+  <si>
+    <t>Epoch 4, loss: 8.608480</t>
+  </si>
+  <si>
+    <t>Epoch 5, loss: 8.310584</t>
+  </si>
+  <si>
+    <t>Epoch 6, loss: 8.032576</t>
+  </si>
+  <si>
+    <t>Epoch 7, loss: 7.822782</t>
+  </si>
+  <si>
+    <t>Epoch 8, loss: 7.611291</t>
+  </si>
+  <si>
+    <t>Epoch 9, loss: 7.389453</t>
+  </si>
+  <si>
+    <t>Epoch 10, loss: 7.222379</t>
+  </si>
+  <si>
+    <t>Epoch 11, loss: 7.057654</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +777,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -191,7 +821,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -205,6 +835,10 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="4" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -220,6 +854,4191 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$85</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="84"/>
+                <c:pt idx="0">
+                  <c:v>10.346705999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.3060379999999991</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.7207989999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.2497729999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.85968</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.5018710000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.1969289999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9381649999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7007250000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.4847320000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.3646289999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.1687810000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.5577300000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.469544</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.3833440000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.3525919999999996</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.2695040000000004</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.5577300000000003</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.469544</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5.3833440000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5.3525919999999996</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.5577300000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>5.469544</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>5.3833440000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5.5577300000000003</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.5577300000000003</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.5577300000000003</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.5577300000000003</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5.469544</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.3833440000000001</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5.3525919999999996</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5.2695040000000004</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5.1996339999999996</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.1233880000000003</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5.0633879999999998</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5.0171029999999996</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>4.9706780000000004</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>4.9154640000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-45BC-4970-B77B-D708E170F943}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1245596255"/>
+        <c:axId val="1245596671"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1245596255"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1245596671"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1245596671"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1245596255"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>10.346705999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.3060379999999991</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.7207989999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.2497729999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.85968</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.5018710000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.1969289999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9381649999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7007250000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.4847320000000002</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.3646289999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.1687810000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.0067729999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.8894739999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.7596759999999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.664981</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5677-4722-A790-F513EA4D9845}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$E$2:$E$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>10.534499</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5386319999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.9107800000000008</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.4093689999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.9865000000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.6154909999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.2863490000000004</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.0051769999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7520850000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.5470579999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.3636819999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.2238730000000002</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.0692190000000004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.9175259999999996</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.8086260000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.6935560000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5677-4722-A790-F513EA4D9845}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1346705279"/>
+        <c:axId val="1346704031"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1346705279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1346704031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1346704031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1346705279"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$G$3:$G$122</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="120"/>
+                <c:pt idx="0">
+                  <c:v>11.477461999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.243162</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.4202670000000008</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.6973819999999993</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.0884219999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.5086510000000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.0412369999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.5982589999999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.1949459999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.8677599999999996</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.4542529999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.2220909999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.901389</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.6635010000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4.540565</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4.3348769999999996</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4.1410299999999998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.9825620000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.8649689999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.7848980000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.6353810000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.53911</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.3772129999999998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.352773</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3.2230300000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.0613860000000002</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.974332</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.9002370000000002</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.798476</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.7295699999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.6275230000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.5358360000000002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.4733010000000002</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.3862000000000001</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.3171279999999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.2594259999999999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.191773</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2.123129</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.0486930000000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.0025729999999999</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.9404729999999999</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.8860760000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.835834</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.7772520000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.7253339999999999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.6814629999999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.6397219999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.5963320000000001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.5549010000000001</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.5186409999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.4757910000000001</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1.4367890000000001</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1.4007689999999999</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1.368222</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.3414010000000001</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.310616</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.280481</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1.2560439999999999</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1.2289859999999999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.2167889999999999</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.184456</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.158072</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.136714</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1.1147370000000001</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1.1010690000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1.081159</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1.0610440000000001</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1.0588280000000001</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1.034818</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1.0124949999999999</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.99731400000000003</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.98586799999999997</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.97178399999999998</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.95851600000000003</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.94566899999999998</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.93540299999999998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.92749700000000002</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.91817099999999996</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.90716300000000005</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.89168899999999995</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.88042100000000001</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.87169300000000005</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.86656699999999998</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.85850700000000002</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.84372899999999995</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.83417200000000002</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.84358699999999998</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.82772000000000001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.81028</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.80292300000000005</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.79376500000000005</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.79611699999999996</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.78651000000000004</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.78176699999999999</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.76687700000000003</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.76405400000000001</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.75553400000000004</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.74569099999999999</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.74776600000000004</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.74424699999999999</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.73308700000000004</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.72254099999999999</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.71889000000000003</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.71755100000000005</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.70613999999999999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.70094999999999996</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.70397600000000005</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.70100799999999996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.69382500000000003</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.68252500000000005</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.67935199999999996</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.67225500000000005</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.67538500000000001</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.67403599999999997</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.66656300000000002</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.65870099999999998</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.65180199999999999</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.64833700000000005</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.65347200000000005</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.64718100000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9497-4055-9AE2-A6AE22D50091}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1313945135"/>
+        <c:axId val="1313941391"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1313945135"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1313941391"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1313941391"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1313945135"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$J$3:$J$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>10.178493</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.3791569999999993</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.954072</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.6084800000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.3105840000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.0325760000000006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.8227820000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.6112909999999996</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.3894529999999996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.2223790000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.0576540000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2D5B-404A-995F-ECE236559137}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1404416767"/>
+        <c:axId val="1404414271"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1404416767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1404414271"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1404414271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1404416767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>552449</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>127908</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114298</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF1DF43C-C86B-44EF-9EBD-691CF0DDD1A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>476251</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>138792</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>476251</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>106135</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9542F85-3DDB-4E8C-AD9C-4A8DC874BB52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>345621</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>176894</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>345621</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>144237</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06A78BF8-B4AC-4EF3-AA40-3E68BAA4FBF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>40821</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>68036</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>40821</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>35379</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A4E9968-0D0A-4807-878D-7D7E39C90A08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -768,35 +5587,35 @@
         <v>4</v>
       </c>
       <c r="B11" s="1">
-        <f>B3/B8</f>
+        <f t="shared" ref="B11:I11" si="0">B3/B8</f>
         <v>45</v>
       </c>
       <c r="C11" s="1">
-        <f>C3/C8</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="D11" s="1">
-        <f>D3/D8</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="E11" s="1">
-        <f>E3/E8</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="F11" s="1">
-        <f>F3/F8</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="G11" s="1">
-        <f>G3/G8</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="H11" s="1">
-        <f>H3/H8</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="I11" s="4">
-        <f>I3/I8</f>
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
     </row>
@@ -805,35 +5624,35 @@
         <v>5</v>
       </c>
       <c r="B12" s="1">
-        <f>B4/B8</f>
+        <f t="shared" ref="B12:I12" si="1">B4/B8</f>
         <v>90</v>
       </c>
       <c r="C12" s="1">
-        <f>C4/C8</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="D12" s="1">
-        <f>D4/D8</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="E12" s="1">
-        <f>E4/E8</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="F12" s="1">
-        <f>F4/F8</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="G12" s="1">
-        <f>G4/G8</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="H12" s="1">
-        <f>H4/H8</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="I12" s="4">
-        <f>I4/I8</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
     </row>
@@ -842,35 +5661,35 @@
         <v>10</v>
       </c>
       <c r="B13" s="6">
-        <f>B8*B8*B7</f>
+        <f t="shared" ref="B13:I13" si="2">B8*B8*B7</f>
         <v>1024</v>
       </c>
       <c r="C13" s="6">
-        <f>C8*C8*C7</f>
+        <f t="shared" si="2"/>
         <v>1024</v>
       </c>
       <c r="D13" s="6">
-        <f>D8*D8*D7</f>
+        <f t="shared" si="2"/>
         <v>1024</v>
       </c>
       <c r="E13" s="6">
-        <f>E8*E8*E7</f>
+        <f t="shared" si="2"/>
         <v>1024</v>
       </c>
       <c r="F13" s="6">
-        <f>F8*F8*F7</f>
+        <f t="shared" si="2"/>
         <v>1024</v>
       </c>
       <c r="G13" s="6">
-        <f>G8*G8*G7</f>
+        <f t="shared" si="2"/>
         <v>1024</v>
       </c>
       <c r="H13" s="1">
-        <f>H8*H8*H7</f>
+        <f t="shared" si="2"/>
         <v>1600</v>
       </c>
       <c r="I13" s="4">
-        <f>I8*I8*I7</f>
+        <f t="shared" si="2"/>
         <v>1024</v>
       </c>
     </row>
@@ -879,35 +5698,35 @@
         <v>14</v>
       </c>
       <c r="B14" s="5">
-        <f>B13/B9</f>
+        <f t="shared" ref="B14:I14" si="3">B13/B9</f>
         <v>2</v>
       </c>
       <c r="C14" s="5">
-        <f>C13/C9</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="D14" s="10">
-        <f>D13/D9</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="E14" s="5">
-        <f>E13/E9</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="F14" s="5">
-        <f>F13/F9</f>
+        <f t="shared" si="3"/>
         <v>64</v>
       </c>
       <c r="G14" s="5">
-        <f>G13/G9</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H14" s="5">
-        <f>H13/H9</f>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="I14" s="5">
-        <f>I13/I9</f>
+        <f t="shared" si="3"/>
         <v>256</v>
       </c>
     </row>
@@ -916,35 +5735,35 @@
         <v>6</v>
       </c>
       <c r="B15" s="1">
-        <f>B11*B12</f>
+        <f t="shared" ref="B15:I15" si="4">B11*B12</f>
         <v>4050</v>
       </c>
       <c r="C15" s="1">
-        <f>C11*C12</f>
+        <f t="shared" si="4"/>
         <v>4050</v>
       </c>
       <c r="D15" s="1">
-        <f>D11*D12</f>
+        <f t="shared" si="4"/>
         <v>4050</v>
       </c>
       <c r="E15" s="1">
-        <f>E11*E12</f>
+        <f t="shared" si="4"/>
         <v>4050</v>
       </c>
       <c r="F15" s="1">
-        <f>F11*F12</f>
+        <f t="shared" si="4"/>
         <v>4050</v>
       </c>
       <c r="G15" s="1">
-        <f>G11*G12</f>
+        <f t="shared" si="4"/>
         <v>4050</v>
       </c>
       <c r="H15" s="1">
-        <f>H11*H12</f>
+        <f t="shared" si="4"/>
         <v>2592</v>
       </c>
       <c r="I15" s="4">
-        <f>I11*I12</f>
+        <f t="shared" si="4"/>
         <v>4050</v>
       </c>
     </row>
@@ -957,35 +5776,35 @@
         <v>12</v>
       </c>
       <c r="B17" s="5">
-        <f>B11*B12*B5</f>
+        <f t="shared" ref="B17:I17" si="5">B11*B12*B5</f>
         <v>8100</v>
       </c>
       <c r="C17" s="5">
-        <f>C11*C12*C5</f>
+        <f t="shared" si="5"/>
         <v>12150</v>
       </c>
       <c r="D17" s="5">
-        <f>D11*D12*D5</f>
+        <f t="shared" si="5"/>
         <v>12150</v>
       </c>
       <c r="E17" s="5">
-        <f>E11*E12*E5</f>
+        <f t="shared" si="5"/>
         <v>24300</v>
       </c>
       <c r="F17" s="5">
-        <f>F11*F12*F5</f>
+        <f t="shared" si="5"/>
         <v>48600</v>
       </c>
       <c r="G17" s="5">
-        <f>G11*G12*G5</f>
+        <f t="shared" si="5"/>
         <v>16200</v>
       </c>
       <c r="H17" s="5">
-        <f>H11*H12*H5</f>
+        <f t="shared" si="5"/>
         <v>20736</v>
       </c>
       <c r="I17" s="5">
-        <f>I11*I12*I5</f>
+        <f t="shared" si="5"/>
         <v>97200</v>
       </c>
     </row>
@@ -994,35 +5813,35 @@
         <v>13</v>
       </c>
       <c r="B18" s="1">
-        <f>B17*B17*B9</f>
+        <f t="shared" ref="B18:I18" si="6">B17*B17*B9</f>
         <v>33592320000</v>
       </c>
       <c r="C18" s="1">
-        <f>C17*C17*C9</f>
+        <f t="shared" si="6"/>
         <v>37791360000</v>
       </c>
       <c r="D18" s="1">
-        <f>D17*D17*D9</f>
+        <f t="shared" si="6"/>
         <v>75582720000</v>
       </c>
       <c r="E18" s="1">
-        <f>E17*E17*E9</f>
+        <f t="shared" si="6"/>
         <v>37791360000</v>
       </c>
       <c r="F18" s="1">
-        <f>F17*F17*F9</f>
+        <f t="shared" si="6"/>
         <v>37791360000</v>
       </c>
       <c r="G18" s="1">
-        <f>G17*G17*G9</f>
+        <f t="shared" si="6"/>
         <v>33592320000</v>
       </c>
       <c r="H18" s="1">
-        <f>H17*H17*H9</f>
+        <f t="shared" si="6"/>
         <v>27518828544</v>
       </c>
       <c r="I18" s="4">
-        <f>I17*I17*I9</f>
+        <f t="shared" si="6"/>
         <v>37791360000</v>
       </c>
     </row>
@@ -1031,35 +5850,35 @@
         <v>16</v>
       </c>
       <c r="B20" s="1">
-        <f>B11*B12</f>
+        <f t="shared" ref="B20:I20" si="7">B11*B12</f>
         <v>4050</v>
       </c>
       <c r="C20" s="1">
-        <f>C11*C12</f>
+        <f t="shared" si="7"/>
         <v>4050</v>
       </c>
       <c r="D20" s="1">
-        <f>D11*D12</f>
+        <f t="shared" si="7"/>
         <v>4050</v>
       </c>
       <c r="E20" s="1">
-        <f>E11*E12</f>
+        <f t="shared" si="7"/>
         <v>4050</v>
       </c>
       <c r="F20" s="1">
-        <f>F11*F12</f>
+        <f t="shared" si="7"/>
         <v>4050</v>
       </c>
       <c r="G20" s="1">
-        <f>G11*G12</f>
+        <f t="shared" si="7"/>
         <v>4050</v>
       </c>
       <c r="H20" s="1">
-        <f>H11*H12</f>
+        <f t="shared" si="7"/>
         <v>2592</v>
       </c>
       <c r="I20" s="1">
-        <f>I11*I12</f>
+        <f t="shared" si="7"/>
         <v>4050</v>
       </c>
     </row>
@@ -1068,35 +5887,35 @@
         <v>17</v>
       </c>
       <c r="B21" s="1">
-        <f>B20*B20*B9*B5</f>
+        <f t="shared" ref="B21:I21" si="8">B20*B20*B9*B5</f>
         <v>16796160000</v>
       </c>
       <c r="C21" s="1">
-        <f>C20*C20*C9*C5</f>
+        <f t="shared" si="8"/>
         <v>12597120000</v>
       </c>
       <c r="D21" s="1">
-        <f>D20*D20*D9*D5</f>
+        <f t="shared" si="8"/>
         <v>25194240000</v>
       </c>
       <c r="E21" s="1">
-        <f>E20*E20*E9*E5</f>
+        <f t="shared" si="8"/>
         <v>6298560000</v>
       </c>
       <c r="F21" s="1">
-        <f>F20*F20*F9*F5</f>
+        <f t="shared" si="8"/>
         <v>3149280000</v>
       </c>
       <c r="G21" s="1">
-        <f>G20*G20*G9*G5</f>
+        <f t="shared" si="8"/>
         <v>8398080000</v>
       </c>
       <c r="H21" s="1">
-        <f>H20*H20*H9*H5</f>
+        <f t="shared" si="8"/>
         <v>3439853568</v>
       </c>
       <c r="I21" s="8">
-        <f>I20*I20*I9*I5</f>
+        <f t="shared" si="8"/>
         <v>1574640000</v>
       </c>
     </row>
@@ -1105,31 +5924,31 @@
         <v>18</v>
       </c>
       <c r="B23" s="1">
-        <f>B5*B11</f>
+        <f t="shared" ref="B23:H23" si="9">B5*B11</f>
         <v>90</v>
       </c>
       <c r="C23" s="1">
-        <f>C5*C11</f>
+        <f t="shared" si="9"/>
         <v>135</v>
       </c>
       <c r="D23" s="1">
-        <f>D5*D11</f>
+        <f t="shared" si="9"/>
         <v>135</v>
       </c>
       <c r="E23" s="1">
-        <f>E5*E11</f>
+        <f t="shared" si="9"/>
         <v>270</v>
       </c>
       <c r="F23" s="1">
-        <f>F5*F11</f>
+        <f t="shared" si="9"/>
         <v>540</v>
       </c>
       <c r="G23" s="1">
-        <f>G5*G11</f>
+        <f t="shared" si="9"/>
         <v>180</v>
       </c>
       <c r="H23" s="1">
-        <f>H5*H11</f>
+        <f t="shared" si="9"/>
         <v>288</v>
       </c>
     </row>
@@ -1138,31 +5957,31 @@
         <v>19</v>
       </c>
       <c r="B24" s="1">
-        <f>B23*B23*B9*B12</f>
+        <f t="shared" ref="B24:H24" si="10">B23*B23*B9*B12</f>
         <v>373248000</v>
       </c>
       <c r="C24" s="1">
-        <f>C23*C23*C9*C12</f>
+        <f t="shared" si="10"/>
         <v>419904000</v>
       </c>
       <c r="D24" s="1">
-        <f>D23*D23*D9*D12</f>
+        <f t="shared" si="10"/>
         <v>839808000</v>
       </c>
       <c r="E24" s="1">
-        <f>E23*E23*E9*E12</f>
+        <f t="shared" si="10"/>
         <v>419904000</v>
       </c>
       <c r="F24" s="1">
-        <f>F23*F23*F9*F12</f>
+        <f t="shared" si="10"/>
         <v>419904000</v>
       </c>
       <c r="G24" s="1">
-        <f>G23*G23*G9*G12</f>
+        <f t="shared" si="10"/>
         <v>373248000</v>
       </c>
       <c r="H24" s="1">
-        <f>H23*H23*H9*H12</f>
+        <f t="shared" si="10"/>
         <v>382205952</v>
       </c>
     </row>
@@ -1171,31 +5990,31 @@
         <v>20</v>
       </c>
       <c r="B26" s="1">
-        <f>B5*B12</f>
+        <f t="shared" ref="B26:H26" si="11">B5*B12</f>
         <v>180</v>
       </c>
       <c r="C26" s="1">
-        <f>C5*C12</f>
+        <f t="shared" si="11"/>
         <v>270</v>
       </c>
       <c r="D26" s="1">
-        <f>D5*D12</f>
+        <f t="shared" si="11"/>
         <v>270</v>
       </c>
       <c r="E26" s="1">
-        <f>E5*E12</f>
+        <f t="shared" si="11"/>
         <v>540</v>
       </c>
       <c r="F26" s="1">
-        <f>F5*F12</f>
+        <f t="shared" si="11"/>
         <v>1080</v>
       </c>
       <c r="G26" s="1">
-        <f>G5*G12</f>
+        <f t="shared" si="11"/>
         <v>360</v>
       </c>
       <c r="H26" s="1">
-        <f>H5*H12</f>
+        <f t="shared" si="11"/>
         <v>576</v>
       </c>
     </row>
@@ -1204,31 +6023,31 @@
         <v>21</v>
       </c>
       <c r="B27" s="1">
-        <f>B26*B26*B9*B11</f>
+        <f t="shared" ref="B27:H27" si="12">B26*B26*B9*B11</f>
         <v>746496000</v>
       </c>
       <c r="C27" s="1">
-        <f>C26*C26*C9*C11</f>
+        <f t="shared" si="12"/>
         <v>839808000</v>
       </c>
       <c r="D27" s="8">
-        <f>D26*D26*D9*D11</f>
+        <f t="shared" si="12"/>
         <v>1679616000</v>
       </c>
       <c r="E27" s="1">
-        <f>E26*E26*E9*E11</f>
+        <f t="shared" si="12"/>
         <v>839808000</v>
       </c>
       <c r="F27" s="1">
-        <f>F26*F26*F9*F11</f>
+        <f t="shared" si="12"/>
         <v>839808000</v>
       </c>
       <c r="G27" s="1">
-        <f>G26*G26*G9*G11</f>
+        <f t="shared" si="12"/>
         <v>746496000</v>
       </c>
       <c r="H27" s="1">
-        <f>H26*H26*H9*H11</f>
+        <f t="shared" si="12"/>
         <v>764411904</v>
       </c>
     </row>
@@ -1236,4 +6055,2312 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5DD36A-BC03-40BA-80D8-4DB8E9CC41CB}">
+  <dimension ref="A1:H85"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="22.921875" customWidth="1"/>
+    <col min="2" max="2" width="11.69140625" customWidth="1"/>
+    <col min="3" max="3" width="4.3046875" customWidth="1"/>
+    <col min="4" max="4" width="25.84375" customWidth="1"/>
+    <col min="5" max="5" width="11.3828125" customWidth="1"/>
+    <col min="6" max="6" width="5.3046875" customWidth="1"/>
+    <col min="7" max="7" width="24.61328125" customWidth="1"/>
+    <col min="8" max="8" width="13.07421875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="11" customFormat="1" ht="37.299999999999997" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2">
+        <f>VALUE(TRIM(RIGHT(A2,LEN(A2)-FIND("@",SUBSTITUTE(A2," ","@",LEN(A2)-LEN(SUBSTITUTE(A2," ","")))))))</f>
+        <v>10.346705999999999</v>
+      </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E2">
+        <f>VALUE(TRIM(RIGHT(D2,LEN(D2)-FIND("@",SUBSTITUTE(D2," ","@",LEN(D2)-LEN(SUBSTITUTE(D2," ","")))))))</f>
+        <v>10.534499</v>
+      </c>
+      <c r="G2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <f>VALUE(TRIM(RIGHT(G2,LEN(G2)-FIND("@",SUBSTITUTE(G2," ","@",LEN(G2)-LEN(SUBSTITUTE(G2," ","")))))))</f>
+        <v>11.471894000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B66" si="0">VALUE(TRIM(RIGHT(A3,LEN(A3)-FIND("@",SUBSTITUTE(A3," ","@",LEN(A3)-LEN(SUBSTITUTE(A3," ","")))))))</f>
+        <v>9.3060379999999991</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3" si="1">VALUE(TRIM(RIGHT(D3,LEN(D3)-FIND("@",SUBSTITUTE(D3," ","@",LEN(D3)-LEN(SUBSTITUTE(D3," ","")))))))</f>
+        <v>9.5386319999999998</v>
+      </c>
+      <c r="G3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H4" si="2">VALUE(TRIM(RIGHT(G3,LEN(G3)-FIND("@",SUBSTITUTE(G3," ","@",LEN(G3)-LEN(SUBSTITUTE(G3," ","")))))))</f>
+        <v>11.396761</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>8.7207989999999995</v>
+      </c>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E17" si="3">VALUE(TRIM(RIGHT(D4,LEN(D4)-FIND("@",SUBSTITUTE(D4," ","@",LEN(D4)-LEN(SUBSTITUTE(D4," ","")))))))</f>
+        <v>8.9107800000000008</v>
+      </c>
+      <c r="G4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="2"/>
+        <v>11.330163000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>8.2497729999999994</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="3"/>
+        <v>8.4093689999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>7.85968</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="3"/>
+        <v>7.9865000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>7.5018710000000004</v>
+      </c>
+      <c r="D7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="3"/>
+        <v>7.6154909999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>7.1969289999999999</v>
+      </c>
+      <c r="D8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="3"/>
+        <v>7.2863490000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>6.9381649999999997</v>
+      </c>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="3"/>
+        <v>7.0051769999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>6.7007250000000003</v>
+      </c>
+      <c r="D10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="3"/>
+        <v>6.7520850000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>6.4847320000000002</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="3"/>
+        <v>6.5470579999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>6.3646289999999999</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="3"/>
+        <v>6.3636819999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>6.1687810000000001</v>
+      </c>
+      <c r="D13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="3"/>
+        <v>6.2238730000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>6.0692190000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+      <c r="D15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="3"/>
+        <v>5.9175259999999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="3"/>
+        <v>5.8086260000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>5.664981</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="3"/>
+        <v>5.6935560000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>5.5577300000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>5.469544</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>5.3833440000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>5.3525919999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>5.2695040000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>5.664981</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>5.5577300000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>5.469544</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>5.3833440000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>5.3525919999999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="0"/>
+        <v>5.664981</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="0"/>
+        <v>5.5577300000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="0"/>
+        <v>5.469544</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="0"/>
+        <v>5.3833440000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="0"/>
+        <v>5.664981</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="0"/>
+        <v>5.5577300000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="0"/>
+        <v>5.664981</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="0"/>
+        <v>5.664981</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="0"/>
+        <v>5.5577300000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="0"/>
+        <v>5.664981</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="0"/>
+        <v>5.664981</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63">
+        <f t="shared" si="0"/>
+        <v>5.5577300000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="0"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="0"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="0"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67">
+        <f t="shared" ref="B67:B85" si="4">VALUE(TRIM(RIGHT(A67,LEN(A67)-FIND("@",SUBSTITUTE(A67," ","@",LEN(A67)-LEN(SUBSTITUTE(A67," ","")))))))</f>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68">
+        <f t="shared" si="4"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69">
+        <f t="shared" si="4"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="4"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71">
+        <f t="shared" si="4"/>
+        <v>6.0067729999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>42</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="4"/>
+        <v>5.8894739999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73">
+        <f t="shared" si="4"/>
+        <v>5.7596759999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>44</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="4"/>
+        <v>5.664981</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>45</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="4"/>
+        <v>5.5577300000000003</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>46</v>
+      </c>
+      <c r="B76">
+        <f t="shared" si="4"/>
+        <v>5.469544</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>47</v>
+      </c>
+      <c r="B77">
+        <f t="shared" si="4"/>
+        <v>5.3833440000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="4"/>
+        <v>5.3525919999999996</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>49</v>
+      </c>
+      <c r="B79">
+        <f t="shared" si="4"/>
+        <v>5.2695040000000004</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>50</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="4"/>
+        <v>5.1996339999999996</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>51</v>
+      </c>
+      <c r="B81">
+        <f t="shared" si="4"/>
+        <v>5.1233880000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>52</v>
+      </c>
+      <c r="B82">
+        <f t="shared" si="4"/>
+        <v>5.0633879999999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>53</v>
+      </c>
+      <c r="B83">
+        <f t="shared" si="4"/>
+        <v>5.0171029999999996</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>54</v>
+      </c>
+      <c r="B84">
+        <f t="shared" si="4"/>
+        <v>4.9706780000000004</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>55</v>
+      </c>
+      <c r="B85">
+        <f t="shared" si="4"/>
+        <v>4.9154640000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9581D8F-9826-46D6-82E3-6D1ECCAE1321}">
+  <dimension ref="B1:J122"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="24.921875" customWidth="1"/>
+    <col min="4" max="4" width="9.23046875" style="12"/>
+    <col min="6" max="6" width="26.69140625" customWidth="1"/>
+    <col min="9" max="9" width="22.15234375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3">
+        <f>VALUE(TRIM(RIGHT(B3,LEN(B3)-FIND("@",SUBSTITUTE(B3," ","@",LEN(B3)-LEN(SUBSTITUTE(B3," ","")))))))</f>
+        <v>12.281869</v>
+      </c>
+      <c r="D3" s="12">
+        <v>12.281869</v>
+      </c>
+      <c r="F3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3">
+        <f>VALUE(TRIM(RIGHT(F3,LEN(F3)-FIND("@",SUBSTITUTE(F3," ","@",LEN(F3)-LEN(SUBSTITUTE(F3," ","")))))))</f>
+        <v>11.477461999999999</v>
+      </c>
+      <c r="I3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J3">
+        <f>VALUE(TRIM(RIGHT(I3,LEN(I3)-FIND("@",SUBSTITUTE(I3," ","@",LEN(I3)-LEN(SUBSTITUTE(I3," ","")))))))</f>
+        <v>10.178493</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4">
+        <f t="shared" ref="C4:C22" si="0">VALUE(TRIM(RIGHT(B4,LEN(B4)-FIND("@",SUBSTITUTE(B4," ","@",LEN(B4)-LEN(SUBSTITUTE(B4," ","")))))))</f>
+        <v>10.475529999999999</v>
+      </c>
+      <c r="D4" s="12">
+        <v>10.475529999999999</v>
+      </c>
+      <c r="F4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G67" si="1">VALUE(TRIM(RIGHT(F4,LEN(F4)-FIND("@",SUBSTITUTE(F4," ","@",LEN(F4)-LEN(SUBSTITUTE(F4," ","")))))))</f>
+        <v>10.243162</v>
+      </c>
+      <c r="I4" t="s">
+        <v>222</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J13" si="2">VALUE(TRIM(RIGHT(I4,LEN(I4)-FIND("@",SUBSTITUTE(I4," ","@",LEN(I4)-LEN(SUBSTITUTE(I4," ","")))))))</f>
+        <v>9.3791569999999993</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>9.0221040000000006</v>
+      </c>
+      <c r="D5" s="12">
+        <v>9.0221040000000006</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>9.4202670000000008</v>
+      </c>
+      <c r="I5" t="s">
+        <v>223</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="2"/>
+        <v>8.954072</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>7.710941</v>
+      </c>
+      <c r="D6" s="12">
+        <v>7.710941</v>
+      </c>
+      <c r="F6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>8.6973819999999993</v>
+      </c>
+      <c r="I6" t="s">
+        <v>224</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="2"/>
+        <v>8.6084800000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>6.6865579999999998</v>
+      </c>
+      <c r="D7" s="12">
+        <v>6.6865579999999998</v>
+      </c>
+      <c r="F7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>8.0884219999999996</v>
+      </c>
+      <c r="I7" t="s">
+        <v>225</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="2"/>
+        <v>8.3105840000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>5.719036</v>
+      </c>
+      <c r="D8" s="12">
+        <v>5.719036</v>
+      </c>
+      <c r="F8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>7.5086510000000004</v>
+      </c>
+      <c r="I8" t="s">
+        <v>226</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="2"/>
+        <v>8.0325760000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>4.8801639999999997</v>
+      </c>
+      <c r="D9" s="12">
+        <v>4.8801639999999997</v>
+      </c>
+      <c r="F9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>7.0412369999999997</v>
+      </c>
+      <c r="I9" t="s">
+        <v>227</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="2"/>
+        <v>7.8227820000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>4.1630609999999999</v>
+      </c>
+      <c r="D10" s="12">
+        <v>4.1630609999999999</v>
+      </c>
+      <c r="F10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>6.5982589999999997</v>
+      </c>
+      <c r="I10" t="s">
+        <v>228</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="2"/>
+        <v>7.6112909999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>3.3946689999999999</v>
+      </c>
+      <c r="D11" s="12">
+        <v>3.3946689999999999</v>
+      </c>
+      <c r="F11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>6.1949459999999998</v>
+      </c>
+      <c r="I11" t="s">
+        <v>229</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="2"/>
+        <v>7.3894529999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>2.8382339999999999</v>
+      </c>
+      <c r="D12" s="12">
+        <v>2.8382339999999999</v>
+      </c>
+      <c r="F12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>5.8677599999999996</v>
+      </c>
+      <c r="I12" t="s">
+        <v>230</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="2"/>
+        <v>7.2223790000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>2.4257240000000002</v>
+      </c>
+      <c r="D13" s="12">
+        <v>2.4257240000000002</v>
+      </c>
+      <c r="F13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>5.4542529999999996</v>
+      </c>
+      <c r="I13" t="s">
+        <v>231</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="2"/>
+        <v>7.0576540000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>1.9966729999999999</v>
+      </c>
+      <c r="D14" s="12">
+        <v>1.9966729999999999</v>
+      </c>
+      <c r="F14" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>5.2220909999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>1.602676</v>
+      </c>
+      <c r="D15" s="12">
+        <v>1.602676</v>
+      </c>
+      <c r="F15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>4.901389</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>1.5300419999999999</v>
+      </c>
+      <c r="D16" s="12">
+        <v>1.5300419999999999</v>
+      </c>
+      <c r="F16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>4.6635010000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>1.2425569999999999</v>
+      </c>
+      <c r="D17" s="12">
+        <v>1.2425569999999999</v>
+      </c>
+      <c r="F17" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="1"/>
+        <v>4.540565</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>1.2608379999999999</v>
+      </c>
+      <c r="D18" s="12">
+        <v>1.2608379999999999</v>
+      </c>
+      <c r="F18" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="1"/>
+        <v>4.3348769999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>1.1618409999999999</v>
+      </c>
+      <c r="D19" s="12">
+        <v>1.1618409999999999</v>
+      </c>
+      <c r="F19" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="1"/>
+        <v>4.1410299999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>1.2010959999999999</v>
+      </c>
+      <c r="D20" s="12">
+        <v>1.2010959999999999</v>
+      </c>
+      <c r="F20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="1"/>
+        <v>3.9825620000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="0"/>
+        <v>1.3986829999999999</v>
+      </c>
+      <c r="D21" s="12">
+        <v>1.3986829999999999</v>
+      </c>
+      <c r="F21" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="1"/>
+        <v>3.8649689999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="0"/>
+        <v>1.2133959999999999</v>
+      </c>
+      <c r="D22" s="12">
+        <v>1.2133959999999999</v>
+      </c>
+      <c r="F22" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="1"/>
+        <v>3.7848980000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>3.6353810000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F24" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>3.53911</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F25" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="1"/>
+        <v>3.3772129999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="1"/>
+        <v>3.352773</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="1"/>
+        <v>3.2230300000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F28" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="1"/>
+        <v>3.0613860000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F29" t="s">
+        <v>124</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="1"/>
+        <v>2.974332</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F30" t="s">
+        <v>125</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="1"/>
+        <v>2.9002370000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="1"/>
+        <v>2.798476</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F32" t="s">
+        <v>127</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="1"/>
+        <v>2.7295699999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F33" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="1"/>
+        <v>2.6275230000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F34" t="s">
+        <v>129</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="1"/>
+        <v>2.5358360000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F35" t="s">
+        <v>130</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="1"/>
+        <v>2.4733010000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F36" t="s">
+        <v>131</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="1"/>
+        <v>2.3862000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F37" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="1"/>
+        <v>2.3171279999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F38" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="1"/>
+        <v>2.2594259999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F39" t="s">
+        <v>134</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="1"/>
+        <v>2.191773</v>
+      </c>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F40" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="1"/>
+        <v>2.123129</v>
+      </c>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F41" t="s">
+        <v>136</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="1"/>
+        <v>2.0486930000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F42" t="s">
+        <v>137</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="1"/>
+        <v>2.0025729999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F43" t="s">
+        <v>138</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="1"/>
+        <v>1.9404729999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F44" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="1"/>
+        <v>1.8860760000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F45" t="s">
+        <v>140</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="1"/>
+        <v>1.835834</v>
+      </c>
+    </row>
+    <row r="46" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F46" t="s">
+        <v>141</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="1"/>
+        <v>1.7772520000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="1"/>
+        <v>1.7253339999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F48" t="s">
+        <v>143</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="1"/>
+        <v>1.6814629999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F49" t="s">
+        <v>144</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="1"/>
+        <v>1.6397219999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="1"/>
+        <v>1.5963320000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F51" t="s">
+        <v>146</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="1"/>
+        <v>1.5549010000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F52" t="s">
+        <v>147</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="1"/>
+        <v>1.5186409999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F53" t="s">
+        <v>148</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="1"/>
+        <v>1.4757910000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F54" t="s">
+        <v>149</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="1"/>
+        <v>1.4367890000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F55" t="s">
+        <v>150</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="1"/>
+        <v>1.4007689999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F56" t="s">
+        <v>151</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="1"/>
+        <v>1.368222</v>
+      </c>
+    </row>
+    <row r="57" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F57" t="s">
+        <v>152</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="1"/>
+        <v>1.3414010000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F58" t="s">
+        <v>153</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="1"/>
+        <v>1.310616</v>
+      </c>
+    </row>
+    <row r="59" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F59" t="s">
+        <v>154</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="1"/>
+        <v>1.280481</v>
+      </c>
+    </row>
+    <row r="60" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F60" t="s">
+        <v>155</v>
+      </c>
+      <c r="G60">
+        <f t="shared" si="1"/>
+        <v>1.2560439999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F61" t="s">
+        <v>156</v>
+      </c>
+      <c r="G61">
+        <f t="shared" si="1"/>
+        <v>1.2289859999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F62" t="s">
+        <v>157</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="1"/>
+        <v>1.2167889999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F63" t="s">
+        <v>158</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="1"/>
+        <v>1.184456</v>
+      </c>
+    </row>
+    <row r="64" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F64" t="s">
+        <v>159</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="1"/>
+        <v>1.158072</v>
+      </c>
+    </row>
+    <row r="65" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F65" t="s">
+        <v>160</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="1"/>
+        <v>1.136714</v>
+      </c>
+    </row>
+    <row r="66" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F66" t="s">
+        <v>161</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="1"/>
+        <v>1.1147370000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F67" t="s">
+        <v>162</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="1"/>
+        <v>1.1010690000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F68" t="s">
+        <v>163</v>
+      </c>
+      <c r="G68">
+        <f t="shared" ref="G68:G122" si="3">VALUE(TRIM(RIGHT(F68,LEN(F68)-FIND("@",SUBSTITUTE(F68," ","@",LEN(F68)-LEN(SUBSTITUTE(F68," ","")))))))</f>
+        <v>1.081159</v>
+      </c>
+    </row>
+    <row r="69" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F69" t="s">
+        <v>164</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="3"/>
+        <v>1.0610440000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F70" t="s">
+        <v>165</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="3"/>
+        <v>1.0588280000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F71" t="s">
+        <v>166</v>
+      </c>
+      <c r="G71">
+        <f t="shared" si="3"/>
+        <v>1.034818</v>
+      </c>
+    </row>
+    <row r="72" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F72" t="s">
+        <v>167</v>
+      </c>
+      <c r="G72">
+        <f t="shared" si="3"/>
+        <v>1.0124949999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F73" t="s">
+        <v>168</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="3"/>
+        <v>0.99731400000000003</v>
+      </c>
+    </row>
+    <row r="74" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F74" t="s">
+        <v>169</v>
+      </c>
+      <c r="G74">
+        <f t="shared" si="3"/>
+        <v>0.98586799999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F75" t="s">
+        <v>170</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="3"/>
+        <v>0.97178399999999998</v>
+      </c>
+    </row>
+    <row r="76" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F76" t="s">
+        <v>171</v>
+      </c>
+      <c r="G76">
+        <f t="shared" si="3"/>
+        <v>0.95851600000000003</v>
+      </c>
+    </row>
+    <row r="77" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F77" t="s">
+        <v>172</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="3"/>
+        <v>0.94566899999999998</v>
+      </c>
+    </row>
+    <row r="78" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F78" t="s">
+        <v>173</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="3"/>
+        <v>0.93540299999999998</v>
+      </c>
+    </row>
+    <row r="79" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F79" t="s">
+        <v>174</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="3"/>
+        <v>0.92749700000000002</v>
+      </c>
+    </row>
+    <row r="80" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="3"/>
+        <v>0.91817099999999996</v>
+      </c>
+    </row>
+    <row r="81" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F81" t="s">
+        <v>176</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="3"/>
+        <v>0.90716300000000005</v>
+      </c>
+    </row>
+    <row r="82" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F82" t="s">
+        <v>177</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="3"/>
+        <v>0.89168899999999995</v>
+      </c>
+    </row>
+    <row r="83" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F83" t="s">
+        <v>178</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="3"/>
+        <v>0.88042100000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F84" t="s">
+        <v>179</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="3"/>
+        <v>0.87169300000000005</v>
+      </c>
+    </row>
+    <row r="85" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F85" t="s">
+        <v>180</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="3"/>
+        <v>0.86656699999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F86" t="s">
+        <v>181</v>
+      </c>
+      <c r="G86">
+        <f t="shared" si="3"/>
+        <v>0.85850700000000002</v>
+      </c>
+    </row>
+    <row r="87" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F87" t="s">
+        <v>182</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="3"/>
+        <v>0.84372899999999995</v>
+      </c>
+    </row>
+    <row r="88" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F88" t="s">
+        <v>183</v>
+      </c>
+      <c r="G88">
+        <f t="shared" si="3"/>
+        <v>0.83417200000000002</v>
+      </c>
+    </row>
+    <row r="89" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F89" t="s">
+        <v>184</v>
+      </c>
+      <c r="G89">
+        <f t="shared" si="3"/>
+        <v>0.84358699999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F90" t="s">
+        <v>185</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="3"/>
+        <v>0.82772000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F91" t="s">
+        <v>186</v>
+      </c>
+      <c r="G91">
+        <f t="shared" si="3"/>
+        <v>0.81028</v>
+      </c>
+    </row>
+    <row r="92" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F92" t="s">
+        <v>187</v>
+      </c>
+      <c r="G92">
+        <f t="shared" si="3"/>
+        <v>0.80292300000000005</v>
+      </c>
+    </row>
+    <row r="93" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F93" t="s">
+        <v>188</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="3"/>
+        <v>0.79376500000000005</v>
+      </c>
+    </row>
+    <row r="94" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F94" t="s">
+        <v>189</v>
+      </c>
+      <c r="G94">
+        <f t="shared" si="3"/>
+        <v>0.79611699999999996</v>
+      </c>
+    </row>
+    <row r="95" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F95" t="s">
+        <v>190</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="3"/>
+        <v>0.78651000000000004</v>
+      </c>
+    </row>
+    <row r="96" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F96" t="s">
+        <v>191</v>
+      </c>
+      <c r="G96">
+        <f t="shared" si="3"/>
+        <v>0.78176699999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F97" t="s">
+        <v>192</v>
+      </c>
+      <c r="G97">
+        <f t="shared" si="3"/>
+        <v>0.76687700000000003</v>
+      </c>
+    </row>
+    <row r="98" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F98" t="s">
+        <v>193</v>
+      </c>
+      <c r="G98">
+        <f t="shared" si="3"/>
+        <v>0.76405400000000001</v>
+      </c>
+    </row>
+    <row r="99" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F99" t="s">
+        <v>194</v>
+      </c>
+      <c r="G99">
+        <f t="shared" si="3"/>
+        <v>0.75553400000000004</v>
+      </c>
+    </row>
+    <row r="100" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F100" t="s">
+        <v>195</v>
+      </c>
+      <c r="G100">
+        <f t="shared" si="3"/>
+        <v>0.74569099999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F101" t="s">
+        <v>196</v>
+      </c>
+      <c r="G101">
+        <f t="shared" si="3"/>
+        <v>0.74776600000000004</v>
+      </c>
+    </row>
+    <row r="102" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F102" t="s">
+        <v>197</v>
+      </c>
+      <c r="G102">
+        <f t="shared" si="3"/>
+        <v>0.74424699999999999</v>
+      </c>
+    </row>
+    <row r="103" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F103" t="s">
+        <v>198</v>
+      </c>
+      <c r="G103">
+        <f t="shared" si="3"/>
+        <v>0.73308700000000004</v>
+      </c>
+    </row>
+    <row r="104" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F104" t="s">
+        <v>199</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="3"/>
+        <v>0.72254099999999999</v>
+      </c>
+    </row>
+    <row r="105" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F105" t="s">
+        <v>200</v>
+      </c>
+      <c r="G105">
+        <f t="shared" si="3"/>
+        <v>0.71889000000000003</v>
+      </c>
+    </row>
+    <row r="106" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F106" t="s">
+        <v>201</v>
+      </c>
+      <c r="G106">
+        <f t="shared" si="3"/>
+        <v>0.71755100000000005</v>
+      </c>
+    </row>
+    <row r="107" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F107" t="s">
+        <v>202</v>
+      </c>
+      <c r="G107">
+        <f t="shared" si="3"/>
+        <v>0.70613999999999999</v>
+      </c>
+    </row>
+    <row r="108" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F108" t="s">
+        <v>203</v>
+      </c>
+      <c r="G108">
+        <f t="shared" si="3"/>
+        <v>0.70094999999999996</v>
+      </c>
+    </row>
+    <row r="109" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F109" t="s">
+        <v>204</v>
+      </c>
+      <c r="G109">
+        <f t="shared" si="3"/>
+        <v>0.70397600000000005</v>
+      </c>
+    </row>
+    <row r="110" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F110" t="s">
+        <v>205</v>
+      </c>
+      <c r="G110">
+        <f t="shared" si="3"/>
+        <v>0.70100799999999996</v>
+      </c>
+    </row>
+    <row r="111" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F111" t="s">
+        <v>206</v>
+      </c>
+      <c r="G111">
+        <f t="shared" si="3"/>
+        <v>0.69382500000000003</v>
+      </c>
+    </row>
+    <row r="112" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F112" t="s">
+        <v>207</v>
+      </c>
+      <c r="G112">
+        <f t="shared" si="3"/>
+        <v>0.68252500000000005</v>
+      </c>
+    </row>
+    <row r="113" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F113" t="s">
+        <v>208</v>
+      </c>
+      <c r="G113">
+        <f t="shared" si="3"/>
+        <v>0.67935199999999996</v>
+      </c>
+    </row>
+    <row r="114" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F114" t="s">
+        <v>209</v>
+      </c>
+      <c r="G114">
+        <f t="shared" si="3"/>
+        <v>0.67225500000000005</v>
+      </c>
+    </row>
+    <row r="115" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F115" t="s">
+        <v>210</v>
+      </c>
+      <c r="G115">
+        <f t="shared" si="3"/>
+        <v>0.67538500000000001</v>
+      </c>
+    </row>
+    <row r="116" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F116" t="s">
+        <v>211</v>
+      </c>
+      <c r="G116">
+        <f t="shared" si="3"/>
+        <v>0.67403599999999997</v>
+      </c>
+    </row>
+    <row r="117" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F117" t="s">
+        <v>212</v>
+      </c>
+      <c r="G117">
+        <f t="shared" si="3"/>
+        <v>0.66656300000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F118" t="s">
+        <v>213</v>
+      </c>
+      <c r="G118">
+        <f t="shared" si="3"/>
+        <v>0.65870099999999998</v>
+      </c>
+    </row>
+    <row r="119" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F119" t="s">
+        <v>214</v>
+      </c>
+      <c r="G119">
+        <f t="shared" si="3"/>
+        <v>0.65180199999999999</v>
+      </c>
+    </row>
+    <row r="120" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F120" t="s">
+        <v>215</v>
+      </c>
+      <c r="G120">
+        <f t="shared" si="3"/>
+        <v>0.64833700000000005</v>
+      </c>
+    </row>
+    <row r="121" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F121" t="s">
+        <v>216</v>
+      </c>
+      <c r="G121">
+        <f t="shared" si="3"/>
+        <v>0.65347200000000005</v>
+      </c>
+    </row>
+    <row r="122" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F122" t="s">
+        <v>217</v>
+      </c>
+      <c r="G122">
+        <f t="shared" si="3"/>
+        <v>0.64718100000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/research/HyperParams.xlsx
+++ b/research/HyperParams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Subnet-18-Zeus\research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954EA932-9195-40DD-B1A5-4DE0FC35CBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AFBBDC-D4CB-43D4-9335-B694F95A1C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22149" windowHeight="11623" activeTab="3" xr2:uid="{701B61B4-A6E2-434A-B336-77C79E78CCA1}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="3" xr2:uid="{701B61B4-A6E2-434A-B336-77C79E78CCA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="371">
   <si>
     <t>H</t>
   </si>
@@ -1588,6 +1588,69 @@
       <t>GLU</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">heads </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>128</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+chunks 4
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>layers 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GLU</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1658,7 +1721,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1689,6 +1752,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1702,7 +1771,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1750,6 +1819,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4391,7 +4463,23 @@
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>  </a:t>
+              <a:t> (</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>big</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>) </a:t>
             </a:r>
           </a:p>
           <a:p>
@@ -4419,6 +4507,28 @@
                 </a:solidFill>
               </a:rPr>
               <a:t> &gt;&gt; GLU loss</a:t>
+            </a:r>
+            <a:br>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+            </a:br>
+            <a:br>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+            </a:br>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>MHA has much less effect than others</a:t>
             </a:r>
             <a:endParaRPr lang="en-US">
               <a:solidFill>
@@ -4476,7 +4586,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AO$3</c:f>
+              <c:f>Sheet4!$AQ$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4501,7 +4611,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AO$4:$AO$103</c:f>
+              <c:f>Sheet4!$AQ$4:$AQ$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -4820,7 +4930,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AP$3</c:f>
+              <c:f>Sheet4!$AR$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4845,7 +4955,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AP$4:$AP$103</c:f>
+              <c:f>Sheet4!$AR$4:$AR$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -5164,7 +5274,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AQ$3</c:f>
+              <c:f>Sheet4!$AS$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5189,7 +5299,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AQ$4:$AQ$103</c:f>
+              <c:f>Sheet4!$AS$4:$AS$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -5508,7 +5618,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AR$3</c:f>
+              <c:f>Sheet4!$AT$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5533,7 +5643,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AR$4:$AR$103</c:f>
+              <c:f>Sheet4!$AT$4:$AT$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -5852,7 +5962,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AS$3</c:f>
+              <c:f>Sheet4!$AU$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5878,7 +5988,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AS$4:$AS$103</c:f>
+              <c:f>Sheet4!$AU$4:$AU$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -6197,7 +6307,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AT$3</c:f>
+              <c:f>Sheet4!$AV$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6223,7 +6333,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AT$4:$AT$103</c:f>
+              <c:f>Sheet4!$AV$4:$AV$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -6542,7 +6652,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AU$3</c:f>
+              <c:f>Sheet4!$AW$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6570,7 +6680,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AU$4:$AU$103</c:f>
+              <c:f>Sheet4!$AW$4:$AW$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -6889,7 +6999,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AV$3</c:f>
+              <c:f>Sheet4!$AX$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6917,7 +7027,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AV$4:$AV$103</c:f>
+              <c:f>Sheet4!$AX$4:$AX$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -7527,7 +7637,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AX$3</c:f>
+              <c:f>Sheet4!$BA$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7552,7 +7662,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AX$4:$AX$103</c:f>
+              <c:f>Sheet4!$BA$4:$BA$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -7871,7 +7981,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AY$3</c:f>
+              <c:f>Sheet4!$BB$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7896,7 +8006,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AY$4:$AY$103</c:f>
+              <c:f>Sheet4!$BB$4:$BB$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -8215,7 +8325,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$AZ$3</c:f>
+              <c:f>Sheet4!$BC$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8240,7 +8350,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$AZ$4:$AZ$103</c:f>
+              <c:f>Sheet4!$BC$4:$BC$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -8559,7 +8669,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet4!$BA$3</c:f>
+              <c:f>Sheet4!$BD$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8585,7 +8695,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet4!$BA$4:$BA$103</c:f>
+              <c:f>Sheet4!$BD$4:$BD$103</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="100"/>
@@ -35269,16 +35379,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>239485</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>559652</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>13604</xdr:rowOff>
+      <xdr:rowOff>116057</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>48</xdr:col>
-      <xdr:colOff>375557</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>21771</xdr:rowOff>
+      <xdr:colOff>646739</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -35305,16 +35415,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>274865</xdr:colOff>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>133990</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>57149</xdr:rowOff>
+      <xdr:rowOff>31536</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>53</xdr:col>
-      <xdr:colOff>274865</xdr:colOff>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>133990</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>32656</xdr:rowOff>
+      <xdr:rowOff>7043</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -38668,7 +38778,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFFB2274-E5D0-4835-8B7D-9E309EDBB49C}">
-  <dimension ref="A1:BG503"/>
+  <dimension ref="A1:BJ503"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="9.53515625" customWidth="1"/>
@@ -38680,7 +38790,7 @@
     <col min="36" max="36" width="9.23046875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>0.29550799999999999</v>
       </c>
@@ -38756,54 +38866,55 @@
       <c r="AL1">
         <v>0.16072700000000001</v>
       </c>
-      <c r="AO1" s="23">
+      <c r="AQ1" s="23">
         <v>7.9161999999999996E-2</v>
       </c>
-      <c r="AP1" s="14">
+      <c r="AR1" s="14">
         <v>0.19963700000000001</v>
       </c>
-      <c r="AQ1" s="14">
+      <c r="AS1" s="14">
         <v>9.8531999999999995E-2</v>
       </c>
-      <c r="AR1">
+      <c r="AT1">
         <v>0.225634</v>
       </c>
-      <c r="AS1" s="14">
+      <c r="AU1" s="14">
         <v>8.7580000000000002E-3</v>
       </c>
-      <c r="AT1" s="23">
+      <c r="AV1" s="23">
         <v>3.8289999999999999E-3</v>
       </c>
-      <c r="AU1" s="14">
+      <c r="AW1" s="14">
         <v>5.5079999999999999E-3</v>
       </c>
-      <c r="AV1" s="23">
+      <c r="AX1" s="23">
         <v>3.457E-3</v>
       </c>
-      <c r="AX1">
+      <c r="AY1" s="23"/>
+      <c r="BA1">
         <v>9.1441050171999994E-2</v>
       </c>
-      <c r="AY1" s="14">
+      <c r="BB1" s="14">
         <v>7.0200269109999998E-3</v>
       </c>
-      <c r="AZ1">
+      <c r="BC1">
         <v>1.5699758659999999E-3</v>
       </c>
-      <c r="BA1">
+      <c r="BD1">
         <v>1.557961456E-3</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BF1" t="s">
         <v>368</v>
       </c>
-      <c r="BF1">
-        <f t="shared" ref="BF1" si="0">--TRIM(RIGHT(SUBSTITUTE(SUBSTITUTE(BC1,":"," "), " ", REPT(" ",99)),99))</f>
+      <c r="BI1">
+        <f t="shared" ref="BI1" si="0">--TRIM(RIGHT(SUBSTITUTE(SUBSTITUTE(BF1,":"," "), " ", REPT(" ",99)),99))</f>
         <v>1.557961456E-3</v>
       </c>
-      <c r="BG1">
+      <c r="BJ1">
         <v>1.557961456E-3</v>
       </c>
     </row>
-    <row r="2" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.4">
       <c r="R2" t="s">
         <v>256</v>
       </c>
@@ -38855,12 +38966,6 @@
       <c r="AL2" t="s">
         <v>256</v>
       </c>
-      <c r="AO2" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="AP2" s="14" t="s">
-        <v>263</v>
-      </c>
       <c r="AQ2" s="14" t="s">
         <v>263</v>
       </c>
@@ -38876,25 +38981,34 @@
       <c r="AU2" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="AV2" s="27" t="s">
+      <c r="AV2" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="AW2" s="24"/>
-      <c r="AX2" s="14" t="s">
+      <c r="AW2" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="AY2" s="14" t="s">
+      <c r="AX2" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="AZ2" s="26" t="s">
+      <c r="AY2" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="AZ2" s="24"/>
+      <c r="BA2" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="BB2" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="BC2" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="BA2" s="26" t="s">
+      <c r="BD2" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="BB2" s="26"/>
-    </row>
-    <row r="3" spans="1:59" ht="59.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="BE2" s="26"/>
+    </row>
+    <row r="3" spans="1:62" ht="59.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>232</v>
       </c>
@@ -38972,46 +39086,51 @@
       </c>
       <c r="AM3" s="13"/>
       <c r="AN3" s="13"/>
-      <c r="AO3" s="20" t="s">
+      <c r="AO3" s="13"/>
+      <c r="AP3" s="13"/>
+      <c r="AQ3" s="20" t="s">
         <v>257</v>
       </c>
-      <c r="AP3" s="20" t="s">
+      <c r="AR3" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="AQ3" s="22" t="s">
+      <c r="AS3" s="22" t="s">
         <v>264</v>
       </c>
-      <c r="AR3" s="22" t="s">
+      <c r="AT3" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="AS3" s="20" t="s">
+      <c r="AU3" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="AT3" s="20" t="s">
+      <c r="AV3" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="AU3" s="22" t="s">
+      <c r="AW3" s="22" t="s">
         <v>262</v>
       </c>
-      <c r="AV3" s="28" t="s">
+      <c r="AX3" s="28" t="s">
         <v>369</v>
       </c>
-      <c r="AW3" s="25"/>
-      <c r="AX3" s="13" t="s">
+      <c r="AY3" s="29" t="s">
+        <v>370</v>
+      </c>
+      <c r="AZ3" s="25"/>
+      <c r="BA3" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="AY3" s="22" t="s">
+      <c r="BB3" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="AZ3" s="13" t="s">
+      <c r="BC3" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="BA3" s="13" t="s">
+      <c r="BD3" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="BB3" s="13"/>
-    </row>
-    <row r="4" spans="1:59" x14ac:dyDescent="0.4">
+      <c r="BE3" s="13"/>
+    </row>
+    <row r="4" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1.0018359999999999</v>
       </c>
@@ -39087,54 +39206,54 @@
       <c r="AL4">
         <v>1.9984759999999999</v>
       </c>
-      <c r="AO4">
+      <c r="AQ4">
         <v>2.0014850000000002</v>
       </c>
-      <c r="AP4">
+      <c r="AR4">
         <v>1.9995160000000001</v>
       </c>
-      <c r="AQ4">
+      <c r="AS4">
         <v>2.0018660000000001</v>
       </c>
-      <c r="AR4">
+      <c r="AT4">
         <v>1.9994080000000001</v>
       </c>
-      <c r="AS4">
+      <c r="AU4">
         <v>2.0006780000000002</v>
       </c>
-      <c r="AT4">
+      <c r="AV4">
         <v>2.0007239999999999</v>
       </c>
-      <c r="AU4">
+      <c r="AW4">
         <v>1.998729</v>
       </c>
-      <c r="AV4">
+      <c r="AX4">
         <v>2.0016080000000001</v>
       </c>
-      <c r="AX4">
+      <c r="BA4">
         <v>2.002235412598</v>
       </c>
-      <c r="AY4">
+      <c r="BB4">
         <v>2.0012249946590002</v>
       </c>
-      <c r="AZ4">
+      <c r="BC4">
         <v>2.0052390098570001</v>
       </c>
-      <c r="BA4">
+      <c r="BD4">
         <v>2.0068550109859999</v>
       </c>
-      <c r="BC4" t="s">
+      <c r="BF4" t="s">
         <v>269</v>
       </c>
-      <c r="BF4">
-        <f>--TRIM(RIGHT(SUBSTITUTE(SUBSTITUTE(BC4,":"," "), " ", REPT(" ",99)),99))</f>
+      <c r="BI4">
+        <f>--TRIM(RIGHT(SUBSTITUTE(SUBSTITUTE(BF4,":"," "), " ", REPT(" ",99)),99))</f>
         <v>2.0068550109859999</v>
       </c>
-      <c r="BG4">
+      <c r="BJ4">
         <v>2.0068550109859999</v>
       </c>
     </row>
-    <row r="5" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>0.99840700000000004</v>
       </c>
@@ -39210,54 +39329,54 @@
       <c r="AL5">
         <v>1.9251579999999999</v>
       </c>
-      <c r="AO5">
+      <c r="AQ5">
         <v>1.941721</v>
       </c>
-      <c r="AP5">
+      <c r="AR5">
         <v>1.919864</v>
       </c>
-      <c r="AQ5">
+      <c r="AS5">
         <v>1.941918</v>
       </c>
-      <c r="AR5">
+      <c r="AT5">
         <v>1.9202520000000001</v>
       </c>
-      <c r="AS5">
+      <c r="AU5">
         <v>1.959387</v>
       </c>
-      <c r="AT5">
+      <c r="AV5">
         <v>1.919913</v>
       </c>
-      <c r="AU5">
+      <c r="AW5">
         <v>1.957506</v>
       </c>
-      <c r="AV5">
+      <c r="AX5">
         <v>1.9208460000000001</v>
       </c>
-      <c r="AX5">
+      <c r="BA5">
         <v>1.9422088861469999</v>
       </c>
-      <c r="AY5">
+      <c r="BB5">
         <v>1.95989716053</v>
       </c>
-      <c r="AZ5">
+      <c r="BC5">
         <v>1.7209881544109999</v>
       </c>
-      <c r="BA5">
+      <c r="BD5">
         <v>1.801147460938</v>
       </c>
-      <c r="BC5" t="s">
+      <c r="BF5" t="s">
         <v>270</v>
       </c>
-      <c r="BF5">
-        <f t="shared" ref="BF5:BF68" si="1">--TRIM(RIGHT(SUBSTITUTE(SUBSTITUTE(BC5,":"," "), " ", REPT(" ",99)),99))</f>
+      <c r="BI5">
+        <f t="shared" ref="BI5:BI68" si="1">--TRIM(RIGHT(SUBSTITUTE(SUBSTITUTE(BF5,":"," "), " ", REPT(" ",99)),99))</f>
         <v>1.801147460938</v>
       </c>
-      <c r="BG5">
+      <c r="BJ5">
         <v>1.801147460938</v>
       </c>
     </row>
-    <row r="6" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>0.99566699999999997</v>
       </c>
@@ -39333,54 +39452,54 @@
       <c r="AL6">
         <v>1.8617090000000001</v>
       </c>
-      <c r="AO6">
+      <c r="AQ6">
         <v>1.8966719999999999</v>
       </c>
-      <c r="AP6">
+      <c r="AR6">
         <v>1.85388</v>
       </c>
-      <c r="AQ6">
+      <c r="AS6">
         <v>1.896714</v>
       </c>
-      <c r="AR6">
+      <c r="AT6">
         <v>1.85432</v>
       </c>
-      <c r="AS6">
+      <c r="AU6">
         <v>1.916641</v>
       </c>
-      <c r="AT6">
+      <c r="AV6">
         <v>1.8355699999999999</v>
       </c>
-      <c r="AU6">
+      <c r="AW6">
         <v>1.9146780000000001</v>
       </c>
-      <c r="AV6">
+      <c r="AX6">
         <v>1.8362849999999999</v>
       </c>
-      <c r="AX6">
+      <c r="BA6">
         <v>1.8966548442840001</v>
       </c>
-      <c r="AY6">
+      <c r="BB6">
         <v>1.9169220924379999</v>
       </c>
-      <c r="AZ6">
+      <c r="BC6">
         <v>1.5226994752880001</v>
       </c>
-      <c r="BA6">
+      <c r="BD6">
         <v>1.5372483730319999</v>
       </c>
-      <c r="BC6" t="s">
+      <c r="BF6" t="s">
         <v>271</v>
       </c>
-      <c r="BF6">
+      <c r="BI6">
         <f t="shared" si="1"/>
         <v>1.5372483730319999</v>
       </c>
-      <c r="BG6">
+      <c r="BJ6">
         <v>1.5372483730319999</v>
       </c>
     </row>
-    <row r="7" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>0.99327900000000002</v>
       </c>
@@ -39456,54 +39575,54 @@
       <c r="AL7">
         <v>1.822157</v>
       </c>
-      <c r="AO7">
+      <c r="AQ7">
         <v>1.8536060000000001</v>
       </c>
-      <c r="AP7">
+      <c r="AR7">
         <v>1.7867249999999999</v>
       </c>
-      <c r="AQ7">
+      <c r="AS7">
         <v>1.853434</v>
       </c>
-      <c r="AR7">
+      <c r="AT7">
         <v>1.7873460000000001</v>
       </c>
-      <c r="AS7">
+      <c r="AU7">
         <v>1.8692150000000001</v>
       </c>
-      <c r="AT7">
+      <c r="AV7">
         <v>1.740821</v>
       </c>
-      <c r="AU7">
+      <c r="AW7">
         <v>1.866957</v>
       </c>
-      <c r="AV7">
+      <c r="AX7">
         <v>1.7405870000000001</v>
       </c>
-      <c r="AX7">
+      <c r="BA7">
         <v>1.8531253337860001</v>
       </c>
-      <c r="AY7">
+      <c r="BB7">
         <v>1.8689029216769999</v>
       </c>
-      <c r="AZ7">
+      <c r="BC7">
         <v>1.325358986855</v>
       </c>
-      <c r="BA7">
+      <c r="BD7">
         <v>1.164113044739</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BF7" t="s">
         <v>272</v>
       </c>
-      <c r="BF7">
+      <c r="BI7">
         <f t="shared" si="1"/>
         <v>1.164113044739</v>
       </c>
-      <c r="BG7">
+      <c r="BJ7">
         <v>1.164113044739</v>
       </c>
     </row>
-    <row r="8" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>0.99105900000000002</v>
       </c>
@@ -39579,54 +39698,54 @@
       <c r="AL8">
         <v>1.779982</v>
       </c>
-      <c r="AO8">
+      <c r="AQ8">
         <v>1.8027390000000001</v>
       </c>
-      <c r="AP8">
+      <c r="AR8">
         <v>1.726105</v>
       </c>
-      <c r="AQ8">
+      <c r="AS8">
         <v>1.8020670000000001</v>
       </c>
-      <c r="AR8">
+      <c r="AT8">
         <v>1.726029</v>
       </c>
-      <c r="AS8">
+      <c r="AU8">
         <v>1.8116719999999999</v>
       </c>
-      <c r="AT8">
+      <c r="AV8">
         <v>1.626854</v>
       </c>
-      <c r="AU8">
+      <c r="AW8">
         <v>1.809191</v>
       </c>
-      <c r="AV8">
+      <c r="AX8">
         <v>1.624064</v>
       </c>
-      <c r="AX8">
+      <c r="BA8">
         <v>1.8015244007110001</v>
       </c>
-      <c r="AY8">
+      <c r="BB8">
         <v>1.8102072477340001</v>
       </c>
-      <c r="AZ8">
+      <c r="BC8">
         <v>1.089227557182</v>
       </c>
-      <c r="BA8">
+      <c r="BD8">
         <v>0.72428125143099997</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="BF8" t="s">
         <v>273</v>
       </c>
-      <c r="BF8">
+      <c r="BI8">
         <f t="shared" si="1"/>
         <v>0.72428125143099997</v>
       </c>
-      <c r="BG8">
+      <c r="BJ8">
         <v>0.72428125143099997</v>
       </c>
     </row>
-    <row r="9" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>0.98889700000000003</v>
       </c>
@@ -39702,54 +39821,54 @@
       <c r="AL9">
         <v>1.7060420000000001</v>
       </c>
-      <c r="AO9">
+      <c r="AQ9">
         <v>1.744712</v>
       </c>
-      <c r="AP9">
+      <c r="AR9">
         <v>1.6618379999999999</v>
       </c>
-      <c r="AQ9">
+      <c r="AS9">
         <v>1.742931</v>
       </c>
-      <c r="AR9">
+      <c r="AT9">
         <v>1.6616949999999999</v>
       </c>
-      <c r="AS9">
+      <c r="AU9">
         <v>1.733606</v>
       </c>
-      <c r="AT9">
+      <c r="AV9">
         <v>1.4382520000000001</v>
       </c>
-      <c r="AU9">
+      <c r="AW9">
         <v>1.7317940000000001</v>
       </c>
-      <c r="AV9">
+      <c r="AX9">
         <v>1.430993</v>
       </c>
-      <c r="AX9">
+      <c r="BA9">
         <v>1.74226307869</v>
       </c>
-      <c r="AY9">
+      <c r="BB9">
         <v>1.7302705049510001</v>
       </c>
-      <c r="AZ9">
+      <c r="BC9">
         <v>0.84688341617600005</v>
       </c>
-      <c r="BA9">
+      <c r="BD9">
         <v>0.33384227752700002</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BF9" t="s">
         <v>274</v>
       </c>
-      <c r="BF9">
+      <c r="BI9">
         <f t="shared" si="1"/>
         <v>0.33384227752700002</v>
       </c>
-      <c r="BG9">
+      <c r="BJ9">
         <v>0.33384227752700002</v>
       </c>
     </row>
-    <row r="10" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>0.98673500000000003</v>
       </c>
@@ -39825,54 +39944,54 @@
       <c r="AL10">
         <v>1.658828</v>
       </c>
-      <c r="AO10">
+      <c r="AQ10">
         <v>1.6922520000000001</v>
       </c>
-      <c r="AP10">
+      <c r="AR10">
         <v>1.6099870000000001</v>
       </c>
-      <c r="AQ10">
+      <c r="AS10">
         <v>1.6886289999999999</v>
       </c>
-      <c r="AR10">
+      <c r="AT10">
         <v>1.6068480000000001</v>
       </c>
-      <c r="AS10">
+      <c r="AU10">
         <v>1.6202350000000001</v>
       </c>
-      <c r="AT10">
+      <c r="AV10">
         <v>1.818635</v>
       </c>
-      <c r="AU10">
+      <c r="AW10">
         <v>1.62094</v>
       </c>
-      <c r="AV10">
+      <c r="AX10">
         <v>1.792997</v>
       </c>
-      <c r="AX10">
+      <c r="BA10">
         <v>1.687951564789</v>
       </c>
-      <c r="AY10">
+      <c r="BB10">
         <v>1.6146095991130001</v>
       </c>
-      <c r="AZ10">
+      <c r="BC10">
         <v>0.63938766717899997</v>
       </c>
-      <c r="BA10">
+      <c r="BD10">
         <v>0.43489494919799998</v>
       </c>
-      <c r="BC10" t="s">
+      <c r="BF10" t="s">
         <v>275</v>
       </c>
-      <c r="BF10">
+      <c r="BI10">
         <f t="shared" si="1"/>
         <v>0.43489494919799998</v>
       </c>
-      <c r="BG10">
+      <c r="BJ10">
         <v>0.43489494919799998</v>
       </c>
     </row>
-    <row r="11" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>0.98447799999999996</v>
       </c>
@@ -39948,54 +40067,54 @@
       <c r="AL11">
         <v>1.601097</v>
       </c>
-      <c r="AO11">
+      <c r="AQ11">
         <v>1.64272</v>
       </c>
-      <c r="AP11">
+      <c r="AR11">
         <v>1.5618110000000001</v>
       </c>
-      <c r="AQ11">
+      <c r="AS11">
         <v>1.637588</v>
       </c>
-      <c r="AR11">
+      <c r="AT11">
         <v>1.557553</v>
       </c>
-      <c r="AS11">
+      <c r="AU11">
         <v>1.455638</v>
       </c>
-      <c r="AT11">
+      <c r="AV11">
         <v>1.357251</v>
       </c>
-      <c r="AU11">
+      <c r="AW11">
         <v>1.4630749999999999</v>
       </c>
-      <c r="AV11">
+      <c r="AX11">
         <v>1.3565419999999999</v>
       </c>
-      <c r="AX11">
+      <c r="BA11">
         <v>1.6362717151640001</v>
       </c>
-      <c r="AY11">
+      <c r="BB11">
         <v>1.4485880136489999</v>
       </c>
-      <c r="AZ11">
+      <c r="BC11">
         <v>0.46305507421499997</v>
       </c>
-      <c r="BA11">
+      <c r="BD11">
         <v>0.15559759736100001</v>
       </c>
-      <c r="BC11" t="s">
+      <c r="BF11" t="s">
         <v>276</v>
       </c>
-      <c r="BF11">
+      <c r="BI11">
         <f t="shared" si="1"/>
         <v>0.15559759736100001</v>
       </c>
-      <c r="BG11">
+      <c r="BJ11">
         <v>0.15559759736100001</v>
       </c>
     </row>
-    <row r="12" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>0.98194800000000004</v>
       </c>
@@ -40071,54 +40190,54 @@
       <c r="AL12">
         <v>1.556826</v>
       </c>
-      <c r="AO12">
+      <c r="AQ12">
         <v>1.583815</v>
       </c>
-      <c r="AP12">
+      <c r="AR12">
         <v>1.5122150000000001</v>
       </c>
-      <c r="AQ12">
+      <c r="AS12">
         <v>1.578627</v>
       </c>
-      <c r="AR12">
+      <c r="AT12">
         <v>1.509576</v>
       </c>
-      <c r="AS12">
+      <c r="AU12">
         <v>1.432617</v>
       </c>
-      <c r="AT12">
+      <c r="AV12">
         <v>1.234858</v>
       </c>
-      <c r="AU12">
+      <c r="AW12">
         <v>1.3702300000000001</v>
       </c>
-      <c r="AV12">
+      <c r="AX12">
         <v>1.2457819999999999</v>
       </c>
-      <c r="AX12">
+      <c r="BA12">
         <v>1.575942516327</v>
       </c>
-      <c r="AY12">
+      <c r="BB12">
         <v>1.4213097095489999</v>
       </c>
-      <c r="AZ12">
+      <c r="BC12">
         <v>0.34168970584899999</v>
       </c>
-      <c r="BA12">
+      <c r="BD12">
         <v>0.108639679849</v>
       </c>
-      <c r="BC12" t="s">
+      <c r="BF12" t="s">
         <v>277</v>
       </c>
-      <c r="BF12">
+      <c r="BI12">
         <f t="shared" si="1"/>
         <v>0.108639679849</v>
       </c>
-      <c r="BG12">
+      <c r="BJ12">
         <v>0.108639679849</v>
       </c>
     </row>
-    <row r="13" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>0.97892699999999999</v>
       </c>
@@ -40194,54 +40313,54 @@
       <c r="AL13">
         <v>1.519781</v>
       </c>
-      <c r="AO13">
+      <c r="AQ13">
         <v>1.520764</v>
       </c>
-      <c r="AP13">
+      <c r="AR13">
         <v>1.4695450000000001</v>
       </c>
-      <c r="AQ13">
+      <c r="AS13">
         <v>1.515447</v>
       </c>
-      <c r="AR13">
+      <c r="AT13">
         <v>1.4637610000000001</v>
       </c>
-      <c r="AS13">
+      <c r="AU13">
         <v>1.2982359999999999</v>
       </c>
-      <c r="AT13">
+      <c r="AV13">
         <v>1.195384</v>
       </c>
-      <c r="AU13">
+      <c r="AW13">
         <v>1.284486</v>
       </c>
-      <c r="AV13">
+      <c r="AX13">
         <v>1.206059</v>
       </c>
-      <c r="AX13">
+      <c r="BA13">
         <v>1.5117769241329999</v>
       </c>
-      <c r="AY13">
+      <c r="BB13">
         <v>1.2891058921809999</v>
       </c>
-      <c r="AZ13">
+      <c r="BC13">
         <v>0.27043786644899998</v>
       </c>
-      <c r="BA13">
+      <c r="BD13">
         <v>7.1228377521000003E-2</v>
       </c>
-      <c r="BC13" t="s">
+      <c r="BF13" t="s">
         <v>278</v>
       </c>
-      <c r="BF13">
+      <c r="BI13">
         <f t="shared" si="1"/>
         <v>7.1228377521000003E-2</v>
       </c>
-      <c r="BG13">
+      <c r="BJ13">
         <v>7.1228377521000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>0.97522299999999995</v>
       </c>
@@ -40317,54 +40436,54 @@
       <c r="AL14">
         <v>1.4827490000000001</v>
       </c>
-      <c r="AO14">
+      <c r="AQ14">
         <v>1.458828</v>
       </c>
-      <c r="AP14">
+      <c r="AR14">
         <v>1.4316230000000001</v>
       </c>
-      <c r="AQ14">
+      <c r="AS14">
         <v>1.451552</v>
       </c>
-      <c r="AR14">
+      <c r="AT14">
         <v>1.423117</v>
       </c>
-      <c r="AS14">
+      <c r="AU14">
         <v>1.236362</v>
       </c>
-      <c r="AT14">
+      <c r="AV14">
         <v>1.1230560000000001</v>
       </c>
-      <c r="AU14">
+      <c r="AW14">
         <v>1.2187300000000001</v>
       </c>
-      <c r="AV14">
+      <c r="AX14">
         <v>1.1310789999999999</v>
       </c>
-      <c r="AX14">
+      <c r="BA14">
         <v>1.4476993083950001</v>
       </c>
-      <c r="AY14">
+      <c r="BB14">
         <v>1.2284952402110001</v>
       </c>
-      <c r="AZ14">
+      <c r="BC14">
         <v>0.20793943107099999</v>
       </c>
-      <c r="BA14">
+      <c r="BD14">
         <v>5.3653735666999998E-2</v>
       </c>
-      <c r="BC14" t="s">
+      <c r="BF14" t="s">
         <v>279</v>
       </c>
-      <c r="BF14">
+      <c r="BI14">
         <f t="shared" si="1"/>
         <v>5.3653735666999998E-2</v>
       </c>
-      <c r="BG14">
+      <c r="BJ14">
         <v>5.3653735666999998E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>0.97067700000000001</v>
       </c>
@@ -40440,54 +40559,54 @@
       <c r="AL15">
         <v>1.452413</v>
       </c>
-      <c r="AO15">
+      <c r="AQ15">
         <v>1.39985</v>
       </c>
-      <c r="AP15">
+      <c r="AR15">
         <v>1.381891</v>
       </c>
-      <c r="AQ15">
+      <c r="AS15">
         <v>1.3913819999999999</v>
       </c>
-      <c r="AR15">
+      <c r="AT15">
         <v>1.371149</v>
       </c>
-      <c r="AS15">
+      <c r="AU15">
         <v>1.172944</v>
       </c>
-      <c r="AT15">
+      <c r="AV15">
         <v>1.069812</v>
       </c>
-      <c r="AU15">
+      <c r="AW15">
         <v>1.146218</v>
       </c>
-      <c r="AV15">
+      <c r="AX15">
         <v>1.0590310000000001</v>
       </c>
-      <c r="AX15">
+      <c r="BA15">
         <v>1.3889671564099999</v>
       </c>
-      <c r="AY15">
+      <c r="BB15">
         <v>1.1635917425160001</v>
       </c>
-      <c r="AZ15">
+      <c r="BC15">
         <v>0.15615528821899999</v>
       </c>
-      <c r="BA15">
+      <c r="BD15">
         <v>4.4098272920000001E-2</v>
       </c>
-      <c r="BC15" t="s">
+      <c r="BF15" t="s">
         <v>280</v>
       </c>
-      <c r="BF15">
+      <c r="BI15">
         <f t="shared" si="1"/>
         <v>4.4098272920000001E-2</v>
       </c>
-      <c r="BG15">
+      <c r="BJ15">
         <v>4.4098272920000001E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>0.96513400000000005</v>
       </c>
@@ -40563,54 +40682,54 @@
       <c r="AL16">
         <v>1.452626</v>
       </c>
-      <c r="AO16">
+      <c r="AQ16">
         <v>1.3570800000000001</v>
       </c>
-      <c r="AP16">
+      <c r="AR16">
         <v>1.3457920000000001</v>
       </c>
-      <c r="AQ16">
+      <c r="AS16">
         <v>1.3381130000000001</v>
       </c>
-      <c r="AR16">
+      <c r="AT16">
         <v>1.3355440000000001</v>
       </c>
-      <c r="AS16">
+      <c r="AU16">
         <v>1.130396</v>
       </c>
-      <c r="AT16">
+      <c r="AV16">
         <v>1.0212840000000001</v>
       </c>
-      <c r="AU16">
+      <c r="AW16">
         <v>1.0914269999999999</v>
       </c>
-      <c r="AV16">
+      <c r="AX16">
         <v>1.0289680000000001</v>
       </c>
-      <c r="AX16">
+      <c r="BA16">
         <v>1.3429929018019999</v>
       </c>
-      <c r="AY16">
+      <c r="BB16">
         <v>1.1186946630479999</v>
       </c>
-      <c r="AZ16">
+      <c r="BC16">
         <v>0.1276383847</v>
       </c>
-      <c r="BA16">
+      <c r="BD16">
         <v>3.7159100175000001E-2</v>
       </c>
-      <c r="BC16" t="s">
+      <c r="BF16" t="s">
         <v>281</v>
       </c>
-      <c r="BF16">
+      <c r="BI16">
         <f t="shared" si="1"/>
         <v>3.7159100175000001E-2</v>
       </c>
-      <c r="BG16">
+      <c r="BJ16">
         <v>3.7159100175000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>0.95843699999999998</v>
       </c>
@@ -40686,54 +40805,54 @@
       <c r="AL17">
         <v>1.421271</v>
       </c>
-      <c r="AO17">
+      <c r="AQ17">
         <v>1.3526229999999999</v>
       </c>
-      <c r="AP17">
+      <c r="AR17">
         <v>1.3058050000000001</v>
       </c>
-      <c r="AQ17">
+      <c r="AS17">
         <v>1.312003</v>
       </c>
-      <c r="AR17">
+      <c r="AT17">
         <v>1.2937909999999999</v>
       </c>
-      <c r="AS17">
+      <c r="AU17">
         <v>1.0769709999999999</v>
       </c>
-      <c r="AT17">
+      <c r="AV17">
         <v>0.97205900000000001</v>
       </c>
-      <c r="AU17">
+      <c r="AW17">
         <v>1.0347139999999999</v>
       </c>
-      <c r="AV17">
+      <c r="AX17">
         <v>0.97130399999999995</v>
       </c>
-      <c r="AX17">
+      <c r="BA17">
         <v>1.3304553031919999</v>
       </c>
-      <c r="AY17">
+      <c r="BB17">
         <v>1.064089655876</v>
       </c>
-      <c r="AZ17">
+      <c r="BC17">
         <v>9.8925307392999998E-2</v>
       </c>
-      <c r="BA17">
+      <c r="BD17">
         <v>3.1714715063999997E-2</v>
       </c>
-      <c r="BC17" t="s">
+      <c r="BF17" t="s">
         <v>282</v>
       </c>
-      <c r="BF17">
+      <c r="BI17">
         <f t="shared" si="1"/>
         <v>3.1714715063999997E-2</v>
       </c>
-      <c r="BG17">
+      <c r="BJ17">
         <v>3.1714715063999997E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>0.95043800000000001</v>
       </c>
@@ -40809,54 +40928,54 @@
       <c r="AL18">
         <v>1.3790659999999999</v>
       </c>
-      <c r="AO18">
+      <c r="AQ18">
         <v>1.3090409999999999</v>
       </c>
-      <c r="AP18">
+      <c r="AR18">
         <v>1.2702960000000001</v>
       </c>
-      <c r="AQ18">
+      <c r="AS18">
         <v>1.2987280000000001</v>
       </c>
-      <c r="AR18">
+      <c r="AT18">
         <v>1.256802</v>
       </c>
-      <c r="AS18">
+      <c r="AU18">
         <v>1.029434</v>
       </c>
-      <c r="AT18">
+      <c r="AV18">
         <v>0.91123900000000002</v>
       </c>
-      <c r="AU18">
+      <c r="AW18">
         <v>0.98081499999999999</v>
       </c>
-      <c r="AV18">
+      <c r="AX18">
         <v>0.92918500000000004</v>
       </c>
-      <c r="AX18">
+      <c r="BA18">
         <v>1.2909761667249999</v>
       </c>
-      <c r="AY18">
+      <c r="BB18">
         <v>1.015993952751</v>
       </c>
-      <c r="AZ18">
+      <c r="BC18">
         <v>7.6265811919999996E-2</v>
       </c>
-      <c r="BA18">
+      <c r="BD18">
         <v>2.7700407430999999E-2</v>
       </c>
-      <c r="BC18" t="s">
+      <c r="BF18" t="s">
         <v>283</v>
       </c>
-      <c r="BF18">
+      <c r="BI18">
         <f t="shared" si="1"/>
         <v>2.7700407430999999E-2</v>
       </c>
-      <c r="BG18">
+      <c r="BJ18">
         <v>2.7700407430999999E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>0.94104200000000005</v>
       </c>
@@ -40932,54 +41051,54 @@
       <c r="AL19">
         <v>1.345647</v>
       </c>
-      <c r="AO19">
+      <c r="AQ19">
         <v>1.269458</v>
       </c>
-      <c r="AP19">
+      <c r="AR19">
         <v>1.237179</v>
       </c>
-      <c r="AQ19">
+      <c r="AS19">
         <v>1.2361249999999999</v>
       </c>
-      <c r="AR19">
+      <c r="AT19">
         <v>1.2227809999999999</v>
       </c>
-      <c r="AS19">
+      <c r="AU19">
         <v>0.97483900000000001</v>
       </c>
-      <c r="AT19">
+      <c r="AV19">
         <v>0.85122299999999995</v>
       </c>
-      <c r="AU19">
+      <c r="AW19">
         <v>0.92408299999999999</v>
       </c>
-      <c r="AV19">
+      <c r="AX19">
         <v>0.87070700000000001</v>
       </c>
-      <c r="AX19">
+      <c r="BA19">
         <v>1.246168613434</v>
       </c>
-      <c r="AY19">
+      <c r="BB19">
         <v>0.96099555492400002</v>
       </c>
-      <c r="AZ19">
+      <c r="BC19">
         <v>5.9899646788999998E-2</v>
       </c>
-      <c r="BA19">
+      <c r="BD19">
         <v>2.5062950327999999E-2</v>
       </c>
-      <c r="BC19" t="s">
+      <c r="BF19" t="s">
         <v>284</v>
       </c>
-      <c r="BF19">
+      <c r="BI19">
         <f t="shared" si="1"/>
         <v>2.5062950327999999E-2</v>
       </c>
-      <c r="BG19">
+      <c r="BJ19">
         <v>2.5062950327999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>0.93025500000000005</v>
       </c>
@@ -41055,54 +41174,54 @@
       <c r="AL20">
         <v>1.310025</v>
       </c>
-      <c r="AO20">
+      <c r="AQ20">
         <v>1.235819</v>
       </c>
-      <c r="AP20">
+      <c r="AR20">
         <v>1.20262</v>
       </c>
-      <c r="AQ20">
+      <c r="AS20">
         <v>1.216175</v>
       </c>
-      <c r="AR20">
+      <c r="AT20">
         <v>1.187767</v>
       </c>
-      <c r="AS20">
+      <c r="AU20">
         <v>0.91692499999999999</v>
       </c>
-      <c r="AT20">
+      <c r="AV20">
         <v>0.80543799999999999</v>
       </c>
-      <c r="AU20">
+      <c r="AW20">
         <v>0.86564700000000006</v>
       </c>
-      <c r="AV20">
+      <c r="AX20">
         <v>0.81555100000000003</v>
       </c>
-      <c r="AX20">
+      <c r="BA20">
         <v>1.2156499624249999</v>
       </c>
-      <c r="AY20">
+      <c r="BB20">
         <v>0.902531921864</v>
       </c>
-      <c r="AZ20">
+      <c r="BC20">
         <v>5.0181172788000002E-2</v>
       </c>
-      <c r="BA20">
+      <c r="BD20">
         <v>2.3444138467000001E-2</v>
       </c>
-      <c r="BC20" t="s">
+      <c r="BF20" t="s">
         <v>285</v>
       </c>
-      <c r="BF20">
+      <c r="BI20">
         <f t="shared" si="1"/>
         <v>2.3444138467000001E-2</v>
       </c>
-      <c r="BG20">
+      <c r="BJ20">
         <v>2.3444138467000001E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>0.91823100000000002</v>
       </c>
@@ -41178,54 +41297,54 @@
       <c r="AL21">
         <v>1.3191029999999999</v>
       </c>
-      <c r="AO21">
+      <c r="AQ21">
         <v>1.2189270000000001</v>
       </c>
-      <c r="AP21">
+      <c r="AR21">
         <v>1.1705909999999999</v>
       </c>
-      <c r="AQ21">
+      <c r="AS21">
         <v>1.182498</v>
       </c>
-      <c r="AR21">
+      <c r="AT21">
         <v>1.157116</v>
       </c>
-      <c r="AS21">
+      <c r="AU21">
         <v>0.866004</v>
       </c>
-      <c r="AT21">
+      <c r="AV21">
         <v>0.75692400000000004</v>
       </c>
-      <c r="AU21">
+      <c r="AW21">
         <v>0.81180699999999995</v>
       </c>
-      <c r="AV21">
+      <c r="AX21">
         <v>0.77560799999999996</v>
       </c>
-      <c r="AX21">
+      <c r="BA21">
         <v>1.195297598839</v>
       </c>
-      <c r="AY21">
+      <c r="BB21">
         <v>0.85038059949900002</v>
       </c>
-      <c r="AZ21">
+      <c r="BC21">
         <v>4.2678341268999997E-2</v>
       </c>
-      <c r="BA21">
+      <c r="BD21">
         <v>2.2247051819999999E-2</v>
       </c>
-      <c r="BC21" t="s">
+      <c r="BF21" t="s">
         <v>286</v>
       </c>
-      <c r="BF21">
+      <c r="BI21">
         <f t="shared" si="1"/>
         <v>2.2247051819999999E-2</v>
       </c>
-      <c r="BG21">
+      <c r="BJ21">
         <v>2.2247051819999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>0.90524800000000005</v>
       </c>
@@ -41301,54 +41420,54 @@
       <c r="AL22">
         <v>1.277442</v>
       </c>
-      <c r="AO22">
+      <c r="AQ22">
         <v>1.1954689999999999</v>
       </c>
-      <c r="AP22">
+      <c r="AR22">
         <v>1.142272</v>
       </c>
-      <c r="AQ22">
+      <c r="AS22">
         <v>1.157902</v>
       </c>
-      <c r="AR22">
+      <c r="AT22">
         <v>1.1257969999999999</v>
       </c>
-      <c r="AS22">
+      <c r="AU22">
         <v>0.81881499999999996</v>
       </c>
-      <c r="AT22">
+      <c r="AV22">
         <v>0.71708400000000005</v>
       </c>
-      <c r="AU22">
+      <c r="AW22">
         <v>0.76307800000000003</v>
       </c>
-      <c r="AV22">
+      <c r="AX22">
         <v>0.71721900000000005</v>
       </c>
-      <c r="AX22">
+      <c r="BA22">
         <v>1.1678025722500001</v>
       </c>
-      <c r="AY22">
+      <c r="BB22">
         <v>0.80279219150500003</v>
       </c>
-      <c r="AZ22">
+      <c r="BC22">
         <v>3.6354616284000003E-2</v>
       </c>
-      <c r="BA22">
+      <c r="BD22">
         <v>2.0974807440999998E-2</v>
       </c>
-      <c r="BC22" t="s">
+      <c r="BF22" t="s">
         <v>287</v>
       </c>
-      <c r="BF22">
+      <c r="BI22">
         <f t="shared" si="1"/>
         <v>2.0974807440999998E-2</v>
       </c>
-      <c r="BG22">
+      <c r="BJ22">
         <v>2.0974807440999998E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>0.89161400000000002</v>
       </c>
@@ -41424,54 +41543,54 @@
       <c r="AL23">
         <v>1.23203</v>
       </c>
-      <c r="AO23">
+      <c r="AQ23">
         <v>1.1705939999999999</v>
       </c>
-      <c r="AP23">
+      <c r="AR23">
         <v>1.1168670000000001</v>
       </c>
-      <c r="AQ23">
+      <c r="AS23">
         <v>1.141591</v>
       </c>
-      <c r="AR23">
+      <c r="AT23">
         <v>1.099593</v>
       </c>
-      <c r="AS23">
+      <c r="AU23">
         <v>0.776586</v>
       </c>
-      <c r="AT23">
+      <c r="AV23">
         <v>0.674682</v>
       </c>
-      <c r="AU23">
+      <c r="AW23">
         <v>0.71769400000000005</v>
       </c>
-      <c r="AV23">
+      <c r="AX23">
         <v>0.67741499999999999</v>
       </c>
-      <c r="AX23">
+      <c r="BA23">
         <v>1.1451742649079999</v>
       </c>
-      <c r="AY23">
+      <c r="BB23">
         <v>0.76072132587399999</v>
       </c>
-      <c r="AZ23">
+      <c r="BC23">
         <v>3.1021051109000001E-2</v>
       </c>
-      <c r="BA23">
+      <c r="BD23">
         <v>1.9508382306000001E-2</v>
       </c>
-      <c r="BC23" t="s">
+      <c r="BF23" t="s">
         <v>288</v>
       </c>
-      <c r="BF23">
+      <c r="BI23">
         <f t="shared" si="1"/>
         <v>1.9508382306000001E-2</v>
       </c>
-      <c r="BG23">
+      <c r="BJ23">
         <v>1.9508382306000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>0.87756400000000001</v>
       </c>
@@ -41547,54 +41666,54 @@
       <c r="AL24">
         <v>1.2123679999999999</v>
       </c>
-      <c r="AO24">
+      <c r="AQ24">
         <v>1.149249</v>
       </c>
-      <c r="AP24">
+      <c r="AR24">
         <v>1.0934410000000001</v>
       </c>
-      <c r="AQ24">
+      <c r="AS24">
         <v>1.115305</v>
       </c>
-      <c r="AR24">
+      <c r="AT24">
         <v>1.0775999999999999</v>
       </c>
-      <c r="AS24">
+      <c r="AU24">
         <v>0.73048100000000005</v>
       </c>
-      <c r="AT24">
+      <c r="AV24">
         <v>0.64051100000000005</v>
       </c>
-      <c r="AU24">
+      <c r="AW24">
         <v>0.67308800000000002</v>
       </c>
-      <c r="AV24">
+      <c r="AX24">
         <v>0.64125100000000002</v>
       </c>
-      <c r="AX24">
+      <c r="BA24">
         <v>1.123755693436</v>
       </c>
-      <c r="AY24">
+      <c r="BB24">
         <v>0.71484500169800003</v>
       </c>
-      <c r="AZ24">
+      <c r="BC24">
         <v>2.7081742882999998E-2</v>
       </c>
-      <c r="BA24">
+      <c r="BD24">
         <v>1.7987692728999999E-2</v>
       </c>
-      <c r="BC24" t="s">
+      <c r="BF24" t="s">
         <v>289</v>
       </c>
-      <c r="BF24">
+      <c r="BI24">
         <f t="shared" si="1"/>
         <v>1.7987692728999999E-2</v>
       </c>
-      <c r="BG24">
+      <c r="BJ24">
         <v>1.7987692728999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>0.86320200000000002</v>
       </c>
@@ -41670,54 +41789,54 @@
       <c r="AL25">
         <v>1.189643</v>
       </c>
-      <c r="AO25">
+      <c r="AQ25">
         <v>1.123162</v>
       </c>
-      <c r="AP25">
+      <c r="AR25">
         <v>1.0807329999999999</v>
       </c>
-      <c r="AQ25">
+      <c r="AS25">
         <v>1.0862130000000001</v>
       </c>
-      <c r="AR25">
+      <c r="AT25">
         <v>1.0587610000000001</v>
       </c>
-      <c r="AS25">
+      <c r="AU25">
         <v>0.68913199999999997</v>
       </c>
-      <c r="AT25">
+      <c r="AV25">
         <v>0.60159700000000005</v>
       </c>
-      <c r="AU25">
+      <c r="AW25">
         <v>0.63260899999999998</v>
       </c>
-      <c r="AV25">
+      <c r="AX25">
         <v>0.59903799999999996</v>
       </c>
-      <c r="AX25">
+      <c r="BA25">
         <v>1.094591379166</v>
       </c>
-      <c r="AY25">
+      <c r="BB25">
         <v>0.67277371883399995</v>
       </c>
-      <c r="AZ25">
+      <c r="BC25">
         <v>2.4643385782999998E-2</v>
       </c>
-      <c r="BA25">
+      <c r="BD25">
         <v>1.6524447128000001E-2</v>
       </c>
-      <c r="BC25" t="s">
+      <c r="BF25" t="s">
         <v>290</v>
       </c>
-      <c r="BF25">
+      <c r="BI25">
         <f t="shared" si="1"/>
         <v>1.6524447128000001E-2</v>
       </c>
-      <c r="BG25">
+      <c r="BJ25">
         <v>1.6524447128000001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>0.84857099999999996</v>
       </c>
@@ -41793,54 +41912,54 @@
       <c r="AL26">
         <v>1.156013</v>
       </c>
-      <c r="AO26">
+      <c r="AQ26">
         <v>1.093804</v>
       </c>
-      <c r="AP26">
+      <c r="AR26">
         <v>1.064649</v>
       </c>
-      <c r="AQ26">
+      <c r="AS26">
         <v>1.0642860000000001</v>
       </c>
-      <c r="AR26">
+      <c r="AT26">
         <v>1.035981</v>
       </c>
-      <c r="AS26">
+      <c r="AU26">
         <v>0.65237599999999996</v>
       </c>
-      <c r="AT26">
+      <c r="AV26">
         <v>0.57268699999999995</v>
       </c>
-      <c r="AU26">
+      <c r="AW26">
         <v>0.59618499999999996</v>
       </c>
-      <c r="AV26">
+      <c r="AX26">
         <v>0.56318199999999996</v>
       </c>
-      <c r="AX26">
+      <c r="BA26">
         <v>1.067304134369</v>
       </c>
-      <c r="AY26">
+      <c r="BB26">
         <v>0.63556271791499996</v>
       </c>
-      <c r="AZ26">
+      <c r="BC26">
         <v>2.2391987964999999E-2</v>
       </c>
-      <c r="BA26">
+      <c r="BD26">
         <v>1.5107212587999999E-2</v>
       </c>
-      <c r="BC26" t="s">
+      <c r="BF26" t="s">
         <v>291</v>
       </c>
-      <c r="BF26">
+      <c r="BI26">
         <f t="shared" si="1"/>
         <v>1.5107212587999999E-2</v>
       </c>
-      <c r="BG26">
+      <c r="BJ26">
         <v>1.5107212587999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>0.83374599999999999</v>
       </c>
@@ -41916,54 +42035,54 @@
       <c r="AL27">
         <v>1.1236520000000001</v>
       </c>
-      <c r="AO27">
+      <c r="AQ27">
         <v>1.0710299999999999</v>
       </c>
-      <c r="AP27">
+      <c r="AR27">
         <v>1.0313079999999999</v>
       </c>
-      <c r="AQ27">
+      <c r="AS27">
         <v>1.0398799999999999</v>
       </c>
-      <c r="AR27">
+      <c r="AT27">
         <v>1.0107429999999999</v>
       </c>
-      <c r="AS27">
+      <c r="AU27">
         <v>0.61911099999999997</v>
       </c>
-      <c r="AT27">
+      <c r="AV27">
         <v>0.532887</v>
       </c>
-      <c r="AU27">
+      <c r="AW27">
         <v>0.56113800000000003</v>
       </c>
-      <c r="AV27">
+      <c r="AX27">
         <v>0.52977399999999997</v>
       </c>
-      <c r="AX27">
+      <c r="BA27">
         <v>1.0469511747360001</v>
       </c>
-      <c r="AY27">
+      <c r="BB27">
         <v>0.60231328010600005</v>
       </c>
-      <c r="AZ27">
+      <c r="BC27">
         <v>2.0215334371E-2</v>
       </c>
-      <c r="BA27">
+      <c r="BD27">
         <v>1.3682960532999999E-2</v>
       </c>
-      <c r="BC27" t="s">
+      <c r="BF27" t="s">
         <v>292</v>
       </c>
-      <c r="BF27">
+      <c r="BI27">
         <f t="shared" si="1"/>
         <v>1.3682960532999999E-2</v>
       </c>
-      <c r="BG27">
+      <c r="BJ27">
         <v>1.3682960532999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>0.81885200000000002</v>
       </c>
@@ -42039,54 +42158,54 @@
       <c r="AL28">
         <v>1.0949089999999999</v>
       </c>
-      <c r="AO28">
+      <c r="AQ28">
         <v>1.0496760000000001</v>
       </c>
-      <c r="AP28">
+      <c r="AR28">
         <v>1.004772</v>
       </c>
-      <c r="AQ28">
+      <c r="AS28">
         <v>1.0134449999999999</v>
       </c>
-      <c r="AR28">
+      <c r="AT28">
         <v>0.98355000000000004</v>
       </c>
-      <c r="AS28">
+      <c r="AU28">
         <v>0.58528500000000006</v>
       </c>
-      <c r="AT28">
+      <c r="AV28">
         <v>0.50803399999999999</v>
       </c>
-      <c r="AU28">
+      <c r="AW28">
         <v>0.52812899999999996</v>
       </c>
-      <c r="AV28">
+      <c r="AX28">
         <v>0.494813</v>
       </c>
-      <c r="AX28">
+      <c r="BA28">
         <v>1.0230053663250001</v>
       </c>
-      <c r="AY28">
+      <c r="BB28">
         <v>0.56833851337399999</v>
       </c>
-      <c r="AZ28">
+      <c r="BC28">
         <v>1.8380461261E-2</v>
       </c>
-      <c r="BA28">
+      <c r="BD28">
         <v>1.2241309509000001E-2</v>
       </c>
-      <c r="BC28" t="s">
+      <c r="BF28" t="s">
         <v>293</v>
       </c>
-      <c r="BF28">
+      <c r="BI28">
         <f t="shared" si="1"/>
         <v>1.2241309509000001E-2</v>
       </c>
-      <c r="BG28">
+      <c r="BJ28">
         <v>1.2241309509000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>0.80398800000000004</v>
       </c>
@@ -42162,54 +42281,54 @@
       <c r="AL29">
         <v>1.064206</v>
       </c>
-      <c r="AO29">
+      <c r="AQ29">
         <v>1.0275909999999999</v>
       </c>
-      <c r="AP29">
+      <c r="AR29">
         <v>0.98515200000000003</v>
       </c>
-      <c r="AQ29">
+      <c r="AS29">
         <v>0.99544600000000005</v>
       </c>
-      <c r="AR29">
+      <c r="AT29">
         <v>0.95950500000000005</v>
       </c>
-      <c r="AS29">
+      <c r="AU29">
         <v>0.55362599999999995</v>
       </c>
-      <c r="AT29">
+      <c r="AV29">
         <v>0.47430299999999997</v>
       </c>
-      <c r="AU29">
+      <c r="AW29">
         <v>0.49895299999999998</v>
       </c>
-      <c r="AV29">
+      <c r="AX29">
         <v>0.46590900000000002</v>
       </c>
-      <c r="AX29">
+      <c r="BA29">
         <v>1.0021741390229999</v>
       </c>
-      <c r="AY29">
+      <c r="BB29">
         <v>0.53614062070799995</v>
       </c>
-      <c r="AZ29">
+      <c r="BC29">
         <v>1.6563693061000001E-2</v>
       </c>
-      <c r="BA29">
+      <c r="BD29">
         <v>1.0834204033E-2</v>
       </c>
-      <c r="BC29" t="s">
+      <c r="BF29" t="s">
         <v>294</v>
       </c>
-      <c r="BF29">
+      <c r="BI29">
         <f t="shared" si="1"/>
         <v>1.0834204033E-2</v>
       </c>
-      <c r="BG29">
+      <c r="BJ29">
         <v>1.0834204033E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>0.78917499999999996</v>
       </c>
@@ -42285,54 +42404,54 @@
       <c r="AL30">
         <v>1.0390200000000001</v>
       </c>
-      <c r="AO30">
+      <c r="AQ30">
         <v>1.0099279999999999</v>
       </c>
-      <c r="AP30">
+      <c r="AR30">
         <v>0.96327200000000002</v>
       </c>
-      <c r="AQ30">
+      <c r="AS30">
         <v>0.97447799999999996</v>
       </c>
-      <c r="AR30">
+      <c r="AT30">
         <v>0.93989999999999996</v>
       </c>
-      <c r="AS30">
+      <c r="AU30">
         <v>0.52604300000000004</v>
       </c>
-      <c r="AT30">
+      <c r="AV30">
         <v>0.45128000000000001</v>
       </c>
-      <c r="AU30">
+      <c r="AW30">
         <v>0.47056999999999999</v>
       </c>
-      <c r="AV30">
+      <c r="AX30">
         <v>0.43767600000000001</v>
       </c>
-      <c r="AX30">
+      <c r="BA30">
         <v>0.98317927122100002</v>
       </c>
-      <c r="AY30">
+      <c r="BB30">
         <v>0.508408129215</v>
       </c>
-      <c r="AZ30">
+      <c r="BC30">
         <v>1.4972373843E-2</v>
       </c>
-      <c r="BA30">
+      <c r="BD30">
         <v>9.5554515720000007E-3</v>
       </c>
-      <c r="BC30" t="s">
+      <c r="BF30" t="s">
         <v>295</v>
       </c>
-      <c r="BF30">
+      <c r="BI30">
         <f t="shared" si="1"/>
         <v>9.5554515720000007E-3</v>
       </c>
-      <c r="BG30">
+      <c r="BJ30">
         <v>9.5554515720000007E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>0.77444299999999999</v>
       </c>
@@ -42408,54 +42527,54 @@
       <c r="AL31">
         <v>1.022554</v>
       </c>
-      <c r="AO31">
+      <c r="AQ31">
         <v>0.98763199999999995</v>
       </c>
-      <c r="AP31">
+      <c r="AR31">
         <v>0.94483499999999998</v>
       </c>
-      <c r="AQ31">
+      <c r="AS31">
         <v>0.95252800000000004</v>
       </c>
-      <c r="AR31">
+      <c r="AT31">
         <v>0.92666000000000004</v>
       </c>
-      <c r="AS31">
+      <c r="AU31">
         <v>0.49891799999999997</v>
       </c>
-      <c r="AT31">
+      <c r="AV31">
         <v>0.422292</v>
       </c>
-      <c r="AU31">
+      <c r="AW31">
         <v>0.44308700000000001</v>
       </c>
-      <c r="AV31">
+      <c r="AX31">
         <v>0.41207700000000003</v>
       </c>
-      <c r="AX31">
+      <c r="BA31">
         <v>0.96079635620100001</v>
       </c>
-      <c r="AY31">
+      <c r="BB31">
         <v>0.481347709894</v>
       </c>
-      <c r="AZ31">
+      <c r="BC31">
         <v>1.3314384036E-2</v>
       </c>
-      <c r="BA31">
+      <c r="BD31">
         <v>8.4959259260000003E-3</v>
       </c>
-      <c r="BC31" t="s">
+      <c r="BF31" t="s">
         <v>296</v>
       </c>
-      <c r="BF31">
+      <c r="BI31">
         <f t="shared" si="1"/>
         <v>8.4959259260000003E-3</v>
       </c>
-      <c r="BG31">
+      <c r="BJ31">
         <v>8.4959259260000003E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>0.75983800000000001</v>
       </c>
@@ -42531,54 +42650,54 @@
       <c r="AL32">
         <v>1.024184</v>
       </c>
-      <c r="AO32">
+      <c r="AQ32">
         <v>0.96631299999999998</v>
       </c>
-      <c r="AP32">
+      <c r="AR32">
         <v>0.92145699999999997</v>
       </c>
-      <c r="AQ32">
+      <c r="AS32">
         <v>0.93404200000000004</v>
       </c>
-      <c r="AR32">
+      <c r="AT32">
         <v>0.92715099999999995</v>
       </c>
-      <c r="AS32">
+      <c r="AU32">
         <v>0.47236</v>
       </c>
-      <c r="AT32">
+      <c r="AV32">
         <v>0.39764899999999997</v>
       </c>
-      <c r="AU32">
+      <c r="AW32">
         <v>0.41856100000000002</v>
       </c>
-      <c r="AV32">
+      <c r="AX32">
         <v>0.390378</v>
       </c>
-      <c r="AX32">
+      <c r="BA32">
         <v>0.94083696603800004</v>
       </c>
-      <c r="AY32">
+      <c r="BB32">
         <v>0.454395800829</v>
       </c>
-      <c r="AZ32">
+      <c r="BC32">
         <v>1.1976066977E-2</v>
       </c>
-      <c r="BA32">
+      <c r="BD32">
         <v>7.6792682520000002E-3</v>
       </c>
-      <c r="BC32" t="s">
+      <c r="BF32" t="s">
         <v>297</v>
       </c>
-      <c r="BF32">
+      <c r="BI32">
         <f t="shared" si="1"/>
         <v>7.6792682520000002E-3</v>
       </c>
-      <c r="BG32">
+      <c r="BJ32">
         <v>7.6792682520000002E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>0.74540899999999999</v>
       </c>
@@ -42654,54 +42773,54 @@
       <c r="AL33">
         <v>0.992089</v>
       </c>
-      <c r="AO33">
+      <c r="AQ33">
         <v>0.946801</v>
       </c>
-      <c r="AP33">
+      <c r="AR33">
         <v>0.90535100000000002</v>
       </c>
-      <c r="AQ33">
+      <c r="AS33">
         <v>0.91265700000000005</v>
       </c>
-      <c r="AR33">
+      <c r="AT33">
         <v>0.90751999999999999</v>
       </c>
-      <c r="AS33">
+      <c r="AU33">
         <v>0.44765700000000003</v>
       </c>
-      <c r="AT33">
+      <c r="AV33">
         <v>0.37432700000000002</v>
       </c>
-      <c r="AU33">
+      <c r="AW33">
         <v>0.39482600000000001</v>
       </c>
-      <c r="AV33">
+      <c r="AX33">
         <v>0.36556899999999998</v>
       </c>
-      <c r="AX33">
+      <c r="BA33">
         <v>0.92132985591899996</v>
       </c>
-      <c r="AY33">
+      <c r="BB33">
         <v>0.42979568242999999</v>
       </c>
-      <c r="AZ33">
+      <c r="BC33">
         <v>1.0820464231000001E-2</v>
       </c>
-      <c r="BA33">
+      <c r="BD33">
         <v>7.0295371120000002E-3</v>
       </c>
-      <c r="BC33" t="s">
+      <c r="BF33" t="s">
         <v>298</v>
       </c>
-      <c r="BF33">
+      <c r="BI33">
         <f t="shared" si="1"/>
         <v>7.0295371120000002E-3</v>
       </c>
-      <c r="BG33">
+      <c r="BJ33">
         <v>7.0295371120000002E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>0.73117399999999999</v>
       </c>
@@ -42777,54 +42896,54 @@
       <c r="AL34">
         <v>0.96679599999999999</v>
       </c>
-      <c r="AO34">
+      <c r="AQ34">
         <v>0.92740500000000003</v>
       </c>
-      <c r="AP34">
+      <c r="AR34">
         <v>0.89035600000000004</v>
       </c>
-      <c r="AQ34">
+      <c r="AS34">
         <v>0.89346099999999995</v>
       </c>
-      <c r="AR34">
+      <c r="AT34">
         <v>0.88472799999999996</v>
       </c>
-      <c r="AS34">
+      <c r="AU34">
         <v>0.42479600000000001</v>
       </c>
-      <c r="AT34">
+      <c r="AV34">
         <v>0.349555</v>
       </c>
-      <c r="AU34">
+      <c r="AW34">
         <v>0.37186200000000003</v>
       </c>
-      <c r="AV34">
+      <c r="AX34">
         <v>0.33571099999999998</v>
       </c>
-      <c r="AX34">
+      <c r="BA34">
         <v>0.90196031332000004</v>
       </c>
-      <c r="AY34">
+      <c r="BB34">
         <v>0.40717318654099999</v>
       </c>
-      <c r="AZ34">
+      <c r="BC34">
         <v>9.8038204010000001E-3</v>
       </c>
-      <c r="BA34">
+      <c r="BD34">
         <v>6.437828764E-3</v>
       </c>
-      <c r="BC34" t="s">
+      <c r="BF34" t="s">
         <v>299</v>
       </c>
-      <c r="BF34">
+      <c r="BI34">
         <f t="shared" si="1"/>
         <v>6.437828764E-3</v>
       </c>
-      <c r="BG34">
+      <c r="BJ34">
         <v>6.437828764E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>0.71716299999999999</v>
       </c>
@@ -42900,54 +43019,54 @@
       <c r="AL35">
         <v>0.94805799999999996</v>
       </c>
-      <c r="AO35">
+      <c r="AQ35">
         <v>0.90931300000000004</v>
       </c>
-      <c r="AP35">
+      <c r="AR35">
         <v>0.87656100000000003</v>
       </c>
-      <c r="AQ35">
+      <c r="AS35">
         <v>0.87528499999999998</v>
       </c>
-      <c r="AR35">
+      <c r="AT35">
         <v>0.85434200000000005</v>
       </c>
-      <c r="AS35">
+      <c r="AU35">
         <v>0.40299800000000002</v>
       </c>
-      <c r="AT35">
+      <c r="AV35">
         <v>0.33062000000000002</v>
       </c>
-      <c r="AU35">
+      <c r="AW35">
         <v>0.35123300000000002</v>
       </c>
-      <c r="AV35">
+      <c r="AX35">
         <v>0.31688</v>
       </c>
-      <c r="AX35">
+      <c r="BA35">
         <v>0.88364714384099996</v>
       </c>
-      <c r="AY35">
+      <c r="BB35">
         <v>0.384952932596</v>
       </c>
-      <c r="AZ35">
+      <c r="BC35">
         <v>8.8583119209999991E-3</v>
       </c>
-      <c r="BA35">
+      <c r="BD35">
         <v>5.8710705489999999E-3</v>
       </c>
-      <c r="BC35" t="s">
+      <c r="BF35" t="s">
         <v>300</v>
       </c>
-      <c r="BF35">
+      <c r="BI35">
         <f t="shared" si="1"/>
         <v>5.8710705489999999E-3</v>
       </c>
-      <c r="BG35">
+      <c r="BJ35">
         <v>5.8710705489999999E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>0.703399</v>
       </c>
@@ -43023,54 +43142,54 @@
       <c r="AL36">
         <v>0.91881699999999999</v>
       </c>
-      <c r="AO36">
+      <c r="AQ36">
         <v>0.89066199999999995</v>
       </c>
-      <c r="AP36">
+      <c r="AR36">
         <v>0.85263500000000003</v>
       </c>
-      <c r="AQ36">
+      <c r="AS36">
         <v>0.85612299999999997</v>
       </c>
-      <c r="AR36">
+      <c r="AT36">
         <v>0.83029699999999995</v>
       </c>
-      <c r="AS36">
+      <c r="AU36">
         <v>0.38198399999999999</v>
       </c>
-      <c r="AT36">
+      <c r="AV36">
         <v>0.30769999999999997</v>
       </c>
-      <c r="AU36">
+      <c r="AW36">
         <v>0.33093099999999998</v>
       </c>
-      <c r="AV36">
+      <c r="AX36">
         <v>0.29930600000000002</v>
       </c>
-      <c r="AX36">
+      <c r="BA36">
         <v>0.86500287056000003</v>
       </c>
-      <c r="AY36">
+      <c r="BB36">
         <v>0.36387771367999999</v>
       </c>
-      <c r="AZ36">
+      <c r="BC36">
         <v>7.9154474659999998E-3</v>
       </c>
-      <c r="BA36">
+      <c r="BD36">
         <v>5.3703733719999997E-3</v>
       </c>
-      <c r="BC36" t="s">
+      <c r="BF36" t="s">
         <v>301</v>
       </c>
-      <c r="BF36">
+      <c r="BI36">
         <f t="shared" si="1"/>
         <v>5.3703733719999997E-3</v>
       </c>
-      <c r="BG36">
+      <c r="BJ36">
         <v>5.3703733719999997E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>0.68990700000000005</v>
       </c>
@@ -43146,54 +43265,54 @@
       <c r="AL37">
         <v>0.89270400000000005</v>
       </c>
-      <c r="AO37">
+      <c r="AQ37">
         <v>0.87173900000000004</v>
       </c>
-      <c r="AP37">
+      <c r="AR37">
         <v>0.82907600000000004</v>
       </c>
-      <c r="AQ37">
+      <c r="AS37">
         <v>0.83790900000000001</v>
       </c>
-      <c r="AR37">
+      <c r="AT37">
         <v>0.816052</v>
       </c>
-      <c r="AS37">
+      <c r="AU37">
         <v>0.36186600000000002</v>
       </c>
-      <c r="AT37">
+      <c r="AV37">
         <v>0.29050999999999999</v>
       </c>
-      <c r="AU37">
+      <c r="AW37">
         <v>0.31133100000000002</v>
       </c>
-      <c r="AV37">
+      <c r="AX37">
         <v>0.274677</v>
       </c>
-      <c r="AX37">
+      <c r="BA37">
         <v>0.84643757343299997</v>
       </c>
-      <c r="AY37">
+      <c r="BB37">
         <v>0.34429210424399997</v>
       </c>
-      <c r="AZ37">
+      <c r="BC37">
         <v>7.1761924769999999E-3</v>
       </c>
-      <c r="BA37">
+      <c r="BD37">
         <v>4.9556843010000002E-3</v>
       </c>
-      <c r="BC37" t="s">
+      <c r="BF37" t="s">
         <v>302</v>
       </c>
-      <c r="BF37">
+      <c r="BI37">
         <f t="shared" si="1"/>
         <v>4.9556843010000002E-3</v>
       </c>
-      <c r="BG37">
+      <c r="BJ37">
         <v>4.9556843010000002E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>0.67670699999999995</v>
       </c>
@@ -43269,54 +43388,54 @@
       <c r="AL38">
         <v>0.87325900000000001</v>
       </c>
-      <c r="AO38">
+      <c r="AQ38">
         <v>0.85272400000000004</v>
       </c>
-      <c r="AP38">
+      <c r="AR38">
         <v>0.81277999999999995</v>
       </c>
-      <c r="AQ38">
+      <c r="AS38">
         <v>0.81940500000000005</v>
       </c>
-      <c r="AR38">
+      <c r="AT38">
         <v>0.79624099999999998</v>
       </c>
-      <c r="AS38">
+      <c r="AU38">
         <v>0.34285199999999999</v>
       </c>
-      <c r="AT38">
+      <c r="AV38">
         <v>0.27009100000000003</v>
       </c>
-      <c r="AU38">
+      <c r="AW38">
         <v>0.29350799999999999</v>
       </c>
-      <c r="AV38">
+      <c r="AX38">
         <v>0.26207900000000001</v>
       </c>
-      <c r="AX38">
+      <c r="BA38">
         <v>0.82783460617100002</v>
       </c>
-      <c r="AY38">
+      <c r="BB38">
         <v>0.325260996819</v>
       </c>
-      <c r="AZ38">
+      <c r="BC38">
         <v>6.5247607419999997E-3</v>
       </c>
-      <c r="BA38">
+      <c r="BD38">
         <v>4.6003120949999997E-3</v>
       </c>
-      <c r="BC38" t="s">
+      <c r="BF38" t="s">
         <v>303</v>
       </c>
-      <c r="BF38">
+      <c r="BI38">
         <f t="shared" si="1"/>
         <v>4.6003120949999997E-3</v>
       </c>
-      <c r="BG38">
+      <c r="BJ38">
         <v>4.6003120949999997E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>0.66381000000000001</v>
       </c>
@@ -43392,54 +43511,54 @@
       <c r="AL39">
         <v>0.84859799999999996</v>
       </c>
-      <c r="AO39">
+      <c r="AQ39">
         <v>0.83347000000000004</v>
       </c>
-      <c r="AP39">
+      <c r="AR39">
         <v>0.78858399999999995</v>
       </c>
-      <c r="AQ39">
+      <c r="AS39">
         <v>0.80076999999999998</v>
       </c>
-      <c r="AR39">
+      <c r="AT39">
         <v>0.77944100000000005</v>
       </c>
-      <c r="AS39">
+      <c r="AU39">
         <v>0.32475799999999999</v>
       </c>
-      <c r="AT39">
+      <c r="AV39">
         <v>0.25429499999999999</v>
       </c>
-      <c r="AU39">
+      <c r="AW39">
         <v>0.27592299999999997</v>
       </c>
-      <c r="AV39">
+      <c r="AX39">
         <v>0.23995</v>
       </c>
-      <c r="AX39">
+      <c r="BA39">
         <v>0.80927288532300001</v>
       </c>
-      <c r="AY39">
+      <c r="BB39">
         <v>0.30714550614399999</v>
       </c>
-      <c r="AZ39">
+      <c r="BC39">
         <v>6.0531315389999998E-3</v>
       </c>
-      <c r="BA39">
+      <c r="BD39">
         <v>4.2913667859999999E-3</v>
       </c>
-      <c r="BC39" t="s">
+      <c r="BF39" t="s">
         <v>304</v>
       </c>
-      <c r="BF39">
+      <c r="BI39">
         <f t="shared" si="1"/>
         <v>4.2913667859999999E-3</v>
       </c>
-      <c r="BG39">
+      <c r="BJ39">
         <v>4.2913667859999999E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>0.65122400000000003</v>
       </c>
@@ -43515,54 +43634,54 @@
       <c r="AL40">
         <v>0.83144300000000004</v>
       </c>
-      <c r="AO40">
+      <c r="AQ40">
         <v>0.81489199999999995</v>
       </c>
-      <c r="AP40">
+      <c r="AR40">
         <v>0.77000400000000002</v>
       </c>
-      <c r="AQ40">
+      <c r="AS40">
         <v>0.78240799999999999</v>
       </c>
-      <c r="AR40">
+      <c r="AT40">
         <v>0.77551099999999995</v>
       </c>
-      <c r="AS40">
+      <c r="AU40">
         <v>0.30723400000000001</v>
       </c>
-      <c r="AT40">
+      <c r="AV40">
         <v>0.23672299999999999</v>
       </c>
-      <c r="AU40">
+      <c r="AW40">
         <v>0.25929400000000002</v>
       </c>
-      <c r="AV40">
+      <c r="AX40">
         <v>0.226823</v>
       </c>
-      <c r="AX40">
+      <c r="BA40">
         <v>0.79099929332700003</v>
       </c>
-      <c r="AY40">
+      <c r="BB40">
         <v>0.29000562429400001</v>
       </c>
-      <c r="AZ40">
+      <c r="BC40">
         <v>5.5801928969999998E-3</v>
       </c>
-      <c r="BA40">
+      <c r="BD40">
         <v>4.0450561789999997E-3</v>
       </c>
-      <c r="BC40" t="s">
+      <c r="BF40" t="s">
         <v>305</v>
       </c>
-      <c r="BF40">
+      <c r="BI40">
         <f t="shared" si="1"/>
         <v>4.0450561789999997E-3</v>
       </c>
-      <c r="BG40">
+      <c r="BJ40">
         <v>4.0450561789999997E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>0.63893800000000001</v>
       </c>
@@ -43638,54 +43757,54 @@
       <c r="AL41">
         <v>0.82220000000000004</v>
       </c>
-      <c r="AO41">
+      <c r="AQ41">
         <v>0.796157</v>
       </c>
-      <c r="AP41">
+      <c r="AR41">
         <v>0.75073100000000004</v>
       </c>
-      <c r="AQ41">
+      <c r="AS41">
         <v>0.76393200000000006</v>
       </c>
-      <c r="AR41">
+      <c r="AT41">
         <v>0.78130900000000003</v>
       </c>
-      <c r="AS41">
+      <c r="AU41">
         <v>0.29066900000000001</v>
       </c>
-      <c r="AT41">
+      <c r="AV41">
         <v>0.222305</v>
       </c>
-      <c r="AU41">
+      <c r="AW41">
         <v>0.243871</v>
       </c>
-      <c r="AV41">
+      <c r="AX41">
         <v>0.20804700000000001</v>
       </c>
-      <c r="AX41">
+      <c r="BA41">
         <v>0.77257001400000003</v>
       </c>
-      <c r="AY41">
+      <c r="BB41">
         <v>0.27346304058999998</v>
       </c>
-      <c r="AZ41">
+      <c r="BC41">
         <v>5.2239997310000001E-3</v>
       </c>
-      <c r="BA41">
+      <c r="BD41">
         <v>3.8619774860000002E-3</v>
       </c>
-      <c r="BC41" t="s">
+      <c r="BF41" t="s">
         <v>306</v>
       </c>
-      <c r="BF41">
+      <c r="BI41">
         <f t="shared" si="1"/>
         <v>3.8619774860000002E-3</v>
       </c>
-      <c r="BG41">
+      <c r="BJ41">
         <v>3.8619774860000002E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>0.62694099999999997</v>
       </c>
@@ -43761,54 +43880,54 @@
       <c r="AL42">
         <v>0.79775499999999999</v>
       </c>
-      <c r="AO42">
+      <c r="AQ42">
         <v>0.77763400000000005</v>
       </c>
-      <c r="AP42">
+      <c r="AR42">
         <v>0.73427399999999998</v>
       </c>
-      <c r="AQ42">
+      <c r="AS42">
         <v>0.74573999999999996</v>
       </c>
-      <c r="AR42">
+      <c r="AT42">
         <v>0.75833899999999999</v>
       </c>
-      <c r="AS42">
+      <c r="AU42">
         <v>0.27509600000000001</v>
       </c>
-      <c r="AT42">
+      <c r="AV42">
         <v>0.20697099999999999</v>
       </c>
-      <c r="AU42">
+      <c r="AW42">
         <v>0.22869500000000001</v>
       </c>
-      <c r="AV42">
+      <c r="AX42">
         <v>0.19750100000000001</v>
       </c>
-      <c r="AX42">
+      <c r="BA42">
         <v>0.75441712140999995</v>
       </c>
-      <c r="AY42">
+      <c r="BB42">
         <v>0.25786080956500002</v>
       </c>
-      <c r="AZ42">
+      <c r="BC42">
         <v>4.8486641609999997E-3</v>
       </c>
-      <c r="BA42">
+      <c r="BD42">
         <v>3.7109190599999998E-3</v>
       </c>
-      <c r="BC42" t="s">
+      <c r="BF42" t="s">
         <v>307</v>
       </c>
-      <c r="BF42">
+      <c r="BI42">
         <f t="shared" si="1"/>
         <v>3.7109190599999998E-3</v>
       </c>
-      <c r="BG42">
+      <c r="BJ42">
         <v>3.7109190599999998E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>0.61525300000000005</v>
       </c>
@@ -43884,54 +44003,54 @@
       <c r="AL43">
         <v>0.77254</v>
       </c>
-      <c r="AO43">
+      <c r="AQ43">
         <v>0.75888500000000003</v>
       </c>
-      <c r="AP43">
+      <c r="AR43">
         <v>0.71677100000000005</v>
       </c>
-      <c r="AQ43">
+      <c r="AS43">
         <v>0.72737200000000002</v>
       </c>
-      <c r="AR43">
+      <c r="AT43">
         <v>0.74224000000000001</v>
       </c>
-      <c r="AS43">
+      <c r="AU43">
         <v>0.26006099999999999</v>
       </c>
-      <c r="AT43">
+      <c r="AV43">
         <v>0.19391800000000001</v>
       </c>
-      <c r="AU43">
+      <c r="AW43">
         <v>0.214674</v>
       </c>
-      <c r="AV43">
+      <c r="AX43">
         <v>0.18068200000000001</v>
       </c>
-      <c r="AX43">
+      <c r="BA43">
         <v>0.73603689670600003</v>
       </c>
-      <c r="AY43">
+      <c r="BB43">
         <v>0.24324452877</v>
       </c>
-      <c r="AZ43">
+      <c r="BC43">
         <v>4.5441538099999998E-3</v>
       </c>
-      <c r="BA43">
+      <c r="BD43">
         <v>3.5569528120000002E-3</v>
       </c>
-      <c r="BC43" t="s">
+      <c r="BF43" t="s">
         <v>308</v>
       </c>
-      <c r="BF43">
+      <c r="BI43">
         <f t="shared" si="1"/>
         <v>3.5569528120000002E-3</v>
       </c>
-      <c r="BG43">
+      <c r="BJ43">
         <v>3.5569528120000002E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>0.60390299999999997</v>
       </c>
@@ -44007,54 +44126,54 @@
       <c r="AL44">
         <v>0.74731300000000001</v>
       </c>
-      <c r="AO44">
+      <c r="AQ44">
         <v>0.73985699999999999</v>
       </c>
-      <c r="AP44">
+      <c r="AR44">
         <v>0.69990300000000005</v>
       </c>
-      <c r="AQ44">
+      <c r="AS44">
         <v>0.709206</v>
       </c>
-      <c r="AR44">
+      <c r="AT44">
         <v>0.71747700000000003</v>
       </c>
-      <c r="AS44">
+      <c r="AU44">
         <v>0.24562999999999999</v>
       </c>
-      <c r="AT44">
+      <c r="AV44">
         <v>0.180452</v>
       </c>
-      <c r="AU44">
+      <c r="AW44">
         <v>0.20145299999999999</v>
       </c>
-      <c r="AV44">
+      <c r="AX44">
         <v>0.170597</v>
       </c>
-      <c r="AX44">
+      <c r="BA44">
         <v>0.71764606237399997</v>
       </c>
-      <c r="AY44">
+      <c r="BB44">
         <v>0.22888042032700001</v>
       </c>
-      <c r="AZ44">
+      <c r="BC44">
         <v>4.236876033E-3</v>
       </c>
-      <c r="BA44">
+      <c r="BD44">
         <v>3.3890833149999998E-3</v>
       </c>
-      <c r="BC44" t="s">
+      <c r="BF44" t="s">
         <v>309</v>
       </c>
-      <c r="BF44">
+      <c r="BI44">
         <f t="shared" si="1"/>
         <v>3.3890833149999998E-3</v>
       </c>
-      <c r="BG44">
+      <c r="BJ44">
         <v>3.3890833149999998E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>0.59286300000000003</v>
       </c>
@@ -44130,54 +44249,54 @@
       <c r="AL45">
         <v>0.72789300000000001</v>
       </c>
-      <c r="AO45">
+      <c r="AQ45">
         <v>0.72097699999999998</v>
       </c>
-      <c r="AP45">
+      <c r="AR45">
         <v>0.68355299999999997</v>
       </c>
-      <c r="AQ45">
+      <c r="AS45">
         <v>0.69069000000000003</v>
       </c>
-      <c r="AR45">
+      <c r="AT45">
         <v>0.69740199999999997</v>
       </c>
-      <c r="AS45">
+      <c r="AU45">
         <v>0.23218</v>
       </c>
-      <c r="AT45">
+      <c r="AV45">
         <v>0.16878299999999999</v>
       </c>
-      <c r="AU45">
+      <c r="AW45">
         <v>0.18871599999999999</v>
       </c>
-      <c r="AV45">
+      <c r="AX45">
         <v>0.15679499999999999</v>
       </c>
-      <c r="AX45">
+      <c r="BA45">
         <v>0.69919890165300003</v>
       </c>
-      <c r="AY45">
+      <c r="BB45">
         <v>0.21545492112600001</v>
       </c>
-      <c r="AZ45">
+      <c r="BC45">
         <v>4.0185102260000003E-3</v>
       </c>
-      <c r="BA45">
+      <c r="BD45">
         <v>3.2192240469999999E-3</v>
       </c>
-      <c r="BC45" t="s">
+      <c r="BF45" t="s">
         <v>310</v>
       </c>
-      <c r="BF45">
+      <c r="BI45">
         <f t="shared" si="1"/>
         <v>3.2192240469999999E-3</v>
       </c>
-      <c r="BG45">
+      <c r="BJ45">
         <v>3.2192240469999999E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>0.58213899999999996</v>
       </c>
@@ -44253,54 +44372,54 @@
       <c r="AL46">
         <v>0.70703199999999999</v>
       </c>
-      <c r="AO46">
+      <c r="AQ46">
         <v>0.70183600000000002</v>
       </c>
-      <c r="AP46">
+      <c r="AR46">
         <v>0.67227899999999996</v>
       </c>
-      <c r="AQ46">
+      <c r="AS46">
         <v>0.67230999999999996</v>
       </c>
-      <c r="AR46">
+      <c r="AT46">
         <v>0.68480300000000005</v>
       </c>
-      <c r="AS46">
+      <c r="AU46">
         <v>0.21940899999999999</v>
       </c>
-      <c r="AT46">
+      <c r="AV46">
         <v>0.15711700000000001</v>
       </c>
-      <c r="AU46">
+      <c r="AW46">
         <v>0.17706</v>
       </c>
-      <c r="AV46">
+      <c r="AX46">
         <v>0.14740600000000001</v>
       </c>
-      <c r="AX46">
+      <c r="BA46">
         <v>0.680690348148</v>
       </c>
-      <c r="AY46">
+      <c r="BB46">
         <v>0.20306199789000001</v>
       </c>
-      <c r="AZ46">
+      <c r="BC46">
         <v>3.8139736280000001E-3</v>
       </c>
-      <c r="BA46">
+      <c r="BD46">
         <v>3.061146941E-3</v>
       </c>
-      <c r="BC46" t="s">
+      <c r="BF46" t="s">
         <v>311</v>
       </c>
-      <c r="BF46">
+      <c r="BI46">
         <f t="shared" si="1"/>
         <v>3.061146941E-3</v>
       </c>
-      <c r="BG46">
+      <c r="BJ46">
         <v>3.061146941E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>0.57172299999999998</v>
       </c>
@@ -44376,54 +44495,54 @@
       <c r="AL47">
         <v>0.68652299999999999</v>
       </c>
-      <c r="AO47">
+      <c r="AQ47">
         <v>0.68273099999999998</v>
       </c>
-      <c r="AP47">
+      <c r="AR47">
         <v>0.66068000000000005</v>
       </c>
-      <c r="AQ47">
+      <c r="AS47">
         <v>0.65368300000000001</v>
       </c>
-      <c r="AR47">
+      <c r="AT47">
         <v>0.67068499999999998</v>
       </c>
-      <c r="AS47">
+      <c r="AU47">
         <v>0.207012</v>
       </c>
-      <c r="AT47">
+      <c r="AV47">
         <v>0.146563</v>
       </c>
-      <c r="AU47">
+      <c r="AW47">
         <v>0.16581299999999999</v>
       </c>
-      <c r="AV47">
+      <c r="AX47">
         <v>0.135855</v>
       </c>
-      <c r="AX47">
+      <c r="BA47">
         <v>0.66220086813000001</v>
       </c>
-      <c r="AY47">
+      <c r="BB47">
         <v>0.190929144621</v>
       </c>
-      <c r="AZ47">
+      <c r="BC47">
         <v>3.6453236830000001E-3</v>
       </c>
-      <c r="BA47">
+      <c r="BD47">
         <v>2.9162953139999998E-3</v>
       </c>
-      <c r="BC47" t="s">
+      <c r="BF47" t="s">
         <v>312</v>
       </c>
-      <c r="BF47">
+      <c r="BI47">
         <f t="shared" si="1"/>
         <v>2.9162953139999998E-3</v>
       </c>
-      <c r="BG47">
+      <c r="BJ47">
         <v>2.9162953139999998E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>0.561608</v>
       </c>
@@ -44499,54 +44618,54 @@
       <c r="AL48">
         <v>0.66472200000000004</v>
       </c>
-      <c r="AO48">
+      <c r="AQ48">
         <v>0.66365700000000005</v>
       </c>
-      <c r="AP48">
+      <c r="AR48">
         <v>0.64577399999999996</v>
       </c>
-      <c r="AQ48">
+      <c r="AS48">
         <v>0.63511700000000004</v>
       </c>
-      <c r="AR48">
+      <c r="AT48">
         <v>0.66042999999999996</v>
       </c>
-      <c r="AS48">
+      <c r="AU48">
         <v>0.19536300000000001</v>
       </c>
-      <c r="AT48">
+      <c r="AV48">
         <v>0.13642299999999999</v>
       </c>
-      <c r="AU48">
+      <c r="AW48">
         <v>0.15536900000000001</v>
       </c>
-      <c r="AV48">
+      <c r="AX48">
         <v>0.12653400000000001</v>
       </c>
-      <c r="AX48">
+      <c r="BA48">
         <v>0.64357960224199995</v>
       </c>
-      <c r="AY48">
+      <c r="BB48">
         <v>0.179450795054</v>
       </c>
-      <c r="AZ48">
+      <c r="BC48">
         <v>3.4662315159999998E-3</v>
       </c>
-      <c r="BA48">
+      <c r="BD48">
         <v>2.7813005729999999E-3</v>
       </c>
-      <c r="BC48" t="s">
+      <c r="BF48" t="s">
         <v>313</v>
       </c>
-      <c r="BF48">
+      <c r="BI48">
         <f t="shared" si="1"/>
         <v>2.7813005729999999E-3</v>
       </c>
-      <c r="BG48">
+      <c r="BJ48">
         <v>2.7813005729999999E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>0.55179800000000001</v>
       </c>
@@ -44622,54 +44741,54 @@
       <c r="AL49">
         <v>0.64574299999999996</v>
       </c>
-      <c r="AO49">
+      <c r="AQ49">
         <v>0.64426099999999997</v>
       </c>
-      <c r="AP49">
+      <c r="AR49">
         <v>0.63045099999999998</v>
       </c>
-      <c r="AQ49">
+      <c r="AS49">
         <v>0.61652899999999999</v>
       </c>
-      <c r="AR49">
+      <c r="AT49">
         <v>0.66669299999999998</v>
       </c>
-      <c r="AS49">
+      <c r="AU49">
         <v>0.18452099999999999</v>
       </c>
-      <c r="AT49">
+      <c r="AV49">
         <v>0.127141</v>
       </c>
-      <c r="AU49">
+      <c r="AW49">
         <v>0.14560999999999999</v>
       </c>
-      <c r="AV49">
+      <c r="AX49">
         <v>0.11791600000000001</v>
       </c>
-      <c r="AX49">
+      <c r="BA49">
         <v>0.62478119134900001</v>
       </c>
-      <c r="AY49">
+      <c r="BB49">
         <v>0.168945401907</v>
       </c>
-      <c r="AZ49">
+      <c r="BC49">
         <v>3.3093665259999999E-3</v>
       </c>
-      <c r="BA49">
+      <c r="BD49">
         <v>2.6611716020000001E-3</v>
       </c>
-      <c r="BC49" t="s">
+      <c r="BF49" t="s">
         <v>314</v>
       </c>
-      <c r="BF49">
+      <c r="BI49">
         <f t="shared" si="1"/>
         <v>2.6611716020000001E-3</v>
       </c>
-      <c r="BG49">
+      <c r="BJ49">
         <v>2.6611716020000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>0.54226200000000002</v>
       </c>
@@ -44745,54 +44864,54 @@
       <c r="AL50">
         <v>0.62845200000000001</v>
       </c>
-      <c r="AO50">
+      <c r="AQ50">
         <v>0.62518099999999999</v>
       </c>
-      <c r="AP50">
+      <c r="AR50">
         <v>0.61740499999999998</v>
       </c>
-      <c r="AQ50">
+      <c r="AS50">
         <v>0.59781600000000001</v>
       </c>
-      <c r="AR50">
+      <c r="AT50">
         <v>0.70445599999999997</v>
       </c>
-      <c r="AS50">
+      <c r="AU50">
         <v>0.17408499999999999</v>
       </c>
-      <c r="AT50">
+      <c r="AV50">
         <v>0.11829000000000001</v>
       </c>
-      <c r="AU50">
+      <c r="AW50">
         <v>0.13625999999999999</v>
       </c>
-      <c r="AV50">
+      <c r="AX50">
         <v>0.10846799999999999</v>
       </c>
-      <c r="AX50">
+      <c r="BA50">
         <v>0.60627698898299998</v>
       </c>
-      <c r="AY50">
+      <c r="BB50">
         <v>0.158782571554</v>
       </c>
-      <c r="AZ50">
+      <c r="BC50">
         <v>3.153094091E-3</v>
       </c>
-      <c r="BA50">
+      <c r="BD50">
         <v>2.5633692280000002E-3</v>
       </c>
-      <c r="BC50" t="s">
+      <c r="BF50" t="s">
         <v>315</v>
       </c>
-      <c r="BF50">
+      <c r="BI50">
         <f t="shared" si="1"/>
         <v>2.5633692280000002E-3</v>
       </c>
-      <c r="BG50">
+      <c r="BJ50">
         <v>2.5633692280000002E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>0.533003</v>
       </c>
@@ -44868,54 +44987,54 @@
       <c r="AL51">
         <v>0.609819</v>
       </c>
-      <c r="AO51">
+      <c r="AQ51">
         <v>0.60573100000000002</v>
       </c>
-      <c r="AP51">
+      <c r="AR51">
         <v>0.60600500000000002</v>
       </c>
-      <c r="AQ51">
+      <c r="AS51">
         <v>0.57921</v>
       </c>
-      <c r="AR51">
+      <c r="AT51">
         <v>0.67051000000000005</v>
       </c>
-      <c r="AS51">
+      <c r="AU51">
         <v>0.16411800000000001</v>
       </c>
-      <c r="AT51">
+      <c r="AV51">
         <v>0.110099</v>
       </c>
-      <c r="AU51">
+      <c r="AW51">
         <v>0.127746</v>
       </c>
-      <c r="AV51">
+      <c r="AX51">
         <v>0.10177600000000001</v>
       </c>
-      <c r="AX51">
+      <c r="BA51">
         <v>0.58744102716400004</v>
       </c>
-      <c r="AY51">
+      <c r="BB51">
         <v>0.14920027554000001</v>
       </c>
-      <c r="AZ51">
+      <c r="BC51">
         <v>3.009040141E-3</v>
       </c>
-      <c r="BA51">
+      <c r="BD51">
         <v>2.4827108719999999E-3</v>
       </c>
-      <c r="BC51" t="s">
+      <c r="BF51" t="s">
         <v>316</v>
       </c>
-      <c r="BF51">
+      <c r="BI51">
         <f t="shared" si="1"/>
         <v>2.4827108719999999E-3</v>
       </c>
-      <c r="BG51">
+      <c r="BJ51">
         <v>2.4827108719999999E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>0.524003</v>
       </c>
@@ -44991,54 +45110,54 @@
       <c r="AL52">
         <v>0.59187999999999996</v>
       </c>
-      <c r="AO52">
+      <c r="AQ52">
         <v>0.58668399999999998</v>
       </c>
-      <c r="AP52">
+      <c r="AR52">
         <v>0.59249600000000002</v>
       </c>
-      <c r="AQ52">
+      <c r="AS52">
         <v>0.56043200000000004</v>
       </c>
-      <c r="AR52">
+      <c r="AT52">
         <v>0.63653599999999999</v>
       </c>
-      <c r="AS52">
+      <c r="AU52">
         <v>0.15485299999999999</v>
       </c>
-      <c r="AT52">
+      <c r="AV52">
         <v>0.102474</v>
       </c>
-      <c r="AU52">
+      <c r="AW52">
         <v>0.119521</v>
       </c>
-      <c r="AV52">
+      <c r="AX52">
         <v>9.3312000000000006E-2</v>
       </c>
-      <c r="AX52">
+      <c r="BA52">
         <v>0.56894284486799995</v>
       </c>
-      <c r="AY52">
+      <c r="BB52">
         <v>0.140281528234</v>
       </c>
-      <c r="AZ52">
+      <c r="BC52">
         <v>2.879705047E-3</v>
       </c>
-      <c r="BA52">
+      <c r="BD52">
         <v>2.4057552219999999E-3</v>
       </c>
-      <c r="BC52" t="s">
+      <c r="BF52" t="s">
         <v>317</v>
       </c>
-      <c r="BF52">
+      <c r="BI52">
         <f t="shared" si="1"/>
         <v>2.4057552219999999E-3</v>
       </c>
-      <c r="BG52">
+      <c r="BJ52">
         <v>2.4057552219999999E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>0.51531199999999999</v>
       </c>
@@ -45114,54 +45233,54 @@
       <c r="AL53">
         <v>0.57800099999999999</v>
       </c>
-      <c r="AO53">
+      <c r="AQ53">
         <v>0.56754800000000005</v>
       </c>
-      <c r="AP53">
+      <c r="AR53">
         <v>0.57236799999999999</v>
       </c>
-      <c r="AQ53">
+      <c r="AS53">
         <v>0.54198100000000005</v>
       </c>
-      <c r="AR53">
+      <c r="AT53">
         <v>0.62512199999999996</v>
       </c>
-      <c r="AS53">
+      <c r="AU53">
         <v>0.14607300000000001</v>
       </c>
-      <c r="AT53">
+      <c r="AV53">
         <v>9.5197000000000004E-2</v>
       </c>
-      <c r="AU53">
+      <c r="AW53">
         <v>0.11197500000000001</v>
       </c>
-      <c r="AV53">
+      <c r="AX53">
         <v>8.7345999999999993E-2</v>
       </c>
-      <c r="AX53">
+      <c r="BA53">
         <v>0.55047005415000005</v>
       </c>
-      <c r="AY53">
+      <c r="BB53">
         <v>0.131860166788</v>
       </c>
-      <c r="AZ53">
+      <c r="BC53">
         <v>2.764214994E-3</v>
       </c>
-      <c r="BA53">
+      <c r="BD53">
         <v>2.3284032939999998E-3</v>
       </c>
-      <c r="BC53" t="s">
+      <c r="BF53" t="s">
         <v>318</v>
       </c>
-      <c r="BF53">
+      <c r="BI53">
         <f t="shared" si="1"/>
         <v>2.3284032939999998E-3</v>
       </c>
-      <c r="BG53">
+      <c r="BJ53">
         <v>2.3284032939999998E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>0.50689600000000001</v>
       </c>
@@ -45237,54 +45356,54 @@
       <c r="AL54">
         <v>0.57173700000000005</v>
       </c>
-      <c r="AO54">
+      <c r="AQ54">
         <v>0.54864000000000002</v>
       </c>
-      <c r="AP54">
+      <c r="AR54">
         <v>0.55632899999999996</v>
       </c>
-      <c r="AQ54">
+      <c r="AS54">
         <v>0.52366599999999996</v>
       </c>
-      <c r="AR54">
+      <c r="AT54">
         <v>0.60495600000000005</v>
       </c>
-      <c r="AS54">
+      <c r="AU54">
         <v>0.137657</v>
       </c>
-      <c r="AT54">
+      <c r="AV54">
         <v>8.8624999999999995E-2</v>
       </c>
-      <c r="AU54">
+      <c r="AW54">
         <v>0.10484</v>
       </c>
-      <c r="AV54">
+      <c r="AX54">
         <v>8.0522999999999997E-2</v>
       </c>
-      <c r="AX54">
+      <c r="BA54">
         <v>0.53213030099900005</v>
       </c>
-      <c r="AY54">
+      <c r="BB54">
         <v>0.123946860433</v>
       </c>
-      <c r="AZ54">
+      <c r="BC54">
         <v>2.6655867700000001E-3</v>
       </c>
-      <c r="BA54">
+      <c r="BD54">
         <v>2.2569769059999998E-3</v>
       </c>
-      <c r="BC54" t="s">
+      <c r="BF54" t="s">
         <v>319</v>
       </c>
-      <c r="BF54">
+      <c r="BI54">
         <f t="shared" si="1"/>
         <v>2.2569769059999998E-3</v>
       </c>
-      <c r="BG54">
+      <c r="BJ54">
         <v>2.2569769059999998E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>0.498695</v>
       </c>
@@ -45360,54 +45479,54 @@
       <c r="AL55">
         <v>0.56917300000000004</v>
       </c>
-      <c r="AO55">
+      <c r="AQ55">
         <v>0.52980300000000002</v>
       </c>
-      <c r="AP55">
+      <c r="AR55">
         <v>0.54123299999999996</v>
       </c>
-      <c r="AQ55">
+      <c r="AS55">
         <v>0.505301</v>
       </c>
-      <c r="AR55">
+      <c r="AT55">
         <v>0.58785699999999996</v>
       </c>
-      <c r="AS55">
+      <c r="AU55">
         <v>0.12978300000000001</v>
       </c>
-      <c r="AT55">
+      <c r="AV55">
         <v>8.2253000000000007E-2</v>
       </c>
-      <c r="AU55">
+      <c r="AW55">
         <v>9.8119999999999999E-2</v>
       </c>
-      <c r="AV55">
+      <c r="AX55">
         <v>7.4635999999999994E-2</v>
       </c>
-      <c r="AX55">
+      <c r="BA55">
         <v>0.51405084133099999</v>
       </c>
-      <c r="AY55">
+      <c r="BB55">
         <v>0.11639226228000001</v>
       </c>
-      <c r="AZ55">
+      <c r="BC55">
         <v>2.5616660709999999E-3</v>
       </c>
-      <c r="BA55">
+      <c r="BD55">
         <v>2.194293309E-3</v>
       </c>
-      <c r="BC55" t="s">
+      <c r="BF55" t="s">
         <v>320</v>
       </c>
-      <c r="BF55">
+      <c r="BI55">
         <f t="shared" si="1"/>
         <v>2.194293309E-3</v>
       </c>
-      <c r="BG55">
+      <c r="BJ55">
         <v>2.194293309E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>0.49074099999999998</v>
       </c>
@@ -45483,54 +45602,54 @@
       <c r="AL56">
         <v>0.55869599999999997</v>
       </c>
-      <c r="AO56">
+      <c r="AQ56">
         <v>0.51128600000000002</v>
       </c>
-      <c r="AP56">
+      <c r="AR56">
         <v>0.53359599999999996</v>
       </c>
-      <c r="AQ56">
+      <c r="AS56">
         <v>0.48758299999999999</v>
       </c>
-      <c r="AR56">
+      <c r="AT56">
         <v>0.57567500000000005</v>
       </c>
-      <c r="AS56">
+      <c r="AU56">
         <v>0.12238599999999999</v>
       </c>
-      <c r="AT56">
+      <c r="AV56">
         <v>7.6566999999999996E-2</v>
       </c>
-      <c r="AU56">
+      <c r="AW56">
         <v>9.1902999999999999E-2</v>
       </c>
-      <c r="AV56">
+      <c r="AX56">
         <v>6.9434999999999997E-2</v>
       </c>
-      <c r="AX56">
+      <c r="BA56">
         <v>0.495969563723</v>
       </c>
-      <c r="AY56">
+      <c r="BB56">
         <v>0.109429381788</v>
       </c>
-      <c r="AZ56">
+      <c r="BC56">
         <v>2.4775215419999999E-3</v>
       </c>
-      <c r="BA56">
+      <c r="BD56">
         <v>2.136641182E-3</v>
       </c>
-      <c r="BC56" t="s">
+      <c r="BF56" t="s">
         <v>321</v>
       </c>
-      <c r="BF56">
+      <c r="BI56">
         <f t="shared" si="1"/>
         <v>2.136641182E-3</v>
       </c>
-      <c r="BG56">
+      <c r="BJ56">
         <v>2.136641182E-3</v>
       </c>
     </row>
-    <row r="57" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>0.483043</v>
       </c>
@@ -45606,54 +45725,54 @@
       <c r="AL57">
         <v>0.53642100000000004</v>
       </c>
-      <c r="AO57">
+      <c r="AQ57">
         <v>0.49289300000000003</v>
       </c>
-      <c r="AP57">
+      <c r="AR57">
         <v>0.52909200000000001</v>
       </c>
-      <c r="AQ57">
+      <c r="AS57">
         <v>0.47054499999999999</v>
       </c>
-      <c r="AR57">
+      <c r="AT57">
         <v>0.57422600000000001</v>
       </c>
-      <c r="AS57">
+      <c r="AU57">
         <v>0.115324</v>
       </c>
-      <c r="AT57">
+      <c r="AV57">
         <v>7.0981000000000002E-2</v>
       </c>
-      <c r="AU57">
+      <c r="AW57">
         <v>8.5972000000000007E-2</v>
       </c>
-      <c r="AV57">
+      <c r="AX57">
         <v>6.3865000000000005E-2</v>
       </c>
-      <c r="AX57">
+      <c r="BA57">
         <v>0.47823593020400001</v>
       </c>
-      <c r="AY57">
+      <c r="BB57">
         <v>0.102841347456</v>
       </c>
-      <c r="AZ57">
+      <c r="BC57">
         <v>2.388784895E-3</v>
       </c>
-      <c r="BA57">
+      <c r="BD57">
         <v>2.0831925790000001E-3</v>
       </c>
-      <c r="BC57" t="s">
+      <c r="BF57" t="s">
         <v>322</v>
       </c>
-      <c r="BF57">
+      <c r="BI57">
         <f t="shared" si="1"/>
         <v>2.0831925790000001E-3</v>
       </c>
-      <c r="BG57">
+      <c r="BJ57">
         <v>2.0831925790000001E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>0.47560999999999998</v>
       </c>
@@ -45729,54 +45848,54 @@
       <c r="AL58">
         <v>0.52831399999999995</v>
       </c>
-      <c r="AO58">
+      <c r="AQ58">
         <v>0.47455599999999998</v>
       </c>
-      <c r="AP58">
+      <c r="AR58">
         <v>0.52191399999999999</v>
       </c>
-      <c r="AQ58">
+      <c r="AS58">
         <v>0.454123</v>
       </c>
-      <c r="AR58">
+      <c r="AT58">
         <v>0.58446200000000004</v>
       </c>
-      <c r="AS58">
+      <c r="AU58">
         <v>0.108681</v>
       </c>
-      <c r="AT58">
+      <c r="AV58">
         <v>6.6077999999999998E-2</v>
       </c>
-      <c r="AU58">
+      <c r="AW58">
         <v>8.0528000000000002E-2</v>
       </c>
-      <c r="AV58">
+      <c r="AX58">
         <v>5.9645999999999998E-2</v>
       </c>
-      <c r="AX58">
+      <c r="BA58">
         <v>0.46132159233100001</v>
       </c>
-      <c r="AY58">
+      <c r="BB58">
         <v>9.6540004015E-2</v>
       </c>
-      <c r="AZ58">
+      <c r="BC58">
         <v>2.314530546E-3</v>
       </c>
-      <c r="BA58">
+      <c r="BD58">
         <v>2.0379978229999999E-3</v>
       </c>
-      <c r="BC58" t="s">
+      <c r="BF58" t="s">
         <v>323</v>
       </c>
-      <c r="BF58">
+      <c r="BI58">
         <f t="shared" si="1"/>
         <v>2.0379978229999999E-3</v>
       </c>
-      <c r="BG58">
+      <c r="BJ58">
         <v>2.0379978229999999E-3</v>
       </c>
     </row>
-    <row r="59" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>0.468393</v>
       </c>
@@ -45852,54 +45971,54 @@
       <c r="AL59">
         <v>0.51448199999999999</v>
       </c>
-      <c r="AO59">
+      <c r="AQ59">
         <v>0.45674500000000001</v>
       </c>
-      <c r="AP59">
+      <c r="AR59">
         <v>0.51258700000000001</v>
       </c>
-      <c r="AQ59">
+      <c r="AS59">
         <v>0.43823299999999998</v>
       </c>
-      <c r="AR59">
+      <c r="AT59">
         <v>0.57234799999999997</v>
       </c>
-      <c r="AS59">
+      <c r="AU59">
         <v>0.102478</v>
       </c>
-      <c r="AT59">
+      <c r="AV59">
         <v>6.1233000000000003E-2</v>
       </c>
-      <c r="AU59">
+      <c r="AW59">
         <v>7.5318999999999997E-2</v>
       </c>
-      <c r="AV59">
+      <c r="AX59">
         <v>5.4781000000000003E-2</v>
       </c>
-      <c r="AX59">
+      <c r="BA59">
         <v>0.445090830326</v>
       </c>
-      <c r="AY59">
+      <c r="BB59">
         <v>9.0763486921999995E-2</v>
       </c>
-      <c r="AZ59">
+      <c r="BC59">
         <v>2.2365793119999999E-3</v>
       </c>
-      <c r="BA59">
+      <c r="BD59">
         <v>2.002092544E-3</v>
       </c>
-      <c r="BC59" t="s">
+      <c r="BF59" t="s">
         <v>324</v>
       </c>
-      <c r="BF59">
+      <c r="BI59">
         <f t="shared" si="1"/>
         <v>2.002092544E-3</v>
       </c>
-      <c r="BG59">
+      <c r="BJ59">
         <v>2.002092544E-3</v>
       </c>
     </row>
-    <row r="60" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>0.46144299999999999</v>
       </c>
@@ -45975,54 +46094,54 @@
       <c r="AL60">
         <v>0.49982700000000002</v>
       </c>
-      <c r="AO60">
+      <c r="AQ60">
         <v>0.43937799999999999</v>
       </c>
-      <c r="AP60">
+      <c r="AR60">
         <v>0.49290600000000001</v>
       </c>
-      <c r="AQ60">
+      <c r="AS60">
         <v>0.42243199999999997</v>
       </c>
-      <c r="AR60">
+      <c r="AT60">
         <v>0.56355100000000002</v>
       </c>
-      <c r="AS60">
+      <c r="AU60">
         <v>9.6576999999999996E-2</v>
       </c>
-      <c r="AT60">
+      <c r="AV60">
         <v>5.7003999999999999E-2</v>
       </c>
-      <c r="AU60">
+      <c r="AW60">
         <v>7.0555000000000007E-2</v>
       </c>
-      <c r="AV60">
+      <c r="AX60">
         <v>5.1069999999999997E-2</v>
       </c>
-      <c r="AX60">
+      <c r="BA60">
         <v>0.42970442771900003</v>
       </c>
-      <c r="AY60">
+      <c r="BB60">
         <v>8.5247255861999993E-2</v>
       </c>
-      <c r="AZ60">
+      <c r="BC60">
         <v>2.1812925120000002E-3</v>
       </c>
-      <c r="BA60">
+      <c r="BD60">
         <v>1.97069766E-3</v>
       </c>
-      <c r="BC60" t="s">
+      <c r="BF60" t="s">
         <v>325</v>
       </c>
-      <c r="BF60">
+      <c r="BI60">
         <f t="shared" si="1"/>
         <v>1.97069766E-3</v>
       </c>
-      <c r="BG60">
+      <c r="BJ60">
         <v>1.97069766E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>0.45472800000000002</v>
       </c>
@@ -46098,54 +46217,54 @@
       <c r="AL61">
         <v>0.48334100000000002</v>
       </c>
-      <c r="AO61">
+      <c r="AQ61">
         <v>0.422404</v>
       </c>
-      <c r="AP61">
+      <c r="AR61">
         <v>0.47700300000000001</v>
       </c>
-      <c r="AQ61">
+      <c r="AS61">
         <v>0.40749299999999999</v>
       </c>
-      <c r="AR61">
+      <c r="AT61">
         <v>0.52972399999999997</v>
       </c>
-      <c r="AS61">
+      <c r="AU61">
         <v>9.0975E-2</v>
       </c>
-      <c r="AT61">
+      <c r="AV61">
         <v>5.2809000000000002E-2</v>
       </c>
-      <c r="AU61">
+      <c r="AW61">
         <v>6.5976000000000007E-2</v>
       </c>
-      <c r="AV61">
+      <c r="AX61">
         <v>4.7099000000000002E-2</v>
       </c>
-      <c r="AX61">
+      <c r="BA61">
         <v>0.41484349966</v>
       </c>
-      <c r="AY61">
+      <c r="BB61">
         <v>8.0080851911999998E-2</v>
       </c>
-      <c r="AZ61">
+      <c r="BC61">
         <v>2.1338271910000001E-3</v>
       </c>
-      <c r="BA61">
+      <c r="BD61">
         <v>1.9395353740000001E-3</v>
       </c>
-      <c r="BC61" t="s">
+      <c r="BF61" t="s">
         <v>326</v>
       </c>
-      <c r="BF61">
+      <c r="BI61">
         <f t="shared" si="1"/>
         <v>1.9395353740000001E-3</v>
       </c>
-      <c r="BG61">
+      <c r="BJ61">
         <v>1.9395353740000001E-3</v>
       </c>
     </row>
-    <row r="62" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>0.44808199999999998</v>
       </c>
@@ -46221,54 +46340,54 @@
       <c r="AL62">
         <v>0.46621899999999999</v>
       </c>
-      <c r="AO62">
+      <c r="AQ62">
         <v>0.40559800000000001</v>
       </c>
-      <c r="AP62">
+      <c r="AR62">
         <v>0.46698000000000001</v>
       </c>
-      <c r="AQ62">
+      <c r="AS62">
         <v>0.393146</v>
       </c>
-      <c r="AR62">
+      <c r="AT62">
         <v>0.51728099999999999</v>
       </c>
-      <c r="AS62">
+      <c r="AU62">
         <v>8.5750999999999994E-2</v>
       </c>
-      <c r="AT62">
+      <c r="AV62">
         <v>4.9119999999999997E-2</v>
       </c>
-      <c r="AU62">
+      <c r="AW62">
         <v>6.1800000000000001E-2</v>
       </c>
-      <c r="AV62">
+      <c r="AX62">
         <v>4.3610999999999997E-2</v>
       </c>
-      <c r="AX62">
+      <c r="BA62">
         <v>0.400544375181</v>
       </c>
-      <c r="AY62">
+      <c r="BB62">
         <v>7.5207807124000006E-2</v>
       </c>
-      <c r="AZ62">
+      <c r="BC62">
         <v>2.0897227809999999E-3</v>
       </c>
-      <c r="BA62">
+      <c r="BD62">
         <v>1.909143408E-3</v>
       </c>
-      <c r="BC62" t="s">
+      <c r="BF62" t="s">
         <v>327</v>
       </c>
-      <c r="BF62">
+      <c r="BI62">
         <f t="shared" si="1"/>
         <v>1.909143408E-3</v>
       </c>
-      <c r="BG62">
+      <c r="BJ62">
         <v>1.909143408E-3</v>
       </c>
     </row>
-    <row r="63" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>0.441803</v>
       </c>
@@ -46344,54 +46463,54 @@
       <c r="AL63">
         <v>0.45236100000000001</v>
       </c>
-      <c r="AO63">
+      <c r="AQ63">
         <v>0.39011299999999999</v>
       </c>
-      <c r="AP63">
+      <c r="AR63">
         <v>0.44743500000000003</v>
       </c>
-      <c r="AQ63">
+      <c r="AS63">
         <v>0.37830799999999998</v>
       </c>
-      <c r="AR63">
+      <c r="AT63">
         <v>0.50387400000000004</v>
       </c>
-      <c r="AS63">
+      <c r="AU63">
         <v>8.0829999999999999E-2</v>
       </c>
-      <c r="AT63">
+      <c r="AV63">
         <v>4.5533999999999998E-2</v>
       </c>
-      <c r="AU63">
+      <c r="AW63">
         <v>5.7787999999999999E-2</v>
       </c>
-      <c r="AV63">
+      <c r="AX63">
         <v>4.0529999999999997E-2</v>
       </c>
-      <c r="AX63">
+      <c r="BA63">
         <v>0.386328965425</v>
       </c>
-      <c r="AY63">
+      <c r="BB63">
         <v>7.0678502320999995E-2</v>
       </c>
-      <c r="AZ63">
+      <c r="BC63">
         <v>2.0423568789999999E-3</v>
       </c>
-      <c r="BA63">
+      <c r="BD63">
         <v>1.881283941E-3</v>
       </c>
-      <c r="BC63" t="s">
+      <c r="BF63" t="s">
         <v>328</v>
       </c>
-      <c r="BF63">
+      <c r="BI63">
         <f t="shared" si="1"/>
         <v>1.881283941E-3</v>
       </c>
-      <c r="BG63">
+      <c r="BJ63">
         <v>1.881283941E-3</v>
       </c>
     </row>
-    <row r="64" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>0.43566700000000003</v>
       </c>
@@ -46467,54 +46586,54 @@
       <c r="AL64">
         <v>0.43823499999999999</v>
       </c>
-      <c r="AO64">
+      <c r="AQ64">
         <v>0.37480599999999997</v>
       </c>
-      <c r="AP64">
+      <c r="AR64">
         <v>0.44400299999999998</v>
       </c>
-      <c r="AQ64">
+      <c r="AS64">
         <v>0.36442600000000003</v>
       </c>
-      <c r="AR64">
+      <c r="AT64">
         <v>0.489568</v>
       </c>
-      <c r="AS64">
+      <c r="AU64">
         <v>7.6138999999999998E-2</v>
       </c>
-      <c r="AT64">
+      <c r="AV64">
         <v>4.2298000000000002E-2</v>
       </c>
-      <c r="AU64">
+      <c r="AW64">
         <v>5.4122999999999998E-2</v>
       </c>
-      <c r="AV64">
+      <c r="AX64">
         <v>3.7275000000000003E-2</v>
       </c>
-      <c r="AX64">
+      <c r="BA64">
         <v>0.37377035617799997</v>
       </c>
-      <c r="AY64">
+      <c r="BB64">
         <v>6.6363587976000005E-2</v>
       </c>
-      <c r="AZ64">
+      <c r="BC64">
         <v>1.9956822509999998E-3</v>
       </c>
-      <c r="BA64">
+      <c r="BD64">
         <v>1.855093637E-3</v>
       </c>
-      <c r="BC64" t="s">
+      <c r="BF64" t="s">
         <v>329</v>
       </c>
-      <c r="BF64">
+      <c r="BI64">
         <f t="shared" si="1"/>
         <v>1.855093637E-3</v>
       </c>
-      <c r="BG64">
+      <c r="BJ64">
         <v>1.855093637E-3</v>
       </c>
     </row>
-    <row r="65" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>0.42972300000000002</v>
       </c>
@@ -46590,54 +46709,54 @@
       <c r="AL65">
         <v>0.42899700000000002</v>
       </c>
-      <c r="AO65">
+      <c r="AQ65">
         <v>0.359767</v>
       </c>
-      <c r="AP65">
+      <c r="AR65">
         <v>0.43648500000000001</v>
       </c>
-      <c r="AQ65">
+      <c r="AS65">
         <v>0.35046899999999997</v>
       </c>
-      <c r="AR65">
+      <c r="AT65">
         <v>0.48288399999999998</v>
       </c>
-      <c r="AS65">
+      <c r="AU65">
         <v>7.1744000000000002E-2</v>
       </c>
-      <c r="AT65">
+      <c r="AV65">
         <v>3.9282999999999998E-2</v>
       </c>
-      <c r="AU65">
+      <c r="AW65">
         <v>5.0613999999999999E-2</v>
       </c>
-      <c r="AV65">
+      <c r="AX65">
         <v>3.4791000000000002E-2</v>
       </c>
-      <c r="AX65">
+      <c r="BA65">
         <v>0.36017560958900002</v>
       </c>
-      <c r="AY65">
+      <c r="BB65">
         <v>6.2326639890999999E-2</v>
       </c>
-      <c r="AZ65">
+      <c r="BC65">
         <v>1.960502705E-3</v>
       </c>
-      <c r="BA65">
+      <c r="BD65">
         <v>1.829426037E-3</v>
       </c>
-      <c r="BC65" t="s">
+      <c r="BF65" t="s">
         <v>330</v>
       </c>
-      <c r="BF65">
+      <c r="BI65">
         <f t="shared" si="1"/>
         <v>1.829426037E-3</v>
       </c>
-      <c r="BG65">
+      <c r="BJ65">
         <v>1.829426037E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>0.42407499999999998</v>
       </c>
@@ -46713,54 +46832,54 @@
       <c r="AL66">
         <v>0.42052699999999998</v>
       </c>
-      <c r="AO66">
+      <c r="AQ66">
         <v>0.34503800000000001</v>
       </c>
-      <c r="AP66">
+      <c r="AR66">
         <v>0.42942399999999997</v>
       </c>
-      <c r="AQ66">
+      <c r="AS66">
         <v>0.33778799999999998</v>
       </c>
-      <c r="AR66">
+      <c r="AT66">
         <v>0.482406</v>
       </c>
-      <c r="AS66">
+      <c r="AU66">
         <v>6.7637000000000003E-2</v>
       </c>
-      <c r="AT66">
+      <c r="AV66">
         <v>3.6436999999999997E-2</v>
       </c>
-      <c r="AU66">
+      <c r="AW66">
         <v>4.7402E-2</v>
       </c>
-      <c r="AV66">
+      <c r="AX66">
         <v>3.1980000000000001E-2</v>
       </c>
-      <c r="AX66">
+      <c r="BA66">
         <v>0.34736883640299998</v>
       </c>
-      <c r="AY66">
+      <c r="BB66">
         <v>5.8570031076999998E-2</v>
       </c>
-      <c r="AZ66">
+      <c r="BC66">
         <v>1.927325618E-3</v>
       </c>
-      <c r="BA66">
+      <c r="BD66">
         <v>1.805895241E-3</v>
       </c>
-      <c r="BC66" t="s">
+      <c r="BF66" t="s">
         <v>331</v>
       </c>
-      <c r="BF66">
+      <c r="BI66">
         <f t="shared" si="1"/>
         <v>1.805895241E-3</v>
       </c>
-      <c r="BG66">
+      <c r="BJ66">
         <v>1.805895241E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>0.41834300000000002</v>
       </c>
@@ -46836,54 +46955,54 @@
       <c r="AL67">
         <v>0.40642200000000001</v>
       </c>
-      <c r="AO67">
+      <c r="AQ67">
         <v>0.33175500000000002</v>
       </c>
-      <c r="AP67">
+      <c r="AR67">
         <v>0.418933</v>
       </c>
-      <c r="AQ67">
+      <c r="AS67">
         <v>0.32473099999999999</v>
       </c>
-      <c r="AR67">
+      <c r="AT67">
         <v>0.471549</v>
       </c>
-      <c r="AS67">
+      <c r="AU67">
         <v>6.3718999999999998E-2</v>
       </c>
-      <c r="AT67">
+      <c r="AV67">
         <v>3.3883999999999997E-2</v>
       </c>
-      <c r="AU67">
+      <c r="AW67">
         <v>4.4339000000000003E-2</v>
       </c>
-      <c r="AV67">
+      <c r="AX67">
         <v>2.9794999999999999E-2</v>
       </c>
-      <c r="AX67">
+      <c r="BA67">
         <v>0.33277854323400002</v>
       </c>
-      <c r="AY67">
+      <c r="BB67">
         <v>5.4990913719000001E-2</v>
       </c>
-      <c r="AZ67">
+      <c r="BC67">
         <v>1.901925891E-3</v>
       </c>
-      <c r="BA67">
+      <c r="BD67">
         <v>1.7864507390000001E-3</v>
       </c>
-      <c r="BC67" t="s">
+      <c r="BF67" t="s">
         <v>332</v>
       </c>
-      <c r="BF67">
+      <c r="BI67">
         <f t="shared" si="1"/>
         <v>1.7864507390000001E-3</v>
       </c>
-      <c r="BG67">
+      <c r="BJ67">
         <v>1.7864507390000001E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>0.41297099999999998</v>
       </c>
@@ -46959,54 +47078,54 @@
       <c r="AL68">
         <v>0.39202799999999999</v>
       </c>
-      <c r="AO68">
+      <c r="AQ68">
         <v>0.31981999999999999</v>
       </c>
-      <c r="AP68">
+      <c r="AR68">
         <v>0.41161900000000001</v>
       </c>
-      <c r="AQ68">
+      <c r="AS68">
         <v>0.31220500000000001</v>
       </c>
-      <c r="AR68">
+      <c r="AT68">
         <v>0.45358799999999999</v>
       </c>
-      <c r="AS68">
+      <c r="AU68">
         <v>6.0035999999999999E-2</v>
       </c>
-      <c r="AT68">
+      <c r="AV68">
         <v>3.1400999999999998E-2</v>
       </c>
-      <c r="AU68">
+      <c r="AW68">
         <v>4.1528000000000002E-2</v>
       </c>
-      <c r="AV68">
+      <c r="AX68">
         <v>2.7490000000000001E-2</v>
       </c>
-      <c r="AX68">
+      <c r="BA68">
         <v>0.32187116146099998</v>
       </c>
-      <c r="AY68">
+      <c r="BB68">
         <v>5.1652569324000003E-2</v>
       </c>
-      <c r="AZ68">
+      <c r="BC68">
         <v>1.87335629E-3</v>
       </c>
-      <c r="BA68">
+      <c r="BD68">
         <v>1.7700917090000001E-3</v>
       </c>
-      <c r="BC68" t="s">
+      <c r="BF68" t="s">
         <v>333</v>
       </c>
-      <c r="BF68">
+      <c r="BI68">
         <f t="shared" si="1"/>
         <v>1.7700917090000001E-3</v>
       </c>
-      <c r="BG68">
+      <c r="BJ68">
         <v>1.7700917090000001E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>0.40770800000000001</v>
       </c>
@@ -47082,54 +47201,54 @@
       <c r="AL69">
         <v>0.38206699999999999</v>
       </c>
-      <c r="AO69">
+      <c r="AQ69">
         <v>0.30739100000000003</v>
       </c>
-      <c r="AP69">
+      <c r="AR69">
         <v>0.39805699999999999</v>
       </c>
-      <c r="AQ69">
+      <c r="AS69">
         <v>0.30252800000000002</v>
       </c>
-      <c r="AR69">
+      <c r="AT69">
         <v>0.44248300000000002</v>
       </c>
-      <c r="AS69">
+      <c r="AU69">
         <v>5.6598000000000002E-2</v>
       </c>
-      <c r="AT69">
+      <c r="AV69">
         <v>2.9227E-2</v>
       </c>
-      <c r="AU69">
+      <c r="AW69">
         <v>3.8855000000000001E-2</v>
       </c>
-      <c r="AV69">
+      <c r="AX69">
         <v>2.5517999999999999E-2</v>
       </c>
-      <c r="AX69">
+      <c r="BA69">
         <v>0.307764410973</v>
       </c>
-      <c r="AY69">
+      <c r="BB69">
         <v>4.8524122684999997E-2</v>
       </c>
-      <c r="AZ69">
+      <c r="BC69">
         <v>1.8484551689999999E-3</v>
       </c>
-      <c r="BA69">
+      <c r="BD69">
         <v>1.754725468E-3</v>
       </c>
-      <c r="BC69" t="s">
+      <c r="BF69" t="s">
         <v>334</v>
       </c>
-      <c r="BF69">
-        <f t="shared" ref="BF69:BF103" si="2">--TRIM(RIGHT(SUBSTITUTE(SUBSTITUTE(BC69,":"," "), " ", REPT(" ",99)),99))</f>
+      <c r="BI69">
+        <f t="shared" ref="BI69:BI103" si="2">--TRIM(RIGHT(SUBSTITUTE(SUBSTITUTE(BF69,":"," "), " ", REPT(" ",99)),99))</f>
         <v>1.754725468E-3</v>
       </c>
-      <c r="BG69">
+      <c r="BJ69">
         <v>1.754725468E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>0.40271000000000001</v>
       </c>
@@ -47205,54 +47324,54 @@
       <c r="AL70">
         <v>0.37281300000000001</v>
       </c>
-      <c r="AO70">
+      <c r="AQ70">
         <v>0.29559999999999997</v>
       </c>
-      <c r="AP70">
+      <c r="AR70">
         <v>0.38816600000000001</v>
       </c>
-      <c r="AQ70">
+      <c r="AS70">
         <v>0.29075200000000001</v>
       </c>
-      <c r="AR70">
+      <c r="AT70">
         <v>0.429697</v>
       </c>
-      <c r="AS70">
+      <c r="AU70">
         <v>5.3329000000000001E-2</v>
       </c>
-      <c r="AT70">
+      <c r="AV70">
         <v>2.7097E-2</v>
       </c>
-      <c r="AU70">
+      <c r="AW70">
         <v>3.6391E-2</v>
       </c>
-      <c r="AV70">
+      <c r="AX70">
         <v>2.3657999999999998E-2</v>
       </c>
-      <c r="AX70">
+      <c r="BA70">
         <v>0.29549995064700002</v>
       </c>
-      <c r="AY70">
+      <c r="BB70">
         <v>4.5576803386000002E-2</v>
       </c>
-      <c r="AZ70">
+      <c r="BC70">
         <v>1.82551553E-3</v>
       </c>
-      <c r="BA70">
+      <c r="BD70">
         <v>1.7402411899999999E-3</v>
       </c>
-      <c r="BC70" t="s">
+      <c r="BF70" t="s">
         <v>335</v>
       </c>
-      <c r="BF70">
+      <c r="BI70">
         <f t="shared" si="2"/>
         <v>1.7402411899999999E-3</v>
       </c>
-      <c r="BG70">
+      <c r="BJ70">
         <v>1.7402411899999999E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>0.39774799999999999</v>
       </c>
@@ -47328,54 +47447,54 @@
       <c r="AL71">
         <v>0.35913600000000001</v>
       </c>
-      <c r="AO71">
+      <c r="AQ71">
         <v>0.28454000000000002</v>
       </c>
-      <c r="AP71">
+      <c r="AR71">
         <v>0.37356499999999998</v>
       </c>
-      <c r="AQ71">
+      <c r="AS71">
         <v>0.281246</v>
       </c>
-      <c r="AR71">
+      <c r="AT71">
         <v>0.41690100000000002</v>
       </c>
-      <c r="AS71">
+      <c r="AU71">
         <v>5.0257000000000003E-2</v>
       </c>
-      <c r="AT71">
+      <c r="AV71">
         <v>2.5208999999999999E-2</v>
       </c>
-      <c r="AU71">
+      <c r="AW71">
         <v>3.4072999999999999E-2</v>
       </c>
-      <c r="AV71">
+      <c r="AX71">
         <v>2.1881000000000001E-2</v>
       </c>
-      <c r="AX71">
+      <c r="BA71">
         <v>0.28456515073799998</v>
       </c>
-      <c r="AY71">
+      <c r="BB71">
         <v>4.2801424860999998E-2</v>
       </c>
-      <c r="AZ71">
+      <c r="BC71">
         <v>1.8039772989999999E-3</v>
       </c>
-      <c r="BA71">
+      <c r="BD71">
         <v>1.727331197E-3</v>
       </c>
-      <c r="BC71" t="s">
+      <c r="BF71" t="s">
         <v>336</v>
       </c>
-      <c r="BF71">
+      <c r="BI71">
         <f t="shared" si="2"/>
         <v>1.727331197E-3</v>
       </c>
-      <c r="BG71">
+      <c r="BJ71">
         <v>1.727331197E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>0.39299800000000001</v>
       </c>
@@ -47451,54 +47570,54 @@
       <c r="AL72">
         <v>0.35064200000000001</v>
       </c>
-      <c r="AO72">
+      <c r="AQ72">
         <v>0.27337800000000001</v>
       </c>
-      <c r="AP72">
+      <c r="AR72">
         <v>0.36238599999999999</v>
       </c>
-      <c r="AQ72">
+      <c r="AS72">
         <v>0.27026099999999997</v>
       </c>
-      <c r="AR72">
+      <c r="AT72">
         <v>0.40635300000000002</v>
       </c>
-      <c r="AS72">
+      <c r="AU72">
         <v>4.7384999999999997E-2</v>
       </c>
-      <c r="AT72">
+      <c r="AV72">
         <v>2.3424E-2</v>
       </c>
-      <c r="AU72">
+      <c r="AW72">
         <v>3.1904000000000002E-2</v>
       </c>
-      <c r="AV72">
+      <c r="AX72">
         <v>2.0381E-2</v>
       </c>
-      <c r="AX72">
+      <c r="BA72">
         <v>0.27333715558100002</v>
       </c>
-      <c r="AY72">
+      <c r="BB72">
         <v>4.0225211530999998E-2</v>
       </c>
-      <c r="AZ72">
+      <c r="BC72">
         <v>1.7861429370000001E-3</v>
       </c>
-      <c r="BA72">
+      <c r="BD72">
         <v>1.715317601E-3</v>
       </c>
-      <c r="BC72" t="s">
+      <c r="BF72" t="s">
         <v>337</v>
       </c>
-      <c r="BF72">
+      <c r="BI72">
         <f t="shared" si="2"/>
         <v>1.715317601E-3</v>
       </c>
-      <c r="BG72">
+      <c r="BJ72">
         <v>1.715317601E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>0.38836199999999999</v>
       </c>
@@ -47574,54 +47693,54 @@
       <c r="AL73">
         <v>0.34357799999999999</v>
       </c>
-      <c r="AO73">
+      <c r="AQ73">
         <v>0.26252999999999999</v>
       </c>
-      <c r="AP73">
+      <c r="AR73">
         <v>0.35189900000000002</v>
       </c>
-      <c r="AQ73">
+      <c r="AS73">
         <v>0.26121800000000001</v>
       </c>
-      <c r="AR73">
+      <c r="AT73">
         <v>0.39848800000000001</v>
       </c>
-      <c r="AS73">
+      <c r="AU73">
         <v>4.4656000000000001E-2</v>
       </c>
-      <c r="AT73">
+      <c r="AV73">
         <v>2.1759000000000001E-2</v>
       </c>
-      <c r="AU73">
+      <c r="AW73">
         <v>2.9898999999999998E-2</v>
       </c>
-      <c r="AV73">
+      <c r="AX73">
         <v>1.8811000000000001E-2</v>
       </c>
-      <c r="AX73">
+      <c r="BA73">
         <v>0.26317360997200001</v>
       </c>
-      <c r="AY73">
+      <c r="BB73">
         <v>3.7784799932999998E-2</v>
       </c>
-      <c r="AZ73">
+      <c r="BC73">
         <v>1.768425689E-3</v>
       </c>
-      <c r="BA73">
+      <c r="BD73">
         <v>1.7033710609999999E-3</v>
       </c>
-      <c r="BC73" t="s">
+      <c r="BF73" t="s">
         <v>338</v>
       </c>
-      <c r="BF73">
+      <c r="BI73">
         <f t="shared" si="2"/>
         <v>1.7033710609999999E-3</v>
       </c>
-      <c r="BG73">
+      <c r="BJ73">
         <v>1.7033710609999999E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>0.383909</v>
       </c>
@@ -47697,54 +47816,54 @@
       <c r="AL74">
         <v>0.33682400000000001</v>
       </c>
-      <c r="AO74">
+      <c r="AQ74">
         <v>0.25209599999999999</v>
       </c>
-      <c r="AP74">
+      <c r="AR74">
         <v>0.343613</v>
       </c>
-      <c r="AQ74">
+      <c r="AS74">
         <v>0.24992900000000001</v>
       </c>
-      <c r="AR74">
+      <c r="AT74">
         <v>0.389677</v>
       </c>
-      <c r="AS74">
+      <c r="AU74">
         <v>4.2098999999999998E-2</v>
       </c>
-      <c r="AT74">
+      <c r="AV74">
         <v>2.0274E-2</v>
       </c>
-      <c r="AU74">
+      <c r="AW74">
         <v>2.7994999999999999E-2</v>
       </c>
-      <c r="AV74">
+      <c r="AX74">
         <v>1.7569999999999999E-2</v>
       </c>
-      <c r="AX74">
+      <c r="BA74">
         <v>0.25318303704299999</v>
       </c>
-      <c r="AY74">
+      <c r="BB74">
         <v>3.5500433296E-2</v>
       </c>
-      <c r="AZ74">
+      <c r="BC74">
         <v>1.7547606260000001E-3</v>
       </c>
-      <c r="BA74">
+      <c r="BD74">
         <v>1.692191698E-3</v>
       </c>
-      <c r="BC74" t="s">
+      <c r="BF74" t="s">
         <v>339</v>
       </c>
-      <c r="BF74">
+      <c r="BI74">
         <f t="shared" si="2"/>
         <v>1.692191698E-3</v>
       </c>
-      <c r="BG74">
+      <c r="BJ74">
         <v>1.692191698E-3</v>
       </c>
     </row>
-    <row r="75" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>0.37962600000000002</v>
       </c>
@@ -47820,54 +47939,54 @@
       <c r="AL75">
         <v>0.33133299999999999</v>
       </c>
-      <c r="AO75">
+      <c r="AQ75">
         <v>0.24194399999999999</v>
       </c>
-      <c r="AP75">
+      <c r="AR75">
         <v>0.33266699999999999</v>
       </c>
-      <c r="AQ75">
+      <c r="AS75">
         <v>0.24072099999999999</v>
       </c>
-      <c r="AR75">
+      <c r="AT75">
         <v>0.38584099999999999</v>
       </c>
-      <c r="AS75">
+      <c r="AU75">
         <v>3.9703000000000002E-2</v>
       </c>
-      <c r="AT75">
+      <c r="AV75">
         <v>1.8825999999999999E-2</v>
       </c>
-      <c r="AU75">
+      <c r="AW75">
         <v>2.6252999999999999E-2</v>
       </c>
-      <c r="AV75">
+      <c r="AX75">
         <v>1.6226000000000001E-2</v>
       </c>
-      <c r="AX75">
+      <c r="BA75">
         <v>0.24403122067499999</v>
       </c>
-      <c r="AY75">
+      <c r="BB75">
         <v>3.3377636224000001E-2</v>
       </c>
-      <c r="AZ75">
+      <c r="BC75">
         <v>1.7400794900000001E-3</v>
       </c>
-      <c r="BA75">
+      <c r="BD75">
         <v>1.6827000070000001E-3</v>
       </c>
-      <c r="BC75" t="s">
+      <c r="BF75" t="s">
         <v>340</v>
       </c>
-      <c r="BF75">
+      <c r="BI75">
         <f t="shared" si="2"/>
         <v>1.6827000070000001E-3</v>
       </c>
-      <c r="BG75">
+      <c r="BJ75">
         <v>1.6827000070000001E-3</v>
       </c>
     </row>
-    <row r="76" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>0.37530000000000002</v>
       </c>
@@ -47943,54 +48062,54 @@
       <c r="AL76">
         <v>0.321627</v>
       </c>
-      <c r="AO76">
+      <c r="AQ76">
         <v>0.233017</v>
       </c>
-      <c r="AP76">
+      <c r="AR76">
         <v>0.32901000000000002</v>
       </c>
-      <c r="AQ76">
+      <c r="AS76">
         <v>0.231544</v>
       </c>
-      <c r="AR76">
+      <c r="AT76">
         <v>0.38853900000000002</v>
       </c>
-      <c r="AS76">
+      <c r="AU76">
         <v>3.7429999999999998E-2</v>
       </c>
-      <c r="AT76">
+      <c r="AV76">
         <v>1.7548999999999999E-2</v>
       </c>
-      <c r="AU76">
+      <c r="AW76">
         <v>2.46E-2</v>
       </c>
-      <c r="AV76">
+      <c r="AX76">
         <v>1.5167E-2</v>
       </c>
-      <c r="AX76">
+      <c r="BA76">
         <v>0.23522838950200001</v>
       </c>
-      <c r="AY76">
+      <c r="BB76">
         <v>3.1358793378000002E-2</v>
       </c>
-      <c r="AZ76">
+      <c r="BC76">
         <v>1.7266942889999999E-3</v>
       </c>
-      <c r="BA76">
+      <c r="BD76">
         <v>1.6744425519999999E-3</v>
       </c>
-      <c r="BC76" t="s">
+      <c r="BF76" t="s">
         <v>341</v>
       </c>
-      <c r="BF76">
+      <c r="BI76">
         <f t="shared" si="2"/>
         <v>1.6744425519999999E-3</v>
       </c>
-      <c r="BG76">
+      <c r="BJ76">
         <v>1.6744425519999999E-3</v>
       </c>
     </row>
-    <row r="77" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>0.37128100000000003</v>
       </c>
@@ -48066,54 +48185,54 @@
       <c r="AL77">
         <v>0.31307499999999999</v>
       </c>
-      <c r="AO77">
+      <c r="AQ77">
         <v>0.223885</v>
       </c>
-      <c r="AP77">
+      <c r="AR77">
         <v>0.322766</v>
       </c>
-      <c r="AQ77">
+      <c r="AS77">
         <v>0.22242899999999999</v>
       </c>
-      <c r="AR77">
+      <c r="AT77">
         <v>0.38841799999999999</v>
       </c>
-      <c r="AS77">
+      <c r="AU77">
         <v>3.5302E-2</v>
       </c>
-      <c r="AT77">
+      <c r="AV77">
         <v>1.6337000000000001E-2</v>
       </c>
-      <c r="AU77">
+      <c r="AW77">
         <v>2.3068999999999999E-2</v>
       </c>
-      <c r="AV77">
+      <c r="AX77">
         <v>1.4037000000000001E-2</v>
       </c>
-      <c r="AX77">
+      <c r="BA77">
         <v>0.225740715861</v>
       </c>
-      <c r="AY77">
+      <c r="BB77">
         <v>2.9492028058000001E-2</v>
       </c>
-      <c r="AZ77">
+      <c r="BC77">
         <v>1.7147425099999999E-3</v>
       </c>
-      <c r="BA77">
+      <c r="BD77">
         <v>1.666588243E-3</v>
       </c>
-      <c r="BC77" t="s">
+      <c r="BF77" t="s">
         <v>342</v>
       </c>
-      <c r="BF77">
+      <c r="BI77">
         <f t="shared" si="2"/>
         <v>1.666588243E-3</v>
       </c>
-      <c r="BG77">
+      <c r="BJ77">
         <v>1.666588243E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>0.367118</v>
       </c>
@@ -48189,54 +48308,54 @@
       <c r="AL78">
         <v>0.302846</v>
       </c>
-      <c r="AO78">
+      <c r="AQ78">
         <v>0.21451500000000001</v>
       </c>
-      <c r="AP78">
+      <c r="AR78">
         <v>0.31371700000000002</v>
       </c>
-      <c r="AQ78">
+      <c r="AS78">
         <v>0.21409600000000001</v>
       </c>
-      <c r="AR78">
+      <c r="AT78">
         <v>0.38206899999999999</v>
       </c>
-      <c r="AS78">
+      <c r="AU78">
         <v>3.3307000000000003E-2</v>
       </c>
-      <c r="AT78">
+      <c r="AV78">
         <v>1.5216E-2</v>
       </c>
-      <c r="AU78">
+      <c r="AW78">
         <v>2.1649999999999999E-2</v>
       </c>
-      <c r="AV78">
+      <c r="AX78">
         <v>1.3129999999999999E-2</v>
       </c>
-      <c r="AX78">
+      <c r="BA78">
         <v>0.21804642677300001</v>
       </c>
-      <c r="AY78">
+      <c r="BB78">
         <v>2.7730228379000001E-2</v>
       </c>
-      <c r="AZ78">
+      <c r="BC78">
         <v>1.7024199480000001E-3</v>
       </c>
-      <c r="BA78">
+      <c r="BD78">
         <v>1.659192611E-3</v>
       </c>
-      <c r="BC78" t="s">
+      <c r="BF78" t="s">
         <v>343</v>
       </c>
-      <c r="BF78">
+      <c r="BI78">
         <f t="shared" si="2"/>
         <v>1.659192611E-3</v>
       </c>
-      <c r="BG78">
+      <c r="BJ78">
         <v>1.659192611E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>0.36332300000000001</v>
       </c>
@@ -48312,54 +48431,54 @@
       <c r="AL79">
         <v>0.294902</v>
       </c>
-      <c r="AO79">
+      <c r="AQ79">
         <v>0.20704600000000001</v>
       </c>
-      <c r="AP79">
+      <c r="AR79">
         <v>0.30863600000000002</v>
       </c>
-      <c r="AQ79">
+      <c r="AS79">
         <v>0.205457</v>
       </c>
-      <c r="AR79">
+      <c r="AT79">
         <v>0.381216</v>
       </c>
-      <c r="AS79">
+      <c r="AU79">
         <v>3.1417E-2</v>
       </c>
-      <c r="AT79">
+      <c r="AV79">
         <v>1.4206999999999999E-2</v>
       </c>
-      <c r="AU79">
+      <c r="AW79">
         <v>2.0305E-2</v>
       </c>
-      <c r="AV79">
+      <c r="AX79">
         <v>1.2189E-2</v>
       </c>
-      <c r="AX79">
+      <c r="BA79">
         <v>0.209024623036</v>
       </c>
-      <c r="AY79">
+      <c r="BB79">
         <v>2.6083953678999999E-2</v>
       </c>
-      <c r="AZ79">
+      <c r="BC79">
         <v>1.6927468819999999E-3</v>
       </c>
-      <c r="BA79">
+      <c r="BD79">
         <v>1.6524541419999999E-3</v>
       </c>
-      <c r="BC79" t="s">
+      <c r="BF79" t="s">
         <v>344</v>
       </c>
-      <c r="BF79">
+      <c r="BI79">
         <f t="shared" si="2"/>
         <v>1.6524541419999999E-3</v>
       </c>
-      <c r="BG79">
+      <c r="BJ79">
         <v>1.6524541419999999E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>0.35952800000000001</v>
       </c>
@@ -48435,54 +48554,54 @@
       <c r="AL80">
         <v>0.28975299999999998</v>
       </c>
-      <c r="AO80">
+      <c r="AQ80">
         <v>0.199104</v>
       </c>
-      <c r="AP80">
+      <c r="AR80">
         <v>0.30201899999999998</v>
       </c>
-      <c r="AQ80">
+      <c r="AS80">
         <v>0.19756899999999999</v>
       </c>
-      <c r="AR80">
+      <c r="AT80">
         <v>0.38428200000000001</v>
       </c>
-      <c r="AS80">
+      <c r="AU80">
         <v>2.9648999999999998E-2</v>
       </c>
-      <c r="AT80">
+      <c r="AV80">
         <v>1.3242E-2</v>
       </c>
-      <c r="AU80">
+      <c r="AW80">
         <v>1.9071999999999999E-2</v>
       </c>
-      <c r="AV80">
+      <c r="AX80">
         <v>1.1396999999999999E-2</v>
       </c>
-      <c r="AX80">
+      <c r="BA80">
         <v>0.20195345580599999</v>
       </c>
-      <c r="AY80">
+      <c r="BB80">
         <v>2.4540755898000002E-2</v>
       </c>
-      <c r="AZ80">
+      <c r="BC80">
         <v>1.6833179400000001E-3</v>
       </c>
-      <c r="BA80">
+      <c r="BD80">
         <v>1.6458970489999999E-3</v>
       </c>
-      <c r="BC80" t="s">
+      <c r="BF80" t="s">
         <v>345</v>
       </c>
-      <c r="BF80">
+      <c r="BI80">
         <f t="shared" si="2"/>
         <v>1.6458970489999999E-3</v>
       </c>
-      <c r="BG80">
+      <c r="BJ80">
         <v>1.6458970489999999E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>0.35589100000000001</v>
       </c>
@@ -48558,54 +48677,54 @@
       <c r="AL81">
         <v>0.295211</v>
       </c>
-      <c r="AO81">
+      <c r="AQ81">
         <v>0.19036600000000001</v>
       </c>
-      <c r="AP81">
+      <c r="AR81">
         <v>0.29505799999999999</v>
       </c>
-      <c r="AQ81">
+      <c r="AS81">
         <v>0.189438</v>
       </c>
-      <c r="AR81">
+      <c r="AT81">
         <v>0.375861</v>
       </c>
-      <c r="AS81">
+      <c r="AU81">
         <v>2.7990000000000001E-2</v>
       </c>
-      <c r="AT81">
+      <c r="AV81">
         <v>1.2377000000000001E-2</v>
       </c>
-      <c r="AU81">
+      <c r="AW81">
         <v>1.7915E-2</v>
       </c>
-      <c r="AV81">
+      <c r="AX81">
         <v>1.0628E-2</v>
       </c>
-      <c r="AX81">
+      <c r="BA81">
         <v>0.19465158879800001</v>
       </c>
-      <c r="AY81">
+      <c r="BB81">
         <v>2.3097414523000001E-2</v>
       </c>
-      <c r="AZ81">
+      <c r="BC81">
         <v>1.674724277E-3</v>
       </c>
-      <c r="BA81">
+      <c r="BD81">
         <v>1.639198512E-3</v>
       </c>
-      <c r="BC81" t="s">
+      <c r="BF81" t="s">
         <v>346</v>
       </c>
-      <c r="BF81">
+      <c r="BI81">
         <f t="shared" si="2"/>
         <v>1.639198512E-3</v>
       </c>
-      <c r="BG81">
+      <c r="BJ81">
         <v>1.639198512E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>0.35230499999999998</v>
       </c>
@@ -48681,54 +48800,54 @@
       <c r="AL82">
         <v>0.30200500000000002</v>
       </c>
-      <c r="AO82">
+      <c r="AQ82">
         <v>0.182949</v>
       </c>
-      <c r="AP82">
+      <c r="AR82">
         <v>0.29266599999999998</v>
       </c>
-      <c r="AQ82">
+      <c r="AS82">
         <v>0.182557</v>
       </c>
-      <c r="AR82">
+      <c r="AT82">
         <v>0.36477300000000001</v>
       </c>
-      <c r="AS82">
+      <c r="AU82">
         <v>2.6421E-2</v>
       </c>
-      <c r="AT82">
+      <c r="AV82">
         <v>1.1573999999999999E-2</v>
       </c>
-      <c r="AU82">
+      <c r="AW82">
         <v>1.6829E-2</v>
       </c>
-      <c r="AV82">
+      <c r="AX82">
         <v>9.9340000000000001E-3</v>
       </c>
-      <c r="AX82">
+      <c r="BA82">
         <v>0.187145754695</v>
       </c>
-      <c r="AY82">
+      <c r="BB82">
         <v>2.1745359525000001E-2</v>
       </c>
-      <c r="AZ82">
+      <c r="BC82">
         <v>1.6664830040000001E-3</v>
       </c>
-      <c r="BA82">
+      <c r="BD82">
         <v>1.6328166239999999E-3</v>
       </c>
-      <c r="BC82" t="s">
+      <c r="BF82" t="s">
         <v>347</v>
       </c>
-      <c r="BF82">
+      <c r="BI82">
         <f t="shared" si="2"/>
         <v>1.6328166239999999E-3</v>
       </c>
-      <c r="BG82">
+      <c r="BJ82">
         <v>1.6328166239999999E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>0.34893800000000003</v>
       </c>
@@ -48804,54 +48923,54 @@
       <c r="AL83">
         <v>0.30922899999999998</v>
       </c>
-      <c r="AO83">
+      <c r="AQ83">
         <v>0.17569599999999999</v>
       </c>
-      <c r="AP83">
+      <c r="AR83">
         <v>0.28557300000000002</v>
       </c>
-      <c r="AQ83">
+      <c r="AS83">
         <v>0.17635600000000001</v>
       </c>
-      <c r="AR83">
+      <c r="AT83">
         <v>0.35217500000000002</v>
       </c>
-      <c r="AS83">
+      <c r="AU83">
         <v>2.4955000000000001E-2</v>
       </c>
-      <c r="AT83">
+      <c r="AV83">
         <v>1.0815999999999999E-2</v>
       </c>
-      <c r="AU83">
+      <c r="AW83">
         <v>1.583E-2</v>
       </c>
-      <c r="AV83">
+      <c r="AX83">
         <v>9.299E-3</v>
       </c>
-      <c r="AX83">
+      <c r="BA83">
         <v>0.18114253878600001</v>
       </c>
-      <c r="AY83">
+      <c r="BB83">
         <v>2.0477918907999999E-2</v>
       </c>
-      <c r="AZ83">
+      <c r="BC83">
         <v>1.6582151869999999E-3</v>
       </c>
-      <c r="BA83">
+      <c r="BD83">
         <v>1.627146616E-3</v>
       </c>
-      <c r="BC83" t="s">
+      <c r="BF83" t="s">
         <v>348</v>
       </c>
-      <c r="BF83">
+      <c r="BI83">
         <f t="shared" si="2"/>
         <v>1.627146616E-3</v>
       </c>
-      <c r="BG83">
+      <c r="BJ83">
         <v>1.627146616E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>0.34551199999999999</v>
       </c>
@@ -48927,54 +49046,54 @@
       <c r="AL84">
         <v>0.293709</v>
       </c>
-      <c r="AO84">
+      <c r="AQ84">
         <v>0.16881299999999999</v>
       </c>
-      <c r="AP84">
+      <c r="AR84">
         <v>0.27689200000000003</v>
       </c>
-      <c r="AQ84">
+      <c r="AS84">
         <v>0.16885700000000001</v>
       </c>
-      <c r="AR84">
+      <c r="AT84">
         <v>0.33789599999999997</v>
       </c>
-      <c r="AS84">
+      <c r="AU84">
         <v>2.3576E-2</v>
       </c>
-      <c r="AT84">
+      <c r="AV84">
         <v>1.0146000000000001E-2</v>
       </c>
-      <c r="AU84">
+      <c r="AW84">
         <v>1.4893999999999999E-2</v>
       </c>
-      <c r="AV84">
+      <c r="AX84">
         <v>8.7039999999999999E-3</v>
       </c>
-      <c r="AX84">
+      <c r="BA84">
         <v>0.17511969804800001</v>
       </c>
-      <c r="AY84">
+      <c r="BB84">
         <v>1.9297687337000002E-2</v>
       </c>
-      <c r="AZ84">
+      <c r="BC84">
         <v>1.651626662E-3</v>
       </c>
-      <c r="BA84">
+      <c r="BD84">
         <v>1.6219486719999999E-3</v>
       </c>
-      <c r="BC84" t="s">
+      <c r="BF84" t="s">
         <v>349</v>
       </c>
-      <c r="BF84">
+      <c r="BI84">
         <f t="shared" si="2"/>
         <v>1.6219486719999999E-3</v>
       </c>
-      <c r="BG84">
+      <c r="BJ84">
         <v>1.6219486719999999E-3</v>
       </c>
     </row>
-    <row r="85" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>0.34215699999999999</v>
       </c>
@@ -49050,54 +49169,54 @@
       <c r="AL85">
         <v>0.28116799999999997</v>
       </c>
-      <c r="AO85">
+      <c r="AQ85">
         <v>0.16156799999999999</v>
       </c>
-      <c r="AP85">
+      <c r="AR85">
         <v>0.26883699999999999</v>
       </c>
-      <c r="AQ85">
+      <c r="AS85">
         <v>0.16373499999999999</v>
       </c>
-      <c r="AR85">
+      <c r="AT85">
         <v>0.323324</v>
       </c>
-      <c r="AS85">
+      <c r="AU85">
         <v>2.2276000000000001E-2</v>
       </c>
-      <c r="AT85">
+      <c r="AV85">
         <v>9.5049999999999996E-3</v>
       </c>
-      <c r="AU85">
+      <c r="AW85">
         <v>1.4015E-2</v>
       </c>
-      <c r="AV85">
+      <c r="AX85">
         <v>8.1740000000000007E-3</v>
       </c>
-      <c r="AX85">
+      <c r="BA85">
         <v>0.168475598097</v>
       </c>
-      <c r="AY85">
+      <c r="BB85">
         <v>1.8187627195999999E-2</v>
       </c>
-      <c r="AZ85">
+      <c r="BC85">
         <v>1.6449432590000001E-3</v>
       </c>
-      <c r="BA85">
+      <c r="BD85">
         <v>1.6170055610000001E-3</v>
       </c>
-      <c r="BC85" t="s">
+      <c r="BF85" t="s">
         <v>350</v>
       </c>
-      <c r="BF85">
+      <c r="BI85">
         <f t="shared" si="2"/>
         <v>1.6170055610000001E-3</v>
       </c>
-      <c r="BG85">
+      <c r="BJ85">
         <v>1.6170055610000001E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>0.33906399999999998</v>
       </c>
@@ -49173,54 +49292,54 @@
       <c r="AL86">
         <v>0.26942899999999997</v>
       </c>
-      <c r="AO86">
+      <c r="AQ86">
         <v>0.15470700000000001</v>
       </c>
-      <c r="AP86">
+      <c r="AR86">
         <v>0.25909799999999999</v>
       </c>
-      <c r="AQ86">
+      <c r="AS86">
         <v>0.15787200000000001</v>
       </c>
-      <c r="AR86">
+      <c r="AT86">
         <v>0.317521</v>
       </c>
-      <c r="AS86">
+      <c r="AU86">
         <v>2.1062000000000001E-2</v>
       </c>
-      <c r="AT86">
+      <c r="AV86">
         <v>8.9210000000000001E-3</v>
       </c>
-      <c r="AU86">
+      <c r="AW86">
         <v>1.3207E-2</v>
       </c>
-      <c r="AV86">
+      <c r="AX86">
         <v>7.6660000000000001E-3</v>
       </c>
-      <c r="AX86">
+      <c r="BA86">
         <v>0.16367906332000001</v>
       </c>
-      <c r="AY86">
+      <c r="BB86">
         <v>1.7151089384999998E-2</v>
       </c>
-      <c r="AZ86">
+      <c r="BC86">
         <v>1.6385081690000001E-3</v>
       </c>
-      <c r="BA86">
+      <c r="BD86">
         <v>1.612472115E-3</v>
       </c>
-      <c r="BC86" t="s">
+      <c r="BF86" t="s">
         <v>351</v>
       </c>
-      <c r="BF86">
+      <c r="BI86">
         <f t="shared" si="2"/>
         <v>1.612472115E-3</v>
       </c>
-      <c r="BG86">
+      <c r="BJ86">
         <v>1.612472115E-3</v>
       </c>
     </row>
-    <row r="87" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>0.33604499999999998</v>
       </c>
@@ -49296,54 +49415,54 @@
       <c r="AL87">
         <v>0.26094600000000001</v>
       </c>
-      <c r="AO87">
+      <c r="AQ87">
         <v>0.147975</v>
       </c>
-      <c r="AP87">
+      <c r="AR87">
         <v>0.25368299999999999</v>
       </c>
-      <c r="AQ87">
+      <c r="AS87">
         <v>0.152586</v>
       </c>
-      <c r="AR87">
+      <c r="AT87">
         <v>0.31031399999999998</v>
       </c>
-      <c r="AS87">
+      <c r="AU87">
         <v>1.9916E-2</v>
       </c>
-      <c r="AT87">
+      <c r="AV87">
         <v>8.3920000000000002E-3</v>
       </c>
-      <c r="AU87">
+      <c r="AW87">
         <v>1.2453000000000001E-2</v>
       </c>
-      <c r="AV87">
+      <c r="AX87">
         <v>7.228E-3</v>
       </c>
-      <c r="AX87">
+      <c r="BA87">
         <v>0.15673314034899999</v>
       </c>
-      <c r="AY87">
+      <c r="BB87">
         <v>1.6183668748E-2</v>
       </c>
-      <c r="AZ87">
+      <c r="BC87">
         <v>1.6328190689999999E-3</v>
       </c>
-      <c r="BA87">
+      <c r="BD87">
         <v>1.6083089870000001E-3</v>
       </c>
-      <c r="BC87" t="s">
+      <c r="BF87" t="s">
         <v>352</v>
       </c>
-      <c r="BF87">
+      <c r="BI87">
         <f t="shared" si="2"/>
         <v>1.6083089870000001E-3</v>
       </c>
-      <c r="BG87">
+      <c r="BJ87">
         <v>1.6083089870000001E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>0.33294499999999999</v>
       </c>
@@ -49419,54 +49538,54 @@
       <c r="AL88">
         <v>0.25271700000000002</v>
       </c>
-      <c r="AO88">
+      <c r="AQ88">
         <v>0.14204600000000001</v>
       </c>
-      <c r="AP88">
+      <c r="AR88">
         <v>0.246839</v>
       </c>
-      <c r="AQ88">
+      <c r="AS88">
         <v>0.146866</v>
       </c>
-      <c r="AR88">
+      <c r="AT88">
         <v>0.30349700000000002</v>
       </c>
-      <c r="AS88">
+      <c r="AU88">
         <v>1.8841E-2</v>
       </c>
-      <c r="AT88">
+      <c r="AV88">
         <v>7.8910000000000004E-3</v>
       </c>
-      <c r="AU88">
+      <c r="AW88">
         <v>1.1742000000000001E-2</v>
       </c>
-      <c r="AV88">
+      <c r="AX88">
         <v>6.7949999999999998E-3</v>
       </c>
-      <c r="AX88">
+      <c r="BA88">
         <v>0.153285905719</v>
       </c>
-      <c r="AY88">
+      <c r="BB88">
         <v>1.5276217833E-2</v>
       </c>
-      <c r="AZ88">
+      <c r="BC88">
         <v>1.6272530190000001E-3</v>
       </c>
-      <c r="BA88">
+      <c r="BD88">
         <v>1.6041813649999999E-3</v>
       </c>
-      <c r="BC88" t="s">
+      <c r="BF88" t="s">
         <v>353</v>
       </c>
-      <c r="BF88">
+      <c r="BI88">
         <f t="shared" si="2"/>
         <v>1.6041813649999999E-3</v>
       </c>
-      <c r="BG88">
+      <c r="BJ88">
         <v>1.6041813649999999E-3</v>
       </c>
     </row>
-    <row r="89" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>0.32999800000000001</v>
       </c>
@@ -49542,54 +49661,54 @@
       <c r="AL89">
         <v>0.248283</v>
       </c>
-      <c r="AO89">
+      <c r="AQ89">
         <v>0.136376</v>
       </c>
-      <c r="AP89">
+      <c r="AR89">
         <v>0.243287</v>
       </c>
-      <c r="AQ89">
+      <c r="AS89">
         <v>0.14194100000000001</v>
       </c>
-      <c r="AR89">
+      <c r="AT89">
         <v>0.29770400000000002</v>
       </c>
-      <c r="AS89">
+      <c r="AU89">
         <v>1.7836000000000001E-2</v>
       </c>
-      <c r="AT89">
+      <c r="AV89">
         <v>7.4359999999999999E-3</v>
       </c>
-      <c r="AU89">
+      <c r="AW89">
         <v>1.1087E-2</v>
       </c>
-      <c r="AV89">
+      <c r="AX89">
         <v>6.4289999999999998E-3</v>
       </c>
-      <c r="AX89">
+      <c r="BA89">
         <v>0.148059144616</v>
       </c>
-      <c r="AY89">
+      <c r="BB89">
         <v>1.4427410438999999E-2</v>
       </c>
-      <c r="AZ89">
+      <c r="BC89">
         <v>1.6223401760000001E-3</v>
       </c>
-      <c r="BA89">
+      <c r="BD89">
         <v>1.6000467589999999E-3</v>
       </c>
-      <c r="BC89" t="s">
+      <c r="BF89" t="s">
         <v>354</v>
       </c>
-      <c r="BF89">
+      <c r="BI89">
         <f t="shared" si="2"/>
         <v>1.6000467589999999E-3</v>
       </c>
-      <c r="BG89">
+      <c r="BJ89">
         <v>1.6000467589999999E-3</v>
       </c>
     </row>
-    <row r="90" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>0.32715899999999998</v>
       </c>
@@ -49665,54 +49784,54 @@
       <c r="AL90">
         <v>0.24491199999999999</v>
       </c>
-      <c r="AO90">
+      <c r="AQ90">
         <v>0.130384</v>
       </c>
-      <c r="AP90">
+      <c r="AR90">
         <v>0.23956</v>
       </c>
-      <c r="AQ90">
+      <c r="AS90">
         <v>0.13705100000000001</v>
       </c>
-      <c r="AR90">
+      <c r="AT90">
         <v>0.28810000000000002</v>
       </c>
-      <c r="AS90">
+      <c r="AU90">
         <v>1.6885000000000001E-2</v>
       </c>
-      <c r="AT90">
+      <c r="AV90">
         <v>7.0239999999999999E-3</v>
       </c>
-      <c r="AU90">
+      <c r="AW90">
         <v>1.048E-2</v>
       </c>
-      <c r="AV90">
+      <c r="AX90">
         <v>6.0629999999999998E-3</v>
       </c>
-      <c r="AX90">
+      <c r="BA90">
         <v>0.14395186304999999</v>
       </c>
-      <c r="AY90">
+      <c r="BB90">
         <v>1.3636007905000001E-2</v>
       </c>
-      <c r="AZ90">
+      <c r="BC90">
         <v>1.6172676110000001E-3</v>
       </c>
-      <c r="BA90">
+      <c r="BD90">
         <v>1.5961577880000001E-3</v>
       </c>
-      <c r="BC90" t="s">
+      <c r="BF90" t="s">
         <v>355</v>
       </c>
-      <c r="BF90">
+      <c r="BI90">
         <f t="shared" si="2"/>
         <v>1.5961577880000001E-3</v>
       </c>
-      <c r="BG90">
+      <c r="BJ90">
         <v>1.5961577880000001E-3</v>
       </c>
     </row>
-    <row r="91" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>0.32444699999999999</v>
       </c>
@@ -49788,54 +49907,54 @@
       <c r="AL91">
         <v>0.22989499999999999</v>
       </c>
-      <c r="AO91">
+      <c r="AQ91">
         <v>0.12581800000000001</v>
       </c>
-      <c r="AP91">
+      <c r="AR91">
         <v>0.24008599999999999</v>
       </c>
-      <c r="AQ91">
+      <c r="AS91">
         <v>0.132631</v>
       </c>
-      <c r="AR91">
+      <c r="AT91">
         <v>0.28293400000000002</v>
       </c>
-      <c r="AS91">
+      <c r="AU91">
         <v>1.5997000000000001E-2</v>
       </c>
-      <c r="AT91">
+      <c r="AV91">
         <v>6.6299999999999996E-3</v>
       </c>
-      <c r="AU91">
+      <c r="AW91">
         <v>9.9100000000000004E-3</v>
       </c>
-      <c r="AV91">
+      <c r="AX91">
         <v>5.7549999999999997E-3</v>
       </c>
-      <c r="AX91">
+      <c r="BA91">
         <v>0.13788126409099999</v>
       </c>
-      <c r="AY91">
+      <c r="BB91">
         <v>1.2896374799E-2</v>
       </c>
-      <c r="AZ91">
+      <c r="BC91">
         <v>1.612310065E-3</v>
       </c>
-      <c r="BA91">
+      <c r="BD91">
         <v>1.592552406E-3</v>
       </c>
-      <c r="BC91" t="s">
+      <c r="BF91" t="s">
         <v>356</v>
       </c>
-      <c r="BF91">
+      <c r="BI91">
         <f t="shared" si="2"/>
         <v>1.592552406E-3</v>
       </c>
-      <c r="BG91">
+      <c r="BJ91">
         <v>1.592552406E-3</v>
       </c>
     </row>
-    <row r="92" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>0.32163700000000001</v>
       </c>
@@ -49911,54 +50030,54 @@
       <c r="AL92">
         <v>0.22627700000000001</v>
       </c>
-      <c r="AO92">
+      <c r="AQ92">
         <v>0.121457</v>
       </c>
-      <c r="AP92">
+      <c r="AR92">
         <v>0.248447</v>
       </c>
-      <c r="AQ92">
+      <c r="AS92">
         <v>0.12845100000000001</v>
       </c>
-      <c r="AR92">
+      <c r="AT92">
         <v>0.275453</v>
       </c>
-      <c r="AS92">
+      <c r="AU92">
         <v>1.5162999999999999E-2</v>
       </c>
-      <c r="AT92">
+      <c r="AV92">
         <v>6.2779999999999997E-3</v>
       </c>
-      <c r="AU92">
+      <c r="AW92">
         <v>9.3769999999999999E-3</v>
       </c>
-      <c r="AV92">
+      <c r="AX92">
         <v>5.4479999999999997E-3</v>
       </c>
-      <c r="AX92">
+      <c r="BA92">
         <v>0.13307273387900001</v>
       </c>
-      <c r="AY92">
+      <c r="BB92">
         <v>1.2200922705000001E-2</v>
       </c>
-      <c r="AZ92">
+      <c r="BC92">
         <v>1.6082144580000001E-3</v>
       </c>
-      <c r="BA92">
+      <c r="BD92">
         <v>1.5890845100000001E-3</v>
       </c>
-      <c r="BC92" t="s">
+      <c r="BF92" t="s">
         <v>357</v>
       </c>
-      <c r="BF92">
+      <c r="BI92">
         <f t="shared" si="2"/>
         <v>1.5890845100000001E-3</v>
       </c>
-      <c r="BG92">
+      <c r="BJ92">
         <v>1.5890845100000001E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>0.31891999999999998</v>
       </c>
@@ -50034,54 +50153,54 @@
       <c r="AL93">
         <v>0.220142</v>
       </c>
-      <c r="AO93">
+      <c r="AQ93">
         <v>0.116828</v>
       </c>
-      <c r="AP93">
+      <c r="AR93">
         <v>0.25246000000000002</v>
       </c>
-      <c r="AQ93">
+      <c r="AS93">
         <v>0.12374499999999999</v>
       </c>
-      <c r="AR93">
+      <c r="AT93">
         <v>0.26829799999999998</v>
       </c>
-      <c r="AS93">
+      <c r="AU93">
         <v>1.4378E-2</v>
       </c>
-      <c r="AT93">
+      <c r="AV93">
         <v>5.9540000000000001E-3</v>
       </c>
-      <c r="AU93">
+      <c r="AW93">
         <v>8.8859999999999998E-3</v>
       </c>
-      <c r="AV93">
+      <c r="AX93">
         <v>5.1879999999999999E-3</v>
       </c>
-      <c r="AX93">
+      <c r="BA93">
         <v>0.12759819626800001</v>
       </c>
-      <c r="AY93">
+      <c r="BB93">
         <v>1.1554871685999999E-2</v>
       </c>
-      <c r="AZ93">
+      <c r="BC93">
         <v>1.6040903280000001E-3</v>
       </c>
-      <c r="BA93">
+      <c r="BD93">
         <v>1.5857770340000001E-3</v>
       </c>
-      <c r="BC93" t="s">
+      <c r="BF93" t="s">
         <v>358</v>
       </c>
-      <c r="BF93">
+      <c r="BI93">
         <f t="shared" si="2"/>
         <v>1.5857770340000001E-3</v>
       </c>
-      <c r="BG93">
+      <c r="BJ93">
         <v>1.5857770340000001E-3</v>
       </c>
     </row>
-    <row r="94" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>0.31625999999999999</v>
       </c>
@@ -50157,54 +50276,54 @@
       <c r="AL94">
         <v>0.212226</v>
       </c>
-      <c r="AO94">
+      <c r="AQ94">
         <v>0.111779</v>
       </c>
-      <c r="AP94">
+      <c r="AR94">
         <v>0.24867400000000001</v>
       </c>
-      <c r="AQ94">
+      <c r="AS94">
         <v>0.11946900000000001</v>
       </c>
-      <c r="AR94">
+      <c r="AT94">
         <v>0.267017</v>
       </c>
-      <c r="AS94">
+      <c r="AU94">
         <v>1.3644E-2</v>
       </c>
-      <c r="AT94">
+      <c r="AV94">
         <v>5.6490000000000004E-3</v>
       </c>
-      <c r="AU94">
+      <c r="AW94">
         <v>8.4309999999999993E-3</v>
       </c>
-      <c r="AV94">
+      <c r="AX94">
         <v>4.9290000000000002E-3</v>
       </c>
-      <c r="AX94">
+      <c r="BA94">
         <v>0.122549764812</v>
       </c>
-      <c r="AY94">
+      <c r="BB94">
         <v>1.0952894576000001E-2</v>
       </c>
-      <c r="AZ94">
+      <c r="BC94">
         <v>1.599921496E-3</v>
       </c>
-      <c r="BA94">
+      <c r="BD94">
         <v>1.5826973830000001E-3</v>
       </c>
-      <c r="BC94" t="s">
+      <c r="BF94" t="s">
         <v>359</v>
       </c>
-      <c r="BF94">
+      <c r="BI94">
         <f t="shared" si="2"/>
         <v>1.5826973830000001E-3</v>
       </c>
-      <c r="BG94">
+      <c r="BJ94">
         <v>1.5826973830000001E-3</v>
       </c>
     </row>
-    <row r="95" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>0.31374200000000002</v>
       </c>
@@ -50280,54 +50399,54 @@
       <c r="AL95">
         <v>0.207261</v>
       </c>
-      <c r="AO95">
+      <c r="AQ95">
         <v>0.10784000000000001</v>
       </c>
-      <c r="AP95">
+      <c r="AR95">
         <v>0.23903099999999999</v>
       </c>
-      <c r="AQ95">
+      <c r="AS95">
         <v>0.115315</v>
       </c>
-      <c r="AR95">
+      <c r="AT95">
         <v>0.267509</v>
       </c>
-      <c r="AS95">
+      <c r="AU95">
         <v>1.2952E-2</v>
       </c>
-      <c r="AT95">
+      <c r="AV95">
         <v>5.3730000000000002E-3</v>
       </c>
-      <c r="AU95">
+      <c r="AW95">
         <v>8.005E-3</v>
       </c>
-      <c r="AV95">
+      <c r="AX95">
         <v>4.712E-3</v>
       </c>
-      <c r="AX95">
+      <c r="BA95">
         <v>0.118507504463</v>
       </c>
-      <c r="AY95">
+      <c r="BB95">
         <v>1.0384954512E-2</v>
       </c>
-      <c r="AZ95">
+      <c r="BC95">
         <v>1.59601518E-3</v>
       </c>
-      <c r="BA95">
+      <c r="BD95">
         <v>1.5797114470000001E-3</v>
       </c>
-      <c r="BC95" t="s">
+      <c r="BF95" t="s">
         <v>360</v>
       </c>
-      <c r="BF95">
+      <c r="BI95">
         <f t="shared" si="2"/>
         <v>1.5797114470000001E-3</v>
       </c>
-      <c r="BG95">
+      <c r="BJ95">
         <v>1.5797114470000001E-3</v>
       </c>
     </row>
-    <row r="96" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>0.31129299999999999</v>
       </c>
@@ -50403,54 +50522,54 @@
       <c r="AL96">
         <v>0.199021</v>
       </c>
-      <c r="AO96">
+      <c r="AQ96">
         <v>0.103825</v>
       </c>
-      <c r="AP96">
+      <c r="AR96">
         <v>0.22797100000000001</v>
       </c>
-      <c r="AQ96">
+      <c r="AS96">
         <v>0.112356</v>
       </c>
-      <c r="AR96">
+      <c r="AT96">
         <v>0.26477699999999998</v>
       </c>
-      <c r="AS96">
+      <c r="AU96">
         <v>1.2304000000000001E-2</v>
       </c>
-      <c r="AT96">
+      <c r="AV96">
         <v>5.1219999999999998E-3</v>
       </c>
-      <c r="AU96">
+      <c r="AW96">
         <v>7.6059999999999999E-3</v>
       </c>
-      <c r="AV96">
+      <c r="AX96">
         <v>4.4949999999999999E-3</v>
       </c>
-      <c r="AX96">
+      <c r="BA96">
         <v>0.11447129398600001</v>
       </c>
-      <c r="AY96">
+      <c r="BB96">
         <v>9.8570026460000001E-3</v>
       </c>
-      <c r="AZ96">
+      <c r="BC96">
         <v>1.592242392E-3</v>
       </c>
-      <c r="BA96">
+      <c r="BD96">
         <v>1.5766992000000001E-3</v>
       </c>
-      <c r="BC96" t="s">
+      <c r="BF96" t="s">
         <v>361</v>
       </c>
-      <c r="BF96">
+      <c r="BI96">
         <f t="shared" si="2"/>
         <v>1.5766992000000001E-3</v>
       </c>
-      <c r="BG96">
+      <c r="BJ96">
         <v>1.5766992000000001E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>0.30883699999999997</v>
       </c>
@@ -50526,54 +50645,54 @@
       <c r="AL97">
         <v>0.194582</v>
       </c>
-      <c r="AO97">
+      <c r="AQ97">
         <v>9.9708000000000005E-2</v>
       </c>
-      <c r="AP97">
+      <c r="AR97">
         <v>0.21945000000000001</v>
       </c>
-      <c r="AQ97">
+      <c r="AS97">
         <v>0.108469</v>
       </c>
-      <c r="AR97">
+      <c r="AT97">
         <v>0.27346999999999999</v>
       </c>
-      <c r="AS97">
+      <c r="AU97">
         <v>1.1697000000000001E-2</v>
       </c>
-      <c r="AT97">
+      <c r="AV97">
         <v>4.8840000000000003E-3</v>
       </c>
-      <c r="AU97">
+      <c r="AW97">
         <v>7.2350000000000001E-3</v>
       </c>
-      <c r="AV97">
+      <c r="AX97">
         <v>4.3119999999999999E-3</v>
       </c>
-      <c r="AX97">
+      <c r="BA97">
         <v>0.110092274845</v>
       </c>
-      <c r="AY97">
+      <c r="BB97">
         <v>9.3654189259999993E-3</v>
       </c>
-      <c r="AZ97">
+      <c r="BC97">
         <v>1.5888004559999999E-3</v>
       </c>
-      <c r="BA97">
+      <c r="BD97">
         <v>1.5737458599999999E-3</v>
       </c>
-      <c r="BC97" t="s">
+      <c r="BF97" t="s">
         <v>362</v>
       </c>
-      <c r="BF97">
+      <c r="BI97">
         <f t="shared" si="2"/>
         <v>1.5737458599999999E-3</v>
       </c>
-      <c r="BG97">
+      <c r="BJ97">
         <v>1.5737458599999999E-3</v>
       </c>
     </row>
-    <row r="98" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>0.30654999999999999</v>
       </c>
@@ -50649,54 +50768,54 @@
       <c r="AL98">
         <v>0.185977</v>
       </c>
-      <c r="AO98">
+      <c r="AQ98">
         <v>9.5800999999999997E-2</v>
       </c>
-      <c r="AP98">
+      <c r="AR98">
         <v>0.20941499999999999</v>
       </c>
-      <c r="AQ98">
+      <c r="AS98">
         <v>0.104078</v>
       </c>
-      <c r="AR98">
+      <c r="AT98">
         <v>0.26113700000000001</v>
       </c>
-      <c r="AS98">
+      <c r="AU98">
         <v>1.1124999999999999E-2</v>
       </c>
-      <c r="AT98">
+      <c r="AV98">
         <v>4.6690000000000004E-3</v>
       </c>
-      <c r="AU98">
+      <c r="AW98">
         <v>6.8929999999999998E-3</v>
       </c>
-      <c r="AV98">
+      <c r="AX98">
         <v>4.1310000000000001E-3</v>
       </c>
-      <c r="AX98">
+      <c r="BA98">
         <v>0.10595575720100001</v>
       </c>
-      <c r="AY98">
+      <c r="BB98">
         <v>8.9051937679999991E-3</v>
       </c>
-      <c r="AZ98">
+      <c r="BC98">
         <v>1.585455961E-3</v>
       </c>
-      <c r="BA98">
+      <c r="BD98">
         <v>1.5709276780000001E-3</v>
       </c>
-      <c r="BC98" t="s">
+      <c r="BF98" t="s">
         <v>363</v>
       </c>
-      <c r="BF98">
+      <c r="BI98">
         <f t="shared" si="2"/>
         <v>1.5709276780000001E-3</v>
       </c>
-      <c r="BG98">
+      <c r="BJ98">
         <v>1.5709276780000001E-3</v>
       </c>
     </row>
-    <row r="99" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>0.304255</v>
       </c>
@@ -50772,54 +50891,54 @@
       <c r="AL99">
         <v>0.18060200000000001</v>
       </c>
-      <c r="AO99">
+      <c r="AQ99">
         <v>9.1883000000000006E-2</v>
       </c>
-      <c r="AP99">
+      <c r="AR99">
         <v>0.20519799999999999</v>
       </c>
-      <c r="AQ99">
+      <c r="AS99">
         <v>0.103161</v>
       </c>
-      <c r="AR99">
+      <c r="AT99">
         <v>0.25349899999999997</v>
       </c>
-      <c r="AS99">
+      <c r="AU99">
         <v>1.059E-2</v>
       </c>
-      <c r="AT99">
+      <c r="AV99">
         <v>4.4739999999999997E-3</v>
       </c>
-      <c r="AU99">
+      <c r="AW99">
         <v>6.5760000000000002E-3</v>
       </c>
-      <c r="AV99">
+      <c r="AX99">
         <v>3.9760000000000004E-3</v>
       </c>
-      <c r="AX99">
+      <c r="BA99">
         <v>0.102624945343</v>
       </c>
-      <c r="AY99">
+      <c r="BB99">
         <v>8.4746712819999993E-3</v>
       </c>
-      <c r="AZ99">
+      <c r="BC99">
         <v>1.5820544210000001E-3</v>
       </c>
-      <c r="BA99">
+      <c r="BD99">
         <v>1.568185864E-3</v>
       </c>
-      <c r="BC99" t="s">
+      <c r="BF99" t="s">
         <v>364</v>
       </c>
-      <c r="BF99">
+      <c r="BI99">
         <f t="shared" si="2"/>
         <v>1.568185864E-3</v>
       </c>
-      <c r="BG99">
+      <c r="BJ99">
         <v>1.568185864E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>0.301954</v>
       </c>
@@ -50895,54 +51014,54 @@
       <c r="AL100">
         <v>0.17550399999999999</v>
       </c>
-      <c r="AO100">
+      <c r="AQ100">
         <v>8.9398000000000005E-2</v>
       </c>
-      <c r="AP100">
+      <c r="AR100">
         <v>0.20192599999999999</v>
       </c>
-      <c r="AQ100">
+      <c r="AS100">
         <v>0.101447</v>
       </c>
-      <c r="AR100">
+      <c r="AT100">
         <v>0.23982200000000001</v>
       </c>
-      <c r="AS100">
+      <c r="AU100">
         <v>1.0087E-2</v>
       </c>
-      <c r="AT100">
+      <c r="AV100">
         <v>4.2909999999999997E-3</v>
       </c>
-      <c r="AU100">
+      <c r="AW100">
         <v>6.2810000000000001E-3</v>
       </c>
-      <c r="AV100">
+      <c r="AX100">
         <v>3.8249999999999998E-3</v>
       </c>
-      <c r="AX100">
+      <c r="BA100">
         <v>0.10060104727700001</v>
       </c>
-      <c r="AY100">
+      <c r="BB100">
         <v>8.07098113E-3</v>
       </c>
-      <c r="AZ100">
+      <c r="BC100">
         <v>1.578868367E-3</v>
       </c>
-      <c r="BA100">
+      <c r="BD100">
         <v>1.565503539E-3</v>
       </c>
-      <c r="BC100" t="s">
+      <c r="BF100" t="s">
         <v>365</v>
       </c>
-      <c r="BF100">
+      <c r="BI100">
         <f t="shared" si="2"/>
         <v>1.565503539E-3</v>
       </c>
-      <c r="BG100">
+      <c r="BJ100">
         <v>1.565503539E-3</v>
       </c>
     </row>
-    <row r="101" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>0.29975400000000002</v>
       </c>
@@ -51018,54 +51137,54 @@
       <c r="AL101">
         <v>0.169263</v>
       </c>
-      <c r="AO101">
+      <c r="AQ101">
         <v>8.5545999999999997E-2</v>
       </c>
-      <c r="AP101">
+      <c r="AR101">
         <v>0.20569000000000001</v>
       </c>
-      <c r="AQ101">
+      <c r="AS101">
         <v>9.9962999999999996E-2</v>
       </c>
-      <c r="AR101">
+      <c r="AT101">
         <v>0.23324</v>
       </c>
-      <c r="AS101">
+      <c r="AU101">
         <v>9.6150000000000003E-3</v>
       </c>
-      <c r="AT101">
+      <c r="AV101">
         <v>4.1219999999999998E-3</v>
       </c>
-      <c r="AU101">
+      <c r="AW101">
         <v>6.0049999999999999E-3</v>
       </c>
-      <c r="AV101">
+      <c r="AX101">
         <v>3.6930000000000001E-3</v>
       </c>
-      <c r="AX101">
+      <c r="BA101">
         <v>9.6812672912999997E-2</v>
       </c>
-      <c r="AY101">
+      <c r="BB101">
         <v>7.6963575560000004E-3</v>
       </c>
-      <c r="AZ101">
+      <c r="BC101">
         <v>1.5757812650000001E-3</v>
       </c>
-      <c r="BA101">
+      <c r="BD101">
         <v>1.5629348349999999E-3</v>
       </c>
-      <c r="BC101" t="s">
+      <c r="BF101" t="s">
         <v>366</v>
       </c>
-      <c r="BF101">
+      <c r="BI101">
         <f t="shared" si="2"/>
         <v>1.5629348349999999E-3</v>
       </c>
-      <c r="BG101">
+      <c r="BJ101">
         <v>1.5629348349999999E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>0.29762699999999997</v>
       </c>
@@ -51141,54 +51260,54 @@
       <c r="AL102">
         <v>0.16569400000000001</v>
       </c>
-      <c r="AO102">
+      <c r="AQ102">
         <v>8.2711000000000007E-2</v>
       </c>
-      <c r="AP102">
+      <c r="AR102">
         <v>0.202629</v>
       </c>
-      <c r="AQ102">
+      <c r="AS102">
         <v>9.8642999999999995E-2</v>
       </c>
-      <c r="AR102">
+      <c r="AT102">
         <v>0.22781699999999999</v>
       </c>
-      <c r="AS102">
+      <c r="AU102">
         <v>9.1739999999999999E-3</v>
       </c>
-      <c r="AT102">
+      <c r="AV102">
         <v>3.9709999999999997E-3</v>
       </c>
-      <c r="AU102">
+      <c r="AW102">
         <v>5.7479999999999996E-3</v>
       </c>
-      <c r="AV102">
+      <c r="AX102">
         <v>3.5690000000000001E-3</v>
       </c>
-      <c r="AX102">
+      <c r="BA102">
         <v>9.3960605562000005E-2</v>
       </c>
-      <c r="AY102">
+      <c r="BB102">
         <v>7.346860599E-3</v>
       </c>
-      <c r="AZ102">
+      <c r="BC102">
         <v>1.572768437E-3</v>
       </c>
-      <c r="BA102">
+      <c r="BD102">
         <v>1.560447039E-3</v>
       </c>
-      <c r="BC102" t="s">
+      <c r="BF102" t="s">
         <v>367</v>
       </c>
-      <c r="BF102">
+      <c r="BI102">
         <f t="shared" si="2"/>
         <v>1.560447039E-3</v>
       </c>
-      <c r="BG102">
+      <c r="BJ102">
         <v>1.560447039E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>0.29550799999999999</v>
       </c>
@@ -51264,54 +51383,55 @@
       <c r="AL103">
         <v>0.16072700000000001</v>
       </c>
-      <c r="AO103" s="23">
+      <c r="AQ103" s="23">
         <v>7.9161999999999996E-2</v>
       </c>
-      <c r="AP103" s="14">
+      <c r="AR103" s="14">
         <v>0.19963700000000001</v>
       </c>
-      <c r="AQ103" s="14">
+      <c r="AS103" s="14">
         <v>9.8531999999999995E-2</v>
       </c>
-      <c r="AR103">
+      <c r="AT103">
         <v>0.225634</v>
       </c>
-      <c r="AS103" s="14">
+      <c r="AU103" s="14">
         <v>8.7580000000000002E-3</v>
       </c>
-      <c r="AT103" s="23">
+      <c r="AV103" s="23">
         <v>3.8289999999999999E-3</v>
       </c>
-      <c r="AU103" s="14">
+      <c r="AW103" s="14">
         <v>5.5079999999999999E-3</v>
       </c>
-      <c r="AV103" s="23">
+      <c r="AX103" s="23">
         <v>3.457E-3</v>
       </c>
-      <c r="AX103">
+      <c r="AY103" s="23"/>
+      <c r="BA103">
         <v>9.1441050171999994E-2</v>
       </c>
-      <c r="AY103">
+      <c r="BB103">
         <v>7.0200269109999998E-3</v>
       </c>
-      <c r="AZ103">
+      <c r="BC103">
         <v>1.5699758659999999E-3</v>
       </c>
-      <c r="BA103">
+      <c r="BD103">
         <v>1.557961456E-3</v>
       </c>
-      <c r="BC103" t="s">
+      <c r="BF103" t="s">
         <v>368</v>
       </c>
-      <c r="BF103">
+      <c r="BI103">
         <f t="shared" si="2"/>
         <v>1.557961456E-3</v>
       </c>
-      <c r="BG103">
+      <c r="BJ103">
         <v>1.557961456E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>0.29358000000000001</v>
       </c>
@@ -51337,7 +51457,7 @@
         <v>4.0850000000000001E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>0.291468</v>
       </c>
@@ -51363,7 +51483,7 @@
         <v>3.947E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>0.289524</v>
       </c>
@@ -51389,7 +51509,7 @@
         <v>3.8189999999999999E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>0.287524</v>
       </c>
@@ -51415,7 +51535,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>0.28567100000000001</v>
       </c>
@@ -51441,7 +51561,7 @@
         <v>3.5899999999999999E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>0.28379199999999999</v>
       </c>
@@ -51467,7 +51587,7 @@
         <v>3.4880000000000002E-3</v>
       </c>
     </row>
-    <row r="110" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>0.28197499999999998</v>
       </c>
@@ -51493,7 +51613,7 @@
         <v>3.3939999999999999E-3</v>
       </c>
     </row>
-    <row r="111" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>0.28018799999999999</v>
       </c>
@@ -51519,7 +51639,7 @@
         <v>3.307E-3</v>
       </c>
     </row>
-    <row r="112" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:62" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>0.27847699999999997</v>
       </c>

--- a/research/HyperParams.xlsx
+++ b/research/HyperParams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Subnet-18-Zeus\research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AFBBDC-D4CB-43D4-9335-B694F95A1C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3700DFF2-626F-41F0-885D-451E08049DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" activeTab="3" xr2:uid="{701B61B4-A6E2-434A-B336-77C79E78CCA1}"/>
   </bookViews>
